--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -79,7 +79,7 @@
     <t xml:space="preserve">Also Show Under Objective</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional. The ID of a Strategic Plan Objective (ob…) to show the same KPI under in the Strategic Plan Goal View as well. For more than one Objective, separate the IDs with commas, such as ob18, ob19. Leave blank if the KPI does not belong under an Objective.</t>
+    <t xml:space="preserve">Optional. The ID of a Strategic Plan Objective (ob…) to show the same KPI under in the Strategic Plan Goal View as well. For more than one Objective, separate the IDs with commas, such as ob18, ob19. The KPI's status then counts toward that Objective's color. Leave blank if the KPI does not belong under an Objective.</t>
   </si>
   <si>
     <t xml:space="preserve">Objective Name (auto)</t>
@@ -151,7 +151,7 @@
     <t xml:space="preserve">Drives Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes: this KPI sets the color of its Key Service or Program on the dashboard. No: the KPI is shown but does not change any color. Has no effect on Work Systems or Objectives: a Work System always takes its color from its Key Services, and an Objective from the Programs tagged to it.</t>
+    <t xml:space="preserve">Yes: this KPI sets the color of its Key Service or Program on the dashboard. No: the KPI is shown but does not change any color. Has no effect on Work Systems or Objectives: a Work System always takes its color from its Key Services, and an Objective from the Programs tagged to it plus any KPIs shown under it.</t>
   </si>
   <si>
     <t xml:space="preserve">After editing</t>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="399">
   <si>
     <t xml:space="preserve">KPI tracking workbook</t>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t xml:space="preserve">Benchmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">Every 2 years</t>
@@ -2042,17 +2039,17 @@
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="S2" s="2"/>
     </row>
@@ -10163,7 +10160,7 @@
         <v>59</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="n">
@@ -10173,7 +10170,7 @@
         <v>76.6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10181,7 +10178,7 @@
         <v>59</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8" t="n">
@@ -10191,7 +10188,7 @@
         <v>75.1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10199,7 +10196,7 @@
         <v>59</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="n">
@@ -10215,10 +10212,10 @@
         <v>59</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>79.9</v>
@@ -10231,10 +10228,10 @@
         <v>59</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>78.2</v>
@@ -18222,33 +18219,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -18256,13 +18253,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -18270,13 +18267,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -18284,13 +18281,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -18298,13 +18295,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -18312,13 +18309,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -18326,65 +18323,65 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -18396,2506 +18393,2506 @@
         <v>61</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="D27" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>135</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="D29" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>139</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>141</v>
-      </c>
       <c r="D31" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>143</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>145</v>
-      </c>
       <c r="D33" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="D34" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>149</v>
-      </c>
       <c r="D35" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>151</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>153</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="D38" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="D39" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>159</v>
-      </c>
       <c r="D40" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="D41" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>163</v>
-      </c>
       <c r="D42" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>165</v>
-      </c>
       <c r="D43" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>167</v>
-      </c>
       <c r="D44" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>169</v>
-      </c>
       <c r="D45" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>171</v>
-      </c>
       <c r="D46" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="D47" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>175</v>
-      </c>
       <c r="D48" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="D49" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>179</v>
-      </c>
       <c r="D50" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="D51" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>183</v>
-      </c>
       <c r="D52" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="D53" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="D54" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="D55" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="D56" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>193</v>
-      </c>
       <c r="D57" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>195</v>
-      </c>
       <c r="D58" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>197</v>
-      </c>
       <c r="D59" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>199</v>
-      </c>
       <c r="D60" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>201</v>
-      </c>
       <c r="D61" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>203</v>
-      </c>
       <c r="D62" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>205</v>
-      </c>
       <c r="D63" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>207</v>
-      </c>
       <c r="D64" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="D65" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>211</v>
-      </c>
       <c r="D66" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>213</v>
-      </c>
       <c r="D67" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>215</v>
-      </c>
       <c r="D68" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>217</v>
-      </c>
       <c r="D69" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>219</v>
-      </c>
       <c r="D70" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>221</v>
-      </c>
       <c r="D71" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C72" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>223</v>
-      </c>
       <c r="D72" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>225</v>
-      </c>
       <c r="D73" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>227</v>
-      </c>
       <c r="D74" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>229</v>
-      </c>
       <c r="D75" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="D76" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>233</v>
-      </c>
       <c r="D77" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>235</v>
-      </c>
       <c r="D78" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>237</v>
-      </c>
       <c r="D79" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>239</v>
-      </c>
       <c r="D80" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>241</v>
-      </c>
       <c r="D81" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>243</v>
-      </c>
       <c r="D82" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>245</v>
-      </c>
       <c r="D83" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>247</v>
-      </c>
       <c r="D84" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F84" s="10"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>249</v>
-      </c>
       <c r="D85" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F85" s="10"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>251</v>
-      </c>
       <c r="D86" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>253</v>
-      </c>
       <c r="D87" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F87" s="10"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B88" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>255</v>
-      </c>
       <c r="D88" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F88" s="10"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B89" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>257</v>
-      </c>
       <c r="D89" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F89" s="10"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C90" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B90" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>259</v>
-      </c>
       <c r="D90" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F90" s="10"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B91" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>261</v>
-      </c>
       <c r="D91" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F91" s="10"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B92" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>263</v>
-      </c>
       <c r="D92" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F92" s="10"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>265</v>
-      </c>
       <c r="D93" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F93" s="10"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F94" s="10"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C95" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="D95" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F95" s="10"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>270</v>
-      </c>
       <c r="D96" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F96" s="10"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>272</v>
-      </c>
       <c r="D97" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F97" s="10"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B98" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>274</v>
-      </c>
       <c r="D98" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F98" s="10"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B99" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>276</v>
-      </c>
       <c r="D99" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F99" s="10"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C100" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>278</v>
-      </c>
       <c r="D100" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F100" s="10"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>280</v>
-      </c>
       <c r="D101" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F101" s="10"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>282</v>
-      </c>
       <c r="D102" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F102" s="10"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C103" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>284</v>
-      </c>
       <c r="D103" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F103" s="10"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>286</v>
-      </c>
       <c r="D104" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F104" s="10"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C105" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>288</v>
-      </c>
       <c r="D105" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F105" s="10"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>290</v>
-      </c>
       <c r="D106" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F106" s="10"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B107" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>292</v>
-      </c>
       <c r="D107" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B108" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>294</v>
-      </c>
       <c r="D108" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F108" s="10"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B109" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>296</v>
-      </c>
       <c r="D109" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F109" s="10"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C110" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B110" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>298</v>
-      </c>
       <c r="D110" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F110" s="10"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C111" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B111" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>300</v>
-      </c>
       <c r="D111" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F111" s="10"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B112" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>302</v>
-      </c>
       <c r="D112" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F112" s="10"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B113" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>304</v>
-      </c>
       <c r="D113" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F113" s="10"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>306</v>
-      </c>
       <c r="D114" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F114" s="10"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C115" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="B115" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>308</v>
-      </c>
       <c r="D115" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F115" s="10"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="B116" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>310</v>
-      </c>
       <c r="D116" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F116" s="10"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C117" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="B117" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>312</v>
-      </c>
       <c r="D117" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F117" s="10"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B118" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>314</v>
-      </c>
       <c r="D118" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C119" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B119" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>316</v>
-      </c>
       <c r="D119" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F119" s="10"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="B120" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>318</v>
-      </c>
       <c r="D120" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F120" s="10"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C121" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B121" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>320</v>
-      </c>
       <c r="D121" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F121" s="10"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C122" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B122" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>322</v>
-      </c>
       <c r="D122" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F122" s="10"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C123" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>324</v>
-      </c>
       <c r="D123" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F123" s="10"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C124" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="B124" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>326</v>
-      </c>
       <c r="D124" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F124" s="10"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B125" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>328</v>
-      </c>
       <c r="D125" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F125" s="10"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C126" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="B126" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>330</v>
-      </c>
       <c r="D126" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F126" s="10"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C127" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B127" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>332</v>
-      </c>
       <c r="D127" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F127" s="10"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C128" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>334</v>
-      </c>
       <c r="D128" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F128" s="10"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C129" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="B129" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>336</v>
-      </c>
       <c r="D129" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F129" s="10"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C130" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B130" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>338</v>
-      </c>
       <c r="D130" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F130" s="10"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C131" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B131" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>340</v>
-      </c>
       <c r="D131" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C132" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="B132" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>342</v>
-      </c>
       <c r="D132" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F132" s="10"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C133" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="B133" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>344</v>
-      </c>
       <c r="D133" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F133" s="10"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C134" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="B134" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>346</v>
-      </c>
       <c r="D134" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F134" s="10"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C135" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="B135" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>348</v>
-      </c>
       <c r="D135" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F135" s="10"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="B136" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>350</v>
-      </c>
       <c r="D136" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F136" s="10"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C137" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B137" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>352</v>
-      </c>
       <c r="D137" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F137" s="10"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B138" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>354</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>355</v>
       </c>
       <c r="D138" s="10"/>
       <c r="E138" s="10"/>
       <c r="F138" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C139" s="10" t="s">
         <v>357</v>
-      </c>
-      <c r="B139" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>358</v>
       </c>
       <c r="D139" s="10"/>
       <c r="E139" s="10"/>
       <c r="F139" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C140" s="10" t="s">
         <v>359</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>360</v>
       </c>
       <c r="D140" s="10"/>
       <c r="E140" s="10"/>
       <c r="F140" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C141" s="10" t="s">
         <v>361</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>362</v>
       </c>
       <c r="D141" s="10"/>
       <c r="E141" s="10"/>
       <c r="F141" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C142" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="B142" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>365</v>
       </c>
       <c r="D142" s="10"/>
       <c r="E142" s="10"/>
       <c r="F142" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C143" s="10" t="s">
         <v>366</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>367</v>
       </c>
       <c r="D143" s="10"/>
       <c r="E143" s="10"/>
       <c r="F143" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C144" s="10" t="s">
         <v>368</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>369</v>
       </c>
       <c r="D144" s="10"/>
       <c r="E144" s="10"/>
       <c r="F144" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C145" s="10" t="s">
         <v>371</v>
-      </c>
-      <c r="B145" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>372</v>
       </c>
       <c r="D145" s="10"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C146" s="10" t="s">
         <v>373</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="D146" s="10"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C147" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>376</v>
       </c>
       <c r="D147" s="10"/>
       <c r="E147" s="10"/>
       <c r="F147" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C148" s="10" t="s">
         <v>378</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C148" s="10" t="s">
-        <v>379</v>
       </c>
       <c r="D148" s="10"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C149" s="10" t="s">
         <v>380</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C149" s="10" t="s">
-        <v>381</v>
       </c>
       <c r="D149" s="10"/>
       <c r="E149" s="10"/>
       <c r="F149" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C150" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="D150" s="10"/>
       <c r="E150" s="10"/>
       <c r="F150" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C151" s="10" t="s">
         <v>384</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>385</v>
       </c>
       <c r="D151" s="10"/>
       <c r="E151" s="10"/>
       <c r="F151" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>386</v>
-      </c>
-      <c r="B152" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>387</v>
       </c>
       <c r="D152" s="10"/>
       <c r="E152" s="10"/>
       <c r="F152" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C153" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>389</v>
       </c>
       <c r="D153" s="10"/>
       <c r="E153" s="10"/>
       <c r="F153" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C154" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="D154" s="10"/>
       <c r="E154" s="10"/>
       <c r="F154" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20903,52 +20900,52 @@
         <v>63</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
       <c r="F155" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C156" s="10" t="s">
         <v>395</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C156" s="10" t="s">
-        <v>396</v>
       </c>
       <c r="D156" s="10"/>
       <c r="E156" s="10"/>
       <c r="F156" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C157" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="B157" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>398</v>
       </c>
       <c r="D157" s="10"/>
       <c r="E157" s="10"/>
       <c r="F157" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2723D8-F9A5-9E46-A751-B814E3082C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDD6D4B-20C6-3343-9DCE-DCF343CD2B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -2095,10 +2095,10 @@
         <v>29</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>68</v>
@@ -2152,10 +2152,10 @@
         <v>29</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>68</v>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDD6D4B-20C6-3343-9DCE-DCF343CD2B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDD6D4B-20C6-3343-9DCE-DCF343CD2B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AA08DE-2B5B-D242-B034-BC8BEE40749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16240" yWindow="660" windowWidth="14000" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="449">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1287,6 +1287,108 @@
   </si>
   <si>
     <t>SysAid</t>
+  </si>
+  <si>
+    <t>IT_TIXSLA</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>Urgent</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Help Desk Ticket SLA Compliance</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>IT_PHISHRATE</t>
+  </si>
+  <si>
+    <t>Organization Phish Prone Rate</t>
+  </si>
+  <si>
+    <t>KS7</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Every Quarter</t>
+  </si>
+  <si>
+    <t>Patrick Allmon</t>
+  </si>
+  <si>
+    <t>KnowBe4</t>
+  </si>
+  <si>
+    <t>2019-Q1</t>
+  </si>
+  <si>
+    <t>2020-Q1</t>
+  </si>
+  <si>
+    <t>2020-Q2</t>
+  </si>
+  <si>
+    <t>2022-Q2</t>
+  </si>
+  <si>
+    <t>2022-Q3</t>
+  </si>
+  <si>
+    <t>2022-Q4</t>
+  </si>
+  <si>
+    <t>2023-Q1</t>
+  </si>
+  <si>
+    <t>2023-Q2</t>
+  </si>
+  <si>
+    <t>2023-Q3</t>
+  </si>
+  <si>
+    <t>2023-Q4</t>
+  </si>
+  <si>
+    <t>2024-Q1</t>
+  </si>
+  <si>
+    <t>2024-Q2</t>
+  </si>
+  <si>
+    <t>2024-Q3</t>
+  </si>
+  <si>
+    <t>2024-Q4</t>
+  </si>
+  <si>
+    <t>2025-Q1</t>
+  </si>
+  <si>
+    <t>2025-Q2</t>
+  </si>
+  <si>
+    <t>2025-Q3</t>
+  </si>
+  <si>
+    <t>2025-Q4</t>
+  </si>
+  <si>
+    <t>2026-Q1</t>
+  </si>
+  <si>
+    <t>2026-Q2</t>
+  </si>
+  <si>
+    <t>2026-Q3</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1454,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,6 +1473,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1384,7 +1498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1424,6 +1538,25 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1686,6 +1819,26 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B33"/>
@@ -1920,7 +2073,7 @@
   <dimension ref="A1:S300"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -2172,57 +2325,117 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="6" t="str">
+    <row r="5" spans="1:19" s="21" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="19" t="str">
         <f>IF(D5="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C5="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))=C5),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="6" t="str">
+        <v>Help Desk</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="G5" s="19" t="str">
         <f>IF(F5="","",IF(ISNUMBER(SEARCH(",",F5)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F5,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F5,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+        <v>Key Service: Information Technology Services</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="18">
+        <v>2</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="18">
+        <v>5</v>
+      </c>
+      <c r="M5" s="18">
+        <v>15</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+    </row>
+    <row r="6" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>195</v>
+      </c>
       <c r="E6" s="6" t="str">
         <f>IF(D6="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C6="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))=C6),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F6" s="7"/>
+        <v>Cybersecurity</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>423</v>
+      </c>
       <c r="G6" s="6" t="str">
         <f>IF(F6="","",IF(ISNUMBER(SEARCH(",",F6)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
+        <v>Key Service: Information Technology Services</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="2">
+        <v>5</v>
+      </c>
+      <c r="M6" s="2">
+        <v>15</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>427</v>
+      </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
@@ -10189,7 +10402,8 @@
   <dimension ref="A1:G1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -10491,342 +10705,690 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>416</v>
+      </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="E17" s="8">
+        <v>95</v>
+      </c>
+      <c r="F17" s="8">
+        <v>100</v>
+      </c>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>420</v>
+      </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="E18" s="8">
+        <v>95</v>
+      </c>
+      <c r="F18" s="8">
+        <v>100</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>417</v>
+      </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="E19" s="8">
+        <v>95</v>
+      </c>
+      <c r="F19" s="8">
+        <v>100</v>
+      </c>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>418</v>
+      </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="E20" s="8">
+        <v>95</v>
+      </c>
+      <c r="F20" s="8">
+        <v>100</v>
+      </c>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>416</v>
+      </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="8">
+        <v>95</v>
+      </c>
+      <c r="F21" s="8">
+        <v>100</v>
+      </c>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>420</v>
+      </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="E22" s="8">
+        <v>95</v>
+      </c>
+      <c r="F22" s="8">
+        <v>100</v>
+      </c>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>417</v>
+      </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="8">
+        <v>95</v>
+      </c>
+      <c r="F23" s="8">
+        <v>100</v>
+      </c>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>418</v>
+      </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="E24" s="8">
+        <v>95</v>
+      </c>
+      <c r="F24" s="8">
+        <v>100</v>
+      </c>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>416</v>
+      </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="E25" s="8">
+        <v>95</v>
+      </c>
+      <c r="F25" s="8">
+        <v>100</v>
+      </c>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>420</v>
+      </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="E26" s="8">
+        <v>95</v>
+      </c>
+      <c r="F26" s="8">
+        <v>100</v>
+      </c>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>417</v>
+      </c>
       <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="E27" s="8">
+        <v>95</v>
+      </c>
+      <c r="F27" s="8">
+        <v>100</v>
+      </c>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>418</v>
+      </c>
       <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="E28" s="8">
+        <v>95</v>
+      </c>
+      <c r="F28" s="8">
+        <v>100</v>
+      </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>416</v>
+      </c>
       <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="8">
+        <v>95</v>
+      </c>
+      <c r="F29" s="8">
+        <v>100</v>
+      </c>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>420</v>
+      </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="E30" s="8">
+        <v>95</v>
+      </c>
+      <c r="F30" s="8">
+        <v>100</v>
+      </c>
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>417</v>
+      </c>
       <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="E31" s="8">
+        <v>95</v>
+      </c>
+      <c r="F31" s="8">
+        <v>100</v>
+      </c>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="8"/>
+      <c r="A32" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>418</v>
+      </c>
       <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="E32" s="8">
+        <v>95</v>
+      </c>
+      <c r="F32" s="8">
+        <v>100</v>
+      </c>
       <c r="G32" s="2"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="A33" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="D33" s="8">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="A34" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="D34" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="A35" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="D35" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
+      <c r="A36" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="D36" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="E36" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="A37" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="D37" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F37" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="A38" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="D38" s="8">
+        <v>0.63333333333333297</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F38" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="A39" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="D39" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F39" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="A40" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="D40" s="8">
+        <v>1.13333333333333</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F40" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G40" s="2"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
+      <c r="A41" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>436</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.56666666666666698</v>
+      </c>
+      <c r="E41" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F41" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="A42" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="D42" s="8">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+      <c r="A43" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="D43" s="8">
+        <v>1.5333333333333301</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F43" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
+      <c r="A44" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="D44" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F44" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="A45" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="E45" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F45" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="A46" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="D46" s="8">
+        <v>0.73333333333333295</v>
+      </c>
+      <c r="E46" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F46" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="A47" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="D47" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E47" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="A48" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="D48" s="8">
+        <v>8.3666666666666707</v>
+      </c>
+      <c r="E48" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="A49" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="D49" s="8">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E49" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F49" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="A50" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="D50" s="8">
+        <v>10.5666666666667</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F50" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
+      <c r="A51" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="E51" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F51" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G51" s="2"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="A52" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="D52" s="8">
+        <v>0.73333333333333295</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F52" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="A53" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0.76666666666666705</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3.9</v>
+      </c>
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="8"/>
       <c r="B54" s="9"/>
-      <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
@@ -10835,7 +11397,6 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="8"/>
       <c r="B55" s="9"/>
-      <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AA08DE-2B5B-D242-B034-BC8BEE40749C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B5E61D-8755-194A-98E7-E71B2713FBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16240" yWindow="660" windowWidth="14000" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16240" yWindow="660" windowWidth="14000" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="448">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1311,9 +1311,6 @@
   </si>
   <si>
     <t>Organization Phish Prone Rate</t>
-  </si>
-  <si>
-    <t>KS7</t>
   </si>
   <si>
     <t>No</t>
@@ -2400,7 +2397,7 @@
         <v>Cybersecurity</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>423</v>
+        <v>116</v>
       </c>
       <c r="G6" s="6" t="str">
         <f>IF(F6="","",IF(ISNUMBER(SEARCH(",",F6)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
@@ -2413,7 +2410,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>29</v>
@@ -2428,13 +2425,13 @@
         <v>68</v>
       </c>
       <c r="O6" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="P6" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="Q6" s="12" t="s">
         <v>426</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>427</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -11013,7 +11010,7 @@
         <v>421</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D33" s="8">
         <v>8.8000000000000007</v>
@@ -11031,7 +11028,7 @@
         <v>421</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D34" s="8">
         <v>8.9</v>
@@ -11049,7 +11046,7 @@
         <v>421</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D35" s="8">
         <v>2.4</v>
@@ -11067,7 +11064,7 @@
         <v>421</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D36" s="8">
         <v>1.05</v>
@@ -11085,7 +11082,7 @@
         <v>421</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D37" s="8">
         <v>0.9</v>
@@ -11103,7 +11100,7 @@
         <v>421</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D38" s="8">
         <v>0.63333333333333297</v>
@@ -11121,7 +11118,7 @@
         <v>421</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D39" s="8">
         <v>0.7</v>
@@ -11139,7 +11136,7 @@
         <v>421</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D40" s="8">
         <v>1.13333333333333</v>
@@ -11157,7 +11154,7 @@
         <v>421</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D41" s="8">
         <v>0.56666666666666698</v>
@@ -11175,7 +11172,7 @@
         <v>421</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D42" s="8">
         <v>0.83333333333333304</v>
@@ -11193,7 +11190,7 @@
         <v>421</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D43" s="8">
         <v>1.5333333333333301</v>
@@ -11211,7 +11208,7 @@
         <v>421</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D44" s="8">
         <v>1.1000000000000001</v>
@@ -11229,7 +11226,7 @@
         <v>421</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D45" s="8">
         <v>0.66666666666666696</v>
@@ -11247,7 +11244,7 @@
         <v>421</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D46" s="8">
         <v>0.73333333333333295</v>
@@ -11265,7 +11262,7 @@
         <v>421</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D47" s="8">
         <v>0.75</v>
@@ -11283,7 +11280,7 @@
         <v>421</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D48" s="8">
         <v>8.3666666666666707</v>
@@ -11301,7 +11298,7 @@
         <v>421</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D49" s="8">
         <v>9.6999999999999993</v>
@@ -11319,7 +11316,7 @@
         <v>421</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D50" s="8">
         <v>10.5666666666667</v>
@@ -11337,7 +11334,7 @@
         <v>421</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D51" s="8">
         <v>1.7</v>
@@ -11355,7 +11352,7 @@
         <v>421</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D52" s="8">
         <v>0.73333333333333295</v>
@@ -11373,7 +11370,7 @@
         <v>421</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D53" s="8">
         <v>0.76666666666666705</v>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B5E61D-8755-194A-98E7-E71B2713FBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133EA86F-5953-0945-959A-8CA0A3EE3DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16240" yWindow="660" windowWidth="14000" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="463">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1325,9 +1325,6 @@
     <t>KnowBe4</t>
   </si>
   <si>
-    <t>2019-Q1</t>
-  </si>
-  <si>
     <t>2020-Q1</t>
   </si>
   <si>
@@ -1386,13 +1383,61 @@
   </si>
   <si>
     <t>2026-Q3</t>
+  </si>
+  <si>
+    <t>Total Circulation</t>
+  </si>
+  <si>
+    <t>Physical Circulation</t>
+  </si>
+  <si>
+    <t>Digital Circulation</t>
+  </si>
+  <si>
+    <t>Visitation</t>
+  </si>
+  <si>
+    <t>Program Room Rentals</t>
+  </si>
+  <si>
+    <t>Total Computer Use</t>
+  </si>
+  <si>
+    <t>Unique Wireless Use</t>
+  </si>
+  <si>
+    <t>Reference Questions</t>
+  </si>
+  <si>
+    <t>Total Social Media user engagement</t>
+  </si>
+  <si>
+    <t>Patron per Program</t>
+  </si>
+  <si>
+    <t>Total Program Attendance</t>
+  </si>
+  <si>
+    <t>Total Outreach Contacts</t>
+  </si>
+  <si>
+    <t>LIB_VISITS</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Every Year</t>
+  </si>
+  <si>
+    <t>Luke Alvey-Henderson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1450,6 +1495,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1495,7 +1546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1554,6 +1605,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2436,9 +2491,10 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="22" t="s">
+        <v>447</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="6" t="str">
@@ -2463,9 +2519,11 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="22" t="s">
+        <v>448</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="6" t="str">
@@ -2490,9 +2548,11 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="22" t="s">
+        <v>449</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="6" t="str">
@@ -2517,36 +2577,66 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+    <row r="10" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>332</v>
+      </c>
       <c r="E10" s="6" t="str">
         <f>IF(D10="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C10="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0))=C10),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F10" s="7"/>
+        <v>Community Space</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="G10" s="6" t="str">
         <f>IF(F10="","",IF(ISNUMBER(SEARCH(",",F10)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F10,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F10,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+        <v>Key Service: Library &amp; Learning Services</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+      <c r="M10" s="2">
+        <v>15</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="23" t="s">
+        <v>451</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="6" t="str">
@@ -2571,9 +2661,11 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="23" t="s">
+        <v>452</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6" t="str">
@@ -2598,9 +2690,11 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="23" t="s">
+        <v>453</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6" t="str">
@@ -2625,9 +2719,11 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="23" t="s">
+        <v>454</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="6" t="str">
@@ -2652,9 +2748,11 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="23" t="s">
+        <v>455</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="6" t="str">
@@ -2679,9 +2777,11 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="22" t="s">
+        <v>456</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="6" t="str">
@@ -2706,9 +2806,11 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="22" t="s">
+        <v>457</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="6" t="str">
@@ -2733,9 +2835,11 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="22" t="s">
+        <v>458</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="6" t="str">
@@ -10396,7 +10500,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
@@ -11013,7 +11117,7 @@
         <v>427</v>
       </c>
       <c r="D33" s="8">
-        <v>8.8000000000000007</v>
+        <v>8.9</v>
       </c>
       <c r="E33" s="8">
         <v>3.9</v>
@@ -11031,7 +11135,7 @@
         <v>428</v>
       </c>
       <c r="D34" s="8">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="E34" s="8">
         <v>3.9</v>
@@ -11049,7 +11153,7 @@
         <v>429</v>
       </c>
       <c r="D35" s="8">
-        <v>2.4</v>
+        <v>1.05</v>
       </c>
       <c r="E35" s="8">
         <v>3.9</v>
@@ -11067,7 +11171,7 @@
         <v>430</v>
       </c>
       <c r="D36" s="8">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="E36" s="8">
         <v>3.9</v>
@@ -11085,7 +11189,7 @@
         <v>431</v>
       </c>
       <c r="D37" s="8">
-        <v>0.9</v>
+        <v>0.63333333333333297</v>
       </c>
       <c r="E37" s="8">
         <v>3.9</v>
@@ -11103,7 +11207,7 @@
         <v>432</v>
       </c>
       <c r="D38" s="8">
-        <v>0.63333333333333297</v>
+        <v>0.7</v>
       </c>
       <c r="E38" s="8">
         <v>3.9</v>
@@ -11121,7 +11225,7 @@
         <v>433</v>
       </c>
       <c r="D39" s="8">
-        <v>0.7</v>
+        <v>1.13333333333333</v>
       </c>
       <c r="E39" s="8">
         <v>3.9</v>
@@ -11139,7 +11243,7 @@
         <v>434</v>
       </c>
       <c r="D40" s="8">
-        <v>1.13333333333333</v>
+        <v>0.56666666666666698</v>
       </c>
       <c r="E40" s="8">
         <v>3.9</v>
@@ -11157,7 +11261,7 @@
         <v>435</v>
       </c>
       <c r="D41" s="8">
-        <v>0.56666666666666698</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="E41" s="8">
         <v>3.9</v>
@@ -11175,7 +11279,7 @@
         <v>436</v>
       </c>
       <c r="D42" s="8">
-        <v>0.83333333333333304</v>
+        <v>1.5333333333333301</v>
       </c>
       <c r="E42" s="8">
         <v>3.9</v>
@@ -11193,7 +11297,7 @@
         <v>437</v>
       </c>
       <c r="D43" s="8">
-        <v>1.5333333333333301</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E43" s="8">
         <v>3.9</v>
@@ -11211,7 +11315,7 @@
         <v>438</v>
       </c>
       <c r="D44" s="8">
-        <v>1.1000000000000001</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="E44" s="8">
         <v>3.9</v>
@@ -11229,7 +11333,7 @@
         <v>439</v>
       </c>
       <c r="D45" s="8">
-        <v>0.66666666666666696</v>
+        <v>0.73333333333333295</v>
       </c>
       <c r="E45" s="8">
         <v>3.9</v>
@@ -11247,7 +11351,7 @@
         <v>440</v>
       </c>
       <c r="D46" s="8">
-        <v>0.73333333333333295</v>
+        <v>0.75</v>
       </c>
       <c r="E46" s="8">
         <v>3.9</v>
@@ -11265,7 +11369,7 @@
         <v>441</v>
       </c>
       <c r="D47" s="8">
-        <v>0.75</v>
+        <v>8.3666666666666707</v>
       </c>
       <c r="E47" s="8">
         <v>3.9</v>
@@ -11283,7 +11387,7 @@
         <v>442</v>
       </c>
       <c r="D48" s="8">
-        <v>8.3666666666666707</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="E48" s="8">
         <v>3.9</v>
@@ -11301,7 +11405,7 @@
         <v>443</v>
       </c>
       <c r="D49" s="8">
-        <v>9.6999999999999993</v>
+        <v>10.5666666666667</v>
       </c>
       <c r="E49" s="8">
         <v>3.9</v>
@@ -11319,7 +11423,7 @@
         <v>444</v>
       </c>
       <c r="D50" s="8">
-        <v>10.5666666666667</v>
+        <v>1.7</v>
       </c>
       <c r="E50" s="8">
         <v>3.9</v>
@@ -11337,7 +11441,7 @@
         <v>445</v>
       </c>
       <c r="D51" s="8">
-        <v>1.7</v>
+        <v>0.73333333333333295</v>
       </c>
       <c r="E51" s="8">
         <v>3.9</v>
@@ -11355,7 +11459,7 @@
         <v>446</v>
       </c>
       <c r="D52" s="8">
-        <v>0.73333333333333295</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="E52" s="8">
         <v>3.9</v>
@@ -11367,68 +11471,119 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="D53" s="8">
-        <v>0.76666666666666705</v>
+        <v>65014</v>
       </c>
       <c r="E53" s="8">
-        <v>3.9</v>
+        <v>71834</v>
       </c>
       <c r="F53" s="8">
-        <v>3.9</v>
+        <v>62464</v>
       </c>
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="A54" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" s="8">
+        <v>103774</v>
+      </c>
+      <c r="E54" s="8">
+        <v>102033</v>
+      </c>
+      <c r="F54" s="8">
+        <v>88724</v>
+      </c>
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="A55" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8">
+        <v>211580</v>
+      </c>
+      <c r="E55" s="8">
+        <v>150513</v>
+      </c>
+      <c r="F55" s="8">
+        <v>130881</v>
+      </c>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
+      <c r="A56" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+      <c r="D56" s="8">
+        <v>280116</v>
+      </c>
+      <c r="E56" s="8">
+        <v>173234</v>
+      </c>
+      <c r="F56" s="8">
+        <v>150638</v>
+      </c>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
+      <c r="A57" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="D57" s="8">
+        <v>287958</v>
+      </c>
+      <c r="E57" s="8">
+        <v>197111</v>
+      </c>
+      <c r="F57">
+        <v>171401</v>
+      </c>
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
+      <c r="A58" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="D58" s="8">
+        <v>293189</v>
+      </c>
+      <c r="E58" s="8">
+        <v>201250</v>
+      </c>
+      <c r="F58" s="8">
+        <v>175000</v>
+      </c>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="14"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -19894,15 +20049,6 @@
       <c r="E999" s="8"/>
       <c r="F999" s="8"/>
       <c r="G999" s="2"/>
-    </row>
-    <row r="1000" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1000" s="8"/>
-      <c r="B1000" s="9"/>
-      <c r="C1000" s="8"/>
-      <c r="D1000" s="8"/>
-      <c r="E1000" s="8"/>
-      <c r="F1000" s="8"/>
-      <c r="G1000" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133EA86F-5953-0945-959A-8CA0A3EE3DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F739C-ACAC-714B-B06E-4A9ADC9990DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12720" yWindow="660" windowWidth="17520" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="513">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -230,9 +230,6 @@
     <t>Footnote</t>
   </si>
   <si>
-    <t>EMP-ENG</t>
-  </si>
-  <si>
     <t>Employee engagement score</t>
   </si>
   <si>
@@ -1274,24 +1271,9 @@
     <t>Solar Winds</t>
   </si>
   <si>
-    <t>Bonnie Kling</t>
-  </si>
-  <si>
-    <t>MC Lord</t>
-  </si>
-  <si>
-    <t>IT_PITSURV</t>
-  </si>
-  <si>
-    <t>Point in Time Help Desk Survey</t>
-  </si>
-  <si>
     <t>SysAid</t>
   </si>
   <si>
-    <t>IT_TIXSLA</t>
-  </si>
-  <si>
     <t>Minor</t>
   </si>
   <si>
@@ -1301,27 +1283,15 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>Help Desk Ticket SLA Compliance</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>IT_PHISHRATE</t>
-  </si>
-  <si>
-    <t>Organization Phish Prone Rate</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
     <t>Every Quarter</t>
   </si>
   <si>
-    <t>Patrick Allmon</t>
-  </si>
-  <si>
     <t>KnowBe4</t>
   </si>
   <si>
@@ -1385,59 +1355,239 @@
     <t>2026-Q3</t>
   </si>
   <si>
-    <t>Total Circulation</t>
-  </si>
-  <si>
-    <t>Physical Circulation</t>
-  </si>
-  <si>
-    <t>Digital Circulation</t>
-  </si>
-  <si>
     <t>Visitation</t>
   </si>
   <si>
-    <t>Program Room Rentals</t>
-  </si>
-  <si>
-    <t>Total Computer Use</t>
-  </si>
-  <si>
-    <t>Unique Wireless Use</t>
-  </si>
-  <si>
-    <t>Reference Questions</t>
-  </si>
-  <si>
-    <t>Total Social Media user engagement</t>
-  </si>
-  <si>
-    <t>Patron per Program</t>
-  </si>
-  <si>
-    <t>Total Program Attendance</t>
-  </si>
-  <si>
-    <t>Total Outreach Contacts</t>
-  </si>
-  <si>
-    <t>LIB_VISITS</t>
-  </si>
-  <si>
     <t>number</t>
   </si>
   <si>
     <t>Every Year</t>
   </si>
   <si>
-    <t>Luke Alvey-Henderson</t>
+    <t>HR Director</t>
+  </si>
+  <si>
+    <t>IT Director</t>
+  </si>
+  <si>
+    <t>Library Director</t>
+  </si>
+  <si>
+    <t>HR-TIMETOHIRE</t>
+  </si>
+  <si>
+    <t>HR-EMPENG</t>
+  </si>
+  <si>
+    <t>HR-VACANCYRATE</t>
+  </si>
+  <si>
+    <t>HR-QUITRATE</t>
+  </si>
+  <si>
+    <t>HR-CLICKTHRURATE</t>
+  </si>
+  <si>
+    <t>RISK-DOTCOMP</t>
+  </si>
+  <si>
+    <t>RISK-EMOD</t>
+  </si>
+  <si>
+    <t>RISK-PREMIUMSCORE</t>
+  </si>
+  <si>
+    <t>RISK-WORKCOMP</t>
+  </si>
+  <si>
+    <t>RISK-PROPCLAIMS</t>
+  </si>
+  <si>
+    <t>RISK-ACCIDENTREV</t>
+  </si>
+  <si>
+    <t>RISK-TRAININGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property casualty claims </t>
+  </si>
+  <si>
+    <t>Workers' compensation</t>
+  </si>
+  <si>
+    <t>Experience modificationscore</t>
+  </si>
+  <si>
+    <t>DOT compliance score</t>
+  </si>
+  <si>
+    <t>Accident review board scoring</t>
+  </si>
+  <si>
+    <t>Loss run report for workers' comp</t>
+  </si>
+  <si>
+    <t>Safety trainings</t>
+  </si>
+  <si>
+    <t>Safety / Risk Administrator</t>
+  </si>
+  <si>
+    <t>IT-PITSURV</t>
+  </si>
+  <si>
+    <t>IT-TIXSLA</t>
+  </si>
+  <si>
+    <t>IT-PHISHRATE</t>
+  </si>
+  <si>
+    <t>LIB-VISITS</t>
+  </si>
+  <si>
+    <t>LIB-CIRCTOTAL</t>
+  </si>
+  <si>
+    <t>LIB-CIRCPHYS</t>
+  </si>
+  <si>
+    <t>LIB_CIRCDIGI</t>
+  </si>
+  <si>
+    <t>LIB-ROOMRENTALS</t>
+  </si>
+  <si>
+    <t>LIB-COMPUSE</t>
+  </si>
+  <si>
+    <t>LIB-UNIQWIRELESS</t>
+  </si>
+  <si>
+    <t>LIB-REFQUEST</t>
+  </si>
+  <si>
+    <t>LIB-SOCIALENG</t>
+  </si>
+  <si>
+    <t>LIB-PATRONPPROG</t>
+  </si>
+  <si>
+    <t>LIB-PROGATTEND</t>
+  </si>
+  <si>
+    <t>LIB-OUTREACHCON</t>
+  </si>
+  <si>
+    <t>Click through rate on City's election landing page</t>
+  </si>
+  <si>
+    <t>Voter turnout (%)</t>
+  </si>
+  <si>
+    <t>Response rate for public election related questions</t>
+  </si>
+  <si>
+    <t>CLERK-CLICKTHRURATE</t>
+  </si>
+  <si>
+    <t>CLERK-VOTERTURNOUT</t>
+  </si>
+  <si>
+    <t>CLERK-LOGICTEST</t>
+  </si>
+  <si>
+    <t>Liquor and marijuana license turnaround</t>
+  </si>
+  <si>
+    <t>CLERK-QRESPRATE</t>
+  </si>
+  <si>
+    <t>CLERK-CORARESPRATE</t>
+  </si>
+  <si>
+    <t>CLERK-AGENDAPOST</t>
+  </si>
+  <si>
+    <t>CLERK-LIQMARJLIC</t>
+  </si>
+  <si>
+    <t>CLERK-BIZLIC</t>
+  </si>
+  <si>
+    <t>MUNI-SPECCOURT</t>
+  </si>
+  <si>
+    <t># cases resolved through graduating from specialty court</t>
+  </si>
+  <si>
+    <t>Time to hire</t>
+  </si>
+  <si>
+    <t>90 day quit rate</t>
+  </si>
+  <si>
+    <t>Full time vacancy rate</t>
+  </si>
+  <si>
+    <t>Point in time help desk survey</t>
+  </si>
+  <si>
+    <t>Help desk ticket SLA compliance</t>
+  </si>
+  <si>
+    <t>Organization phish prone rate</t>
+  </si>
+  <si>
+    <t>Total circulation</t>
+  </si>
+  <si>
+    <t>Physical circulation</t>
+  </si>
+  <si>
+    <t>Digital circulation</t>
+  </si>
+  <si>
+    <t>Program room rentals</t>
+  </si>
+  <si>
+    <t>Total computer use</t>
+  </si>
+  <si>
+    <t>Unique wireless use</t>
+  </si>
+  <si>
+    <t>Reference questions</t>
+  </si>
+  <si>
+    <t>Total social media user engagement</t>
+  </si>
+  <si>
+    <t>Patron per program</t>
+  </si>
+  <si>
+    <t>Total program attendance</t>
+  </si>
+  <si>
+    <t>Total outreach contacts</t>
+  </si>
+  <si>
+    <t>Records request response rate</t>
+  </si>
+  <si>
+    <t>Agenda posting time</t>
+  </si>
+  <si>
+    <t>Business license turnaround time</t>
+  </si>
+  <si>
+    <t>Logic and accuracy test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1501,8 +1651,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1521,18 +1679,6 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1546,7 +1692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1589,24 +1735,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2122,11 +2255,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S300"/>
+  <dimension ref="A1:S311"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
@@ -2145,7 +2278,7 @@
     <col min="19" max="19" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -2205,37 +2338,37 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="28" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E2" s="6" t="str">
         <f>IF(D2="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D2,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C2="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D2,'Dashboard Items'!$A$2:$A$500,0))=C2),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D2,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
         <v>Human Resources &amp; Workforce Development</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="6" t="str">
         <f>IF(F2="","",IF(ISNUMBER(SEARCH(",",F2)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F2,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F2,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
         <v>Objective: 6.1 Employee Growth and Retention</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" s="2">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>29</v>
@@ -2247,265 +2380,151 @@
         <v>15</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
+    <row r="3" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
       <c r="E3" s="6" t="str">
         <f>IF(D3="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C3="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0))=C3),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Network and Infrastructure Management</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="6" t="str">
-        <f>IF(F3="","",IF(ISNUMBER(SEARCH(",",F3)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F3,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F3,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v>Several items (the script lists them)</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="2">
-        <v>5</v>
-      </c>
-      <c r="M3" s="2">
-        <v>15</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>409</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>201</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
       <c r="E4" s="6" t="str">
         <f>IF(D4="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C4="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0))=C4),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Help Desk</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G4" s="6" t="str">
-        <f>IF(F4="","",IF(ISNUMBER(SEARCH(",",F4)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F4,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F4,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v>Key Service: Information Technology Services</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="2">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2">
-        <v>15</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q4" s="12" t="s">
-        <v>414</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" s="21" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="19" t="str">
+    <row r="5" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="6" t="str">
         <f>IF(D5="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C5="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))=C5),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Help Desk</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="19" t="str">
-        <f>IF(F5="","",IF(ISNUMBER(SEARCH(",",F5)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F5,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F5,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v>Key Service: Information Technology Services</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="18">
-        <v>2</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="18">
-        <v>5</v>
-      </c>
-      <c r="M5" s="18">
-        <v>15</v>
-      </c>
-      <c r="N5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>414</v>
-      </c>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-    </row>
-    <row r="6" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>195</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="6" t="str">
         <f>IF(D6="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C6="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))=C6),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Cybersecurity</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f>IF(F6="","",IF(ISNUMBER(SEARCH(",",F6)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F6,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v>Key Service: Information Technology Services</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5</v>
-      </c>
-      <c r="M6" s="2">
-        <v>15</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="P6" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q6" s="12" t="s">
-        <v>426</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="B7" s="22" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+    <row r="7" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E7" s="6" t="str">
         <f>IF(D7="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D7,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C7="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D7,'Dashboard Items'!$A$2:$A$500,0))=C7),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D7,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="6" t="str">
-        <f>IF(F7="","",IF(ISNUMBER(SEARCH(",",F7)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F7,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F7,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G7" s="6"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -2514,56 +2533,68 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
+      <c r="P7" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="s">
-        <v>448</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+    <row r="8" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E8" s="6" t="str">
         <f>IF(D8="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D8,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C8="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D8,'Dashboard Items'!$A$2:$A$500,0))=C8),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D8,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="G8" s="6" t="str">
-        <f>IF(F8="","",IF(ISNUMBER(SEARCH(",",F8)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F8,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F8,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G8" s="6"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
+      <c r="P8" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="22" t="s">
-        <v>449</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+    <row r="9" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E9" s="6" t="str">
         <f>IF(D9="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D9,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C9="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D9,'Dashboard Items'!$A$2:$A$500,0))=C9),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D9,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F9" s="7"/>
-      <c r="G9" s="6" t="str">
-        <f>IF(F9="","",IF(ISNUMBER(SEARCH(",",F9)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F9,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F9,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G9" s="6"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -2572,59 +2603,40 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:19" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>460</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="E10" s="6" t="str">
         <f>IF(D10="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C10="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0))=C10),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D10,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Community Space</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="G10" s="6" t="str">
-        <f>IF(F10="","",IF(ISNUMBER(SEARCH(",",F10)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F10,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F10,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v>Key Service: Library &amp; Learning Services</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="2">
-        <v>5</v>
-      </c>
-      <c r="M10" s="2">
-        <v>15</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>461</v>
-      </c>
+        <v>Risk Management</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" s="12" t="s">
         <v>462</v>
       </c>
@@ -2632,22 +2644,25 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+    <row r="11" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E11" s="6" t="str">
         <f>IF(D11="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D11,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C11="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D11,'Dashboard Items'!$A$2:$A$500,0))=C11),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D11,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="6" t="str">
-        <f>IF(F11="","",IF(ISNUMBER(SEARCH(",",F11)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F11,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F11,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G11" s="6"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -2656,189 +2671,319 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="P11" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+    <row r="12" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E12" s="6" t="str">
         <f>IF(D12="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D12,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C12="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D12,'Dashboard Items'!$A$2:$A$500,0))=C12),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D12,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="6" t="str">
-        <f>IF(F12="","",IF(ISNUMBER(SEARCH(",",F12)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F12,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F12,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G12" s="6"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>414</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
+      <c r="P12" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    <row r="13" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>189</v>
+      </c>
       <c r="E13" s="6" t="str">
         <f>IF(D13="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D13,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C13="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D13,'Dashboard Items'!$A$2:$A$500,0))=C13),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D13,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Risk Management</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="6" t="str">
-        <f>IF(F13="","",IF(ISNUMBER(SEARCH(",",F13)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F13,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F13,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
+      <c r="G13" s="6"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
+      <c r="P13" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E14" s="6" t="str">
         <f>IF(D14="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D14,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C14="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D14,'Dashboard Items'!$A$2:$A$500,0))=C14),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D14,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F14" s="7"/>
+        <v>Network and Infrastructure Management</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="G14" s="6" t="str">
         <f>IF(F14="","",IF(ISNUMBER(SEARCH(",",F14)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F14,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F14,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+        <v>Several items (the script lists them)</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5</v>
+      </c>
+      <c r="M14" s="2">
+        <v>15</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>408</v>
+      </c>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="23" t="s">
-        <v>455</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+    <row r="15" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>495</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>200</v>
+      </c>
       <c r="E15" s="6" t="str">
         <f>IF(D15="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D15,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C15="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D15,'Dashboard Items'!$A$2:$A$500,0))=C15),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D15,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F15" s="7"/>
+        <v>Help Desk</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="G15" s="6" t="str">
         <f>IF(F15="","",IF(ISNUMBER(SEARCH(",",F15)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F15,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F15,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
+        <v>Key Service: Information Technology Services</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L15" s="2">
+        <v>5</v>
+      </c>
+      <c r="M15" s="2">
+        <v>15</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>409</v>
+      </c>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22" t="s">
-        <v>456</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
+    <row r="16" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>200</v>
+      </c>
       <c r="E16" s="6" t="str">
         <f>IF(D16="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D16,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C16="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D16,'Dashboard Items'!$A$2:$A$500,0))=C16),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D16,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F16" s="7"/>
+        <v>Help Desk</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="G16" s="6" t="str">
         <f>IF(F16="","",IF(ISNUMBER(SEARCH(",",F16)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F16,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F16,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
+        <v>Key Service: Information Technology Services</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="2">
+        <v>5</v>
+      </c>
+      <c r="M16" s="2">
+        <v>15</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>409</v>
+      </c>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="22" t="s">
-        <v>457</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+    <row r="17" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>194</v>
+      </c>
       <c r="E17" s="6" t="str">
         <f>IF(D17="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D17,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C17="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D17,'Dashboard Items'!$A$2:$A$500,0))=C17),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D17,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F17" s="7"/>
+        <v>Cybersecurity</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="G17" s="6" t="str">
         <f>IF(F17="","",IF(ISNUMBER(SEARCH(",",F17)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F17,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F17,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
+        <v>Key Service: Information Technology Services</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="2">
+        <v>5</v>
+      </c>
+      <c r="M17" s="2">
+        <v>15</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="P17" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>416</v>
+      </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22" t="s">
-        <v>458</v>
+      <c r="A18" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>498</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -2864,9 +3009,13 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+    <row r="19" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>499</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="6" t="str">
@@ -2891,9 +3040,13 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+    <row r="20" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>500</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="6" t="str">
@@ -2918,36 +3071,68 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+    <row r="21" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>331</v>
+      </c>
       <c r="E21" s="6" t="str">
         <f>IF(D21="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D21,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C21="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D21,'Dashboard Items'!$A$2:$A$500,0))=C21),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D21,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F21" s="7"/>
+        <v>Community Space</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="G21" s="6" t="str">
         <f>IF(F21="","",IF(ISNUMBER(SEARCH(",",F21)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F21,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F21,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
+        <v>Key Service: Library &amp; Learning Services</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="2">
+        <v>5</v>
+      </c>
+      <c r="M21" s="2">
+        <v>15</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>442</v>
+      </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+    <row r="22" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>501</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="6" t="str">
@@ -2972,9 +3157,13 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+    <row r="23" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>502</v>
+      </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="6" t="str">
@@ -2999,9 +3188,13 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+    <row r="24" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>503</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="6" t="str">
@@ -3026,9 +3219,13 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+    <row r="25" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>504</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="6" t="str">
@@ -3053,9 +3250,13 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+    <row r="26" spans="1:19" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>505</v>
+      </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="6" t="str">
@@ -3080,9 +3281,13 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
+    <row r="27" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>506</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="6" t="str">
@@ -3107,9 +3312,13 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+    <row r="28" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>507</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="6" t="str">
@@ -3134,9 +3343,13 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+    <row r="29" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>508</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="6" t="str">
@@ -3161,14 +3374,22 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+    <row r="30" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>153</v>
+      </c>
       <c r="E30" s="6" t="str">
         <f>IF(D30="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D30,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C30="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D30,'Dashboard Items'!$A$2:$A$500,0))=C30),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D30,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Elections Administration</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="6" t="str">
@@ -3188,14 +3409,22 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+    <row r="31" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>153</v>
+      </c>
       <c r="E31" s="6" t="str">
         <f>IF(D31="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D31,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C31="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D31,'Dashboard Items'!$A$2:$A$500,0))=C31),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D31,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Elections Administration</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="6" t="str">
@@ -3215,19 +3444,29 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+    <row r="32" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A32" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>153</v>
+      </c>
       <c r="E32" s="6" t="str">
         <f>IF(D32="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D32,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C32="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D32,'Dashboard Items'!$A$2:$A$500,0))=C32),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D32,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F32" s="7"/>
+        <v>Elections Administration</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="G32" s="6" t="str">
         <f>IF(F32="","",IF(ISNUMBER(SEARCH(",",F32)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F32,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F32,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -3242,14 +3481,22 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+    <row r="33" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>153</v>
+      </c>
       <c r="E33" s="6" t="str">
         <f>IF(D33="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D33,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C33="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D33,'Dashboard Items'!$A$2:$A$500,0))=C33),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D33,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Elections Administration</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="6" t="str">
@@ -3269,19 +3516,29 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+    <row r="34" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A34" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>151</v>
+      </c>
       <c r="E34" s="6" t="str">
         <f>IF(D34="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D34,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C34="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D34,'Dashboard Items'!$A$2:$A$500,0))=C34),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D34,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F34" s="7"/>
+        <v>Records Management</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="G34" s="6" t="str">
         <f>IF(F34="","",IF(ISNUMBER(SEARCH(",",F34)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F34,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F34,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -3296,19 +3553,29 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+    <row r="35" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A35" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>155</v>
+      </c>
       <c r="E35" s="6" t="str">
         <f>IF(D35="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D35,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C35="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D35,'Dashboard Items'!$A$2:$A$500,0))=C35),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D35,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F35" s="7"/>
+        <v>Council/Board Support</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="G35" s="6" t="str">
         <f>IF(F35="","",IF(ISNUMBER(SEARCH(",",F35)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F35,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F35,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -3323,19 +3590,29 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+    <row r="36" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A36" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>157</v>
+      </c>
       <c r="E36" s="6" t="str">
         <f>IF(D36="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D36,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C36="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D36,'Dashboard Items'!$A$2:$A$500,0))=C36),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D36,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F36" s="7"/>
+        <v>Licensing</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="G36" s="6" t="str">
         <f>IF(F36="","",IF(ISNUMBER(SEARCH(",",F36)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F36,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F36,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -3350,19 +3627,29 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+    <row r="37" spans="1:19" ht="28" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>157</v>
+      </c>
       <c r="E37" s="6" t="str">
         <f>IF(D37="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D37,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C37="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D37,'Dashboard Items'!$A$2:$A$500,0))=C37),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D37,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F37" s="7"/>
+        <v>Licensing</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>106</v>
+      </c>
       <c r="G37" s="6" t="str">
         <f>IF(F37="","",IF(ISNUMBER(SEARCH(",",F37)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F37,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F37,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -3377,19 +3664,29 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+    <row r="38" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>256</v>
+      </c>
       <c r="E38" s="6" t="str">
         <f>IF(D38="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D38,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C38="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D38,'Dashboard Items'!$A$2:$A$500,0))=C38),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D38,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
-      </c>
-      <c r="F38" s="7"/>
+        <v>Specialty Court</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>125</v>
+      </c>
       <c r="G38" s="6" t="str">
         <f>IF(F38="","",IF(ISNUMBER(SEARCH(",",F38)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F38,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F38,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: Municipal Court</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -10478,17 +10775,314 @@
       <c r="R300" s="2"/>
       <c r="S300" s="2"/>
     </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="6" t="str">
+        <f>IF(D301="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D301,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C301="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D301,'Dashboard Items'!$A$2:$A$500,0))=C301),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D301,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F301" s="7"/>
+      <c r="G301" s="6" t="str">
+        <f>IF(F301="","",IF(ISNUMBER(SEARCH(",",F301)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F301,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F301,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H301" s="2"/>
+      <c r="I301" s="2"/>
+      <c r="J301" s="2"/>
+      <c r="K301" s="2"/>
+      <c r="L301" s="2"/>
+      <c r="M301" s="2"/>
+      <c r="N301" s="2"/>
+      <c r="O301" s="2"/>
+      <c r="P301" s="2"/>
+      <c r="Q301" s="2"/>
+      <c r="R301" s="2"/>
+      <c r="S301" s="2"/>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A302" s="2"/>
+      <c r="B302" s="2"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="6" t="str">
+        <f>IF(D302="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D302,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C302="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D302,'Dashboard Items'!$A$2:$A$500,0))=C302),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D302,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F302" s="7"/>
+      <c r="G302" s="6" t="str">
+        <f>IF(F302="","",IF(ISNUMBER(SEARCH(",",F302)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F302,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F302,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H302" s="2"/>
+      <c r="I302" s="2"/>
+      <c r="J302" s="2"/>
+      <c r="K302" s="2"/>
+      <c r="L302" s="2"/>
+      <c r="M302" s="2"/>
+      <c r="N302" s="2"/>
+      <c r="O302" s="2"/>
+      <c r="P302" s="2"/>
+      <c r="Q302" s="2"/>
+      <c r="R302" s="2"/>
+      <c r="S302" s="2"/>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="6" t="str">
+        <f>IF(D303="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D303,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C303="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D303,'Dashboard Items'!$A$2:$A$500,0))=C303),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D303,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F303" s="7"/>
+      <c r="G303" s="6" t="str">
+        <f>IF(F303="","",IF(ISNUMBER(SEARCH(",",F303)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F303,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F303,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H303" s="2"/>
+      <c r="I303" s="2"/>
+      <c r="J303" s="2"/>
+      <c r="K303" s="2"/>
+      <c r="L303" s="2"/>
+      <c r="M303" s="2"/>
+      <c r="N303" s="2"/>
+      <c r="O303" s="2"/>
+      <c r="P303" s="2"/>
+      <c r="Q303" s="2"/>
+      <c r="R303" s="2"/>
+      <c r="S303" s="2"/>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A304" s="2"/>
+      <c r="B304" s="2"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="6" t="str">
+        <f>IF(D304="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D304,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C304="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D304,'Dashboard Items'!$A$2:$A$500,0))=C304),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D304,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F304" s="7"/>
+      <c r="G304" s="6" t="str">
+        <f>IF(F304="","",IF(ISNUMBER(SEARCH(",",F304)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F304,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F304,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H304" s="2"/>
+      <c r="I304" s="2"/>
+      <c r="J304" s="2"/>
+      <c r="K304" s="2"/>
+      <c r="L304" s="2"/>
+      <c r="M304" s="2"/>
+      <c r="N304" s="2"/>
+      <c r="O304" s="2"/>
+      <c r="P304" s="2"/>
+      <c r="Q304" s="2"/>
+      <c r="R304" s="2"/>
+      <c r="S304" s="2"/>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="6" t="str">
+        <f>IF(D305="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D305,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C305="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D305,'Dashboard Items'!$A$2:$A$500,0))=C305),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D305,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F305" s="7"/>
+      <c r="G305" s="6" t="str">
+        <f>IF(F305="","",IF(ISNUMBER(SEARCH(",",F305)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F305,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F305,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H305" s="2"/>
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="2"/>
+      <c r="M305" s="2"/>
+      <c r="N305" s="2"/>
+      <c r="O305" s="2"/>
+      <c r="P305" s="2"/>
+      <c r="Q305" s="2"/>
+      <c r="R305" s="2"/>
+      <c r="S305" s="2"/>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="6" t="str">
+        <f>IF(D306="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D306,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C306="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D306,'Dashboard Items'!$A$2:$A$500,0))=C306),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D306,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F306" s="7"/>
+      <c r="G306" s="6" t="str">
+        <f>IF(F306="","",IF(ISNUMBER(SEARCH(",",F306)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F306,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F306,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H306" s="2"/>
+      <c r="I306" s="2"/>
+      <c r="J306" s="2"/>
+      <c r="K306" s="2"/>
+      <c r="L306" s="2"/>
+      <c r="M306" s="2"/>
+      <c r="N306" s="2"/>
+      <c r="O306" s="2"/>
+      <c r="P306" s="2"/>
+      <c r="Q306" s="2"/>
+      <c r="R306" s="2"/>
+      <c r="S306" s="2"/>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="6" t="str">
+        <f>IF(D307="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D307,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C307="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D307,'Dashboard Items'!$A$2:$A$500,0))=C307),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D307,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F307" s="7"/>
+      <c r="G307" s="6" t="str">
+        <f>IF(F307="","",IF(ISNUMBER(SEARCH(",",F307)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F307,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F307,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H307" s="2"/>
+      <c r="I307" s="2"/>
+      <c r="J307" s="2"/>
+      <c r="K307" s="2"/>
+      <c r="L307" s="2"/>
+      <c r="M307" s="2"/>
+      <c r="N307" s="2"/>
+      <c r="O307" s="2"/>
+      <c r="P307" s="2"/>
+      <c r="Q307" s="2"/>
+      <c r="R307" s="2"/>
+      <c r="S307" s="2"/>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="6" t="str">
+        <f>IF(D308="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D308,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C308="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D308,'Dashboard Items'!$A$2:$A$500,0))=C308),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D308,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F308" s="7"/>
+      <c r="G308" s="6" t="str">
+        <f>IF(F308="","",IF(ISNUMBER(SEARCH(",",F308)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F308,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F308,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H308" s="2"/>
+      <c r="I308" s="2"/>
+      <c r="J308" s="2"/>
+      <c r="K308" s="2"/>
+      <c r="L308" s="2"/>
+      <c r="M308" s="2"/>
+      <c r="N308" s="2"/>
+      <c r="O308" s="2"/>
+      <c r="P308" s="2"/>
+      <c r="Q308" s="2"/>
+      <c r="R308" s="2"/>
+      <c r="S308" s="2"/>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
+      <c r="E309" s="6" t="str">
+        <f>IF(D309="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D309,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C309="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D309,'Dashboard Items'!$A$2:$A$500,0))=C309),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D309,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F309" s="7"/>
+      <c r="G309" s="6" t="str">
+        <f>IF(F309="","",IF(ISNUMBER(SEARCH(",",F309)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F309,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F309,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H309" s="2"/>
+      <c r="I309" s="2"/>
+      <c r="J309" s="2"/>
+      <c r="K309" s="2"/>
+      <c r="L309" s="2"/>
+      <c r="M309" s="2"/>
+      <c r="N309" s="2"/>
+      <c r="O309" s="2"/>
+      <c r="P309" s="2"/>
+      <c r="Q309" s="2"/>
+      <c r="R309" s="2"/>
+      <c r="S309" s="2"/>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A310" s="2"/>
+      <c r="B310" s="2"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
+      <c r="E310" s="6" t="str">
+        <f>IF(D310="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D310,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C310="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D310,'Dashboard Items'!$A$2:$A$500,0))=C310),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D310,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F310" s="7"/>
+      <c r="G310" s="6" t="str">
+        <f>IF(F310="","",IF(ISNUMBER(SEARCH(",",F310)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F310,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F310,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H310" s="2"/>
+      <c r="I310" s="2"/>
+      <c r="J310" s="2"/>
+      <c r="K310" s="2"/>
+      <c r="L310" s="2"/>
+      <c r="M310" s="2"/>
+      <c r="N310" s="2"/>
+      <c r="O310" s="2"/>
+      <c r="P310" s="2"/>
+      <c r="Q310" s="2"/>
+      <c r="R310" s="2"/>
+      <c r="S310" s="2"/>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A311" s="2"/>
+      <c r="B311" s="2"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
+      <c r="E311" s="6" t="str">
+        <f>IF(D311="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D311,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C311="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D311,'Dashboard Items'!$A$2:$A$500,0))=C311),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D311,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
+        <v/>
+      </c>
+      <c r="F311" s="7"/>
+      <c r="G311" s="6" t="str">
+        <f>IF(F311="","",IF(ISNUMBER(SEARCH(",",F311)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F311,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F311,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
+        <v/>
+      </c>
+      <c r="H311" s="2"/>
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="2"/>
+      <c r="M311" s="2"/>
+      <c r="N311" s="2"/>
+      <c r="O311" s="2"/>
+      <c r="P311" s="2"/>
+      <c r="Q311" s="2"/>
+      <c r="R311" s="2"/>
+      <c r="S311" s="2"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="J2:J300 N2:N300" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J311 N2:N311" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Level" error="Choose Work System, Key Service or Program." sqref="C2:C300" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Level" error="Choose Work System, Key Service or Program." sqref="C2:C311" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Work System,Key Service,Program"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Status Based On" error="Choose Target or Benchmark." sqref="K2:K300" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Status Based On" error="Choose Target or Benchmark." sqref="K2:K311" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Target,Benchmark"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10500,10 +11094,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G999"/>
+  <dimension ref="A1:G996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
@@ -10511,7 +11105,7 @@
     <col min="7" max="7" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
@@ -10535,11 +11129,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>62</v>
+      <c r="A2" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8">
@@ -10550,15 +11144,15 @@
         <v>76.599999999999994</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>80</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8">
@@ -10569,15 +11163,15 @@
         <v>75.099999999999994</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>62</v>
+      <c r="A4" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8">
@@ -10590,14 +11184,14 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>62</v>
+      <c r="A5" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="D5" s="8">
         <v>79.900000000000006</v>
@@ -10607,14 +11201,14 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>62</v>
+      <c r="A6" s="12" t="s">
+        <v>444</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="8">
         <v>78.2</v>
@@ -10625,10 +11219,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8">
@@ -10644,10 +11238,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8">
@@ -10663,10 +11257,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8">
@@ -10681,11 +11275,11 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>72</v>
+      <c r="A10" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8">
@@ -10700,11 +11294,11 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>72</v>
+      <c r="A11" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8">
@@ -10719,11 +11313,11 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>72</v>
+      <c r="A12" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8">
@@ -10739,10 +11333,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8">
@@ -10756,10 +11350,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8">
@@ -10773,10 +11367,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8">
@@ -10790,10 +11384,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8">
@@ -10806,14 +11400,14 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
-        <v>415</v>
+      <c r="A17" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8">
@@ -10825,14 +11419,14 @@
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
-        <v>415</v>
+      <c r="A18" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8">
@@ -10844,14 +11438,14 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
-        <v>415</v>
+      <c r="A19" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8">
@@ -10863,14 +11457,14 @@
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
-        <v>415</v>
+      <c r="A20" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8">
@@ -10882,14 +11476,14 @@
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
-        <v>415</v>
+      <c r="A21" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8">
@@ -10901,14 +11495,14 @@
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
-        <v>415</v>
+      <c r="A22" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8">
@@ -10920,14 +11514,14 @@
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
-        <v>415</v>
+      <c r="A23" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8">
@@ -10939,14 +11533,14 @@
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
-        <v>415</v>
+      <c r="A24" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8">
@@ -10958,14 +11552,14 @@
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>415</v>
+      <c r="A25" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8">
@@ -10977,14 +11571,14 @@
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
-        <v>415</v>
+      <c r="A26" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8">
@@ -10996,14 +11590,14 @@
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
-        <v>415</v>
+      <c r="A27" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8">
@@ -11015,14 +11609,14 @@
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
-        <v>415</v>
+      <c r="A28" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8">
@@ -11034,14 +11628,14 @@
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
-        <v>415</v>
+      <c r="A29" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8">
@@ -11053,14 +11647,14 @@
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
-        <v>415</v>
+      <c r="A30" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8">
@@ -11072,14 +11666,14 @@
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
-        <v>415</v>
+      <c r="A31" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8">
@@ -11091,14 +11685,14 @@
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
-        <v>415</v>
+      <c r="A32" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8">
@@ -11111,10 +11705,10 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D33" s="8">
         <v>8.9</v>
@@ -11129,10 +11723,10 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="D34" s="8">
         <v>2.4</v>
@@ -11147,10 +11741,10 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D35" s="8">
         <v>1.05</v>
@@ -11165,10 +11759,10 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="D36" s="8">
         <v>0.9</v>
@@ -11183,10 +11777,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>421</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>431</v>
       </c>
       <c r="D37" s="8">
         <v>0.63333333333333297</v>
@@ -11201,10 +11795,10 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D38" s="8">
         <v>0.7</v>
@@ -11219,10 +11813,10 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D39" s="8">
         <v>1.13333333333333</v>
@@ -11237,10 +11831,10 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D40" s="8">
         <v>0.56666666666666698</v>
@@ -11255,10 +11849,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D41" s="8">
         <v>0.83333333333333304</v>
@@ -11273,10 +11867,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D42" s="8">
         <v>1.5333333333333301</v>
@@ -11291,10 +11885,10 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D43" s="8">
         <v>1.1000000000000001</v>
@@ -11309,10 +11903,10 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D44" s="8">
         <v>0.66666666666666696</v>
@@ -11327,10 +11921,10 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D45" s="8">
         <v>0.73333333333333295</v>
@@ -11345,10 +11939,10 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D46" s="8">
         <v>0.75</v>
@@ -11363,10 +11957,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D47" s="8">
         <v>8.3666666666666707</v>
@@ -11381,10 +11975,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D48" s="8">
         <v>9.6999999999999993</v>
@@ -11399,10 +11993,10 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="D49" s="8">
         <v>10.5666666666667</v>
@@ -11417,10 +12011,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D50" s="8">
         <v>1.7</v>
@@ -11435,10 +12029,10 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D51" s="8">
         <v>0.73333333333333295</v>
@@ -11453,10 +12047,10 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D52" s="8">
         <v>0.76666666666666705</v>
@@ -11471,10 +12065,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D53" s="8">
         <v>65014</v>
@@ -11489,10 +12083,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D54" s="8">
         <v>103774</v>
@@ -11507,10 +12101,10 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8">
@@ -11526,10 +12120,10 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8">
@@ -11545,10 +12139,10 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8">
@@ -11564,10 +12158,10 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8">
@@ -11582,7 +12176,9 @@
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="12"/>
+      <c r="A59" s="12" t="s">
+        <v>448</v>
+      </c>
       <c r="B59" s="14"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -11591,34 +12187,48 @@
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="8"/>
+      <c r="A60" s="12" t="s">
+        <v>449</v>
+      </c>
       <c r="B60" s="9"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="E60" s="8">
+        <v>1</v>
+      </c>
       <c r="F60" s="8"/>
       <c r="G60" s="2"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="8"/>
+      <c r="A61" s="12" t="s">
+        <v>453</v>
+      </c>
       <c r="B61" s="9"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="E61" s="8">
+        <v>2</v>
+      </c>
       <c r="F61" s="8"/>
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="8"/>
+      <c r="A62" s="12" t="s">
+        <v>454</v>
+      </c>
       <c r="B62" s="9"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="E62" s="8">
+        <v>90</v>
+      </c>
       <c r="F62" s="8"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="8"/>
+      <c r="A63" s="12" t="s">
+        <v>481</v>
+      </c>
       <c r="B63" s="9"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
@@ -11627,7 +12237,9 @@
       <c r="G63" s="2"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="8"/>
+      <c r="A64" s="12" t="s">
+        <v>485</v>
+      </c>
       <c r="B64" s="9"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -11636,7 +12248,9 @@
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="8"/>
+      <c r="A65" s="12" t="s">
+        <v>482</v>
+      </c>
       <c r="B65" s="9"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
@@ -11645,7 +12259,9 @@
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="8"/>
+      <c r="A66" s="12" t="s">
+        <v>483</v>
+      </c>
       <c r="B66" s="9"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -11654,7 +12270,9 @@
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="8"/>
+      <c r="A67" s="12" t="s">
+        <v>486</v>
+      </c>
       <c r="B67" s="9"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -11663,7 +12281,9 @@
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="8"/>
+      <c r="A68" s="12" t="s">
+        <v>487</v>
+      </c>
       <c r="B68" s="9"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -11672,7 +12292,9 @@
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="8"/>
+      <c r="A69" s="12" t="s">
+        <v>488</v>
+      </c>
       <c r="B69" s="9"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -11681,7 +12303,9 @@
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="8"/>
+      <c r="A70" s="12" t="s">
+        <v>489</v>
+      </c>
       <c r="B70" s="9"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -20022,33 +20646,6 @@
       <c r="E996" s="8"/>
       <c r="F996" s="8"/>
       <c r="G996" s="2"/>
-    </row>
-    <row r="997" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A997" s="8"/>
-      <c r="B997" s="9"/>
-      <c r="C997" s="8"/>
-      <c r="D997" s="8"/>
-      <c r="E997" s="8"/>
-      <c r="F997" s="8"/>
-      <c r="G997" s="2"/>
-    </row>
-    <row r="998" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A998" s="8"/>
-      <c r="B998" s="9"/>
-      <c r="C998" s="8"/>
-      <c r="D998" s="8"/>
-      <c r="E998" s="8"/>
-      <c r="F998" s="8"/>
-      <c r="G998" s="2"/>
-    </row>
-    <row r="999" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A999" s="8"/>
-      <c r="B999" s="9"/>
-      <c r="C999" s="8"/>
-      <c r="D999" s="8"/>
-      <c r="E999" s="8"/>
-      <c r="F999" s="8"/>
-      <c r="G999" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -20070,33 +20667,33 @@
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -20104,13 +20701,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -20118,13 +20715,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -20132,13 +20729,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -20146,13 +20743,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>102</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -20160,13 +20757,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -20174,2629 +20771,2629 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>133</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="10"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F26" s="10"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>143</v>
-      </c>
       <c r="D27" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>145</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="D29" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="10"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>149</v>
-      </c>
       <c r="D30" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" s="10"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>151</v>
-      </c>
       <c r="D31" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="10"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>153</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="D33" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F33" s="10"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="D34" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F34" s="10"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>159</v>
-      </c>
       <c r="D35" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F35" s="10"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F36" s="10"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>163</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" s="10"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>165</v>
-      </c>
       <c r="D38" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>167</v>
-      </c>
       <c r="D39" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" s="10"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>169</v>
-      </c>
       <c r="D40" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" s="10"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>171</v>
-      </c>
       <c r="D41" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" s="10"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="D42" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" s="10"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>175</v>
-      </c>
       <c r="D43" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" s="10"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>177</v>
-      </c>
       <c r="D44" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F44" s="10"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>179</v>
-      </c>
       <c r="D45" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F45" s="10"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>181</v>
-      </c>
       <c r="D46" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F46" s="10"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>183</v>
-      </c>
       <c r="D47" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F47" s="10"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="D48" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F48" s="10"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>187</v>
-      </c>
       <c r="D49" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F49" s="10"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>189</v>
-      </c>
       <c r="D50" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F50" s="10"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>191</v>
-      </c>
       <c r="D51" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F51" s="10"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>193</v>
-      </c>
       <c r="D52" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="10"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F53" s="10"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="D54" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F54" s="10"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>198</v>
-      </c>
       <c r="D55" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F55" s="10"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>200</v>
-      </c>
       <c r="D56" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F56" s="10"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>202</v>
-      </c>
       <c r="D57" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F57" s="10"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>204</v>
-      </c>
       <c r="D58" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F58" s="10"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="D59" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F59" s="10"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>208</v>
-      </c>
       <c r="D60" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F60" s="10"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="D61" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F61" s="10"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>212</v>
-      </c>
       <c r="D62" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F62" s="10"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>214</v>
-      </c>
       <c r="D63" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F63" s="10"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>216</v>
-      </c>
       <c r="D64" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F64" s="10"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>218</v>
-      </c>
       <c r="D65" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F65" s="10"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>220</v>
-      </c>
       <c r="D66" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F66" s="10"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>222</v>
-      </c>
       <c r="D67" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F67" s="10"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>224</v>
-      </c>
       <c r="D68" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F68" s="10"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>226</v>
-      </c>
       <c r="D69" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" s="10"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>228</v>
-      </c>
       <c r="D70" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F70" s="10"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>230</v>
-      </c>
       <c r="D71" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F71" s="10"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>232</v>
-      </c>
       <c r="D72" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F72" s="10"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="D73" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F73" s="10"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>236</v>
-      </c>
       <c r="D74" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F74" s="10"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>238</v>
-      </c>
       <c r="D75" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F75" s="10"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>240</v>
-      </c>
       <c r="D76" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F76" s="10"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>242</v>
-      </c>
       <c r="D77" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F77" s="10"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>244</v>
-      </c>
       <c r="D78" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>246</v>
-      </c>
       <c r="D79" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F79" s="10"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>248</v>
-      </c>
       <c r="D80" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F80" s="10"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>250</v>
-      </c>
       <c r="D81" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F81" s="10"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>252</v>
-      </c>
       <c r="D82" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F82" s="10"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>254</v>
-      </c>
       <c r="D83" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F83" s="10"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>256</v>
-      </c>
       <c r="D84" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F84" s="10"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>258</v>
-      </c>
       <c r="D85" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F85" s="10"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B86" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>260</v>
-      </c>
       <c r="D86" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F86" s="10"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B87" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>262</v>
-      </c>
       <c r="D87" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F87" s="10"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B88" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>264</v>
-      </c>
       <c r="D88" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F88" s="10"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B89" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>266</v>
-      </c>
       <c r="D89" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F89" s="10"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C90" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B90" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>268</v>
-      </c>
       <c r="D90" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E90" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F90" s="10"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="B91" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>270</v>
-      </c>
       <c r="D91" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F91" s="10"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C92" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B92" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>272</v>
-      </c>
       <c r="D92" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F92" s="10"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B93" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>274</v>
-      </c>
       <c r="D93" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F93" s="10"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F94" s="10"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B95" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" s="10" t="s">
-        <v>277</v>
-      </c>
       <c r="D95" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F95" s="10"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C96" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>279</v>
-      </c>
       <c r="D96" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F96" s="10"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>281</v>
-      </c>
       <c r="D97" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F97" s="10"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B98" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>283</v>
-      </c>
       <c r="D98" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F98" s="10"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B99" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>285</v>
-      </c>
       <c r="D99" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F99" s="10"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B100" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>287</v>
-      </c>
       <c r="D100" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F100" s="10"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C101" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>289</v>
-      </c>
       <c r="D101" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F101" s="10"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C102" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>291</v>
-      </c>
       <c r="D102" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F102" s="10"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C103" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>293</v>
-      </c>
       <c r="D103" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F103" s="10"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>295</v>
-      </c>
       <c r="D104" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F104" s="10"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C105" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>297</v>
-      </c>
       <c r="D105" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F105" s="10"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C106" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="D106" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F106" s="10"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B107" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>301</v>
-      </c>
       <c r="D107" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F107" s="10"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B108" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>303</v>
-      </c>
       <c r="D108" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E108" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F108" s="10"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B109" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>305</v>
-      </c>
       <c r="D109" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F109" s="10"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C110" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B110" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>307</v>
-      </c>
       <c r="D110" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F110" s="10"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C111" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B111" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>309</v>
-      </c>
       <c r="D111" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F111" s="10"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B112" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>311</v>
-      </c>
       <c r="D112" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E112" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F112" s="10"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B113" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>313</v>
-      </c>
       <c r="D113" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F113" s="10"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C114" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>315</v>
-      </c>
       <c r="D114" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F114" s="10"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C115" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B115" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>317</v>
-      </c>
       <c r="D115" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F115" s="10"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C116" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B116" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>319</v>
-      </c>
       <c r="D116" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E116" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F116" s="10"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C117" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B117" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>321</v>
-      </c>
       <c r="D117" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F117" s="10"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B118" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>323</v>
-      </c>
       <c r="D118" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E118" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F118" s="10"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C119" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B119" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>325</v>
-      </c>
       <c r="D119" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F119" s="10"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C120" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B120" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>327</v>
-      </c>
       <c r="D120" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E120" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F120" s="10"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C121" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B121" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>329</v>
-      </c>
       <c r="D121" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F121" s="10"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B122" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>331</v>
-      </c>
       <c r="D122" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E122" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F122" s="10"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C123" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B123" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>333</v>
-      </c>
       <c r="D123" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F123" s="10"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B124" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>335</v>
-      </c>
       <c r="D124" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F124" s="10"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B125" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>337</v>
-      </c>
       <c r="D125" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F125" s="10"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C126" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B126" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>339</v>
-      </c>
       <c r="D126" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F126" s="10"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C127" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B127" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>341</v>
-      </c>
       <c r="D127" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F127" s="10"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C128" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B128" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>343</v>
-      </c>
       <c r="D128" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F128" s="10"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C129" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B129" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>345</v>
-      </c>
       <c r="D129" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F129" s="10"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C130" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="B130" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C130" s="10" t="s">
-        <v>347</v>
-      </c>
       <c r="D130" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F130" s="10"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C131" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B131" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C131" s="10" t="s">
-        <v>349</v>
-      </c>
       <c r="D131" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F131" s="10"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C132" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="B132" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>351</v>
-      </c>
       <c r="D132" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F132" s="10"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C133" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="B133" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>353</v>
-      </c>
       <c r="D133" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F133" s="10"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C134" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B134" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="D134" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F134" s="10"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C135" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="B135" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>357</v>
-      </c>
       <c r="D135" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F135" s="10"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B136" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>359</v>
-      </c>
       <c r="D136" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E136" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F136" s="10"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C137" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B137" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>361</v>
-      </c>
       <c r="D137" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F137" s="10"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B138" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="C138" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="D138" s="10"/>
       <c r="E138" s="10"/>
       <c r="F138" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C139" s="10" t="s">
         <v>366</v>
-      </c>
-      <c r="B139" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C139" s="10" t="s">
-        <v>367</v>
       </c>
       <c r="D139" s="10"/>
       <c r="E139" s="10"/>
       <c r="F139" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C140" s="10" t="s">
         <v>368</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>369</v>
       </c>
       <c r="D140" s="10"/>
       <c r="E140" s="10"/>
       <c r="F140" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C141" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>371</v>
       </c>
       <c r="D141" s="10"/>
       <c r="E141" s="10"/>
       <c r="F141" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C142" s="10" t="s">
         <v>373</v>
-      </c>
-      <c r="B142" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="D142" s="10"/>
       <c r="E142" s="10"/>
       <c r="F142" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C143" s="10" t="s">
         <v>375</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C143" s="10" t="s">
-        <v>376</v>
       </c>
       <c r="D143" s="10"/>
       <c r="E143" s="10"/>
       <c r="F143" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C144" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>378</v>
       </c>
       <c r="D144" s="10"/>
       <c r="E144" s="10"/>
       <c r="F144" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C145" s="10" t="s">
         <v>380</v>
-      </c>
-      <c r="B145" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C145" s="10" t="s">
-        <v>381</v>
       </c>
       <c r="D145" s="10"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C146" s="10" t="s">
         <v>382</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C146" s="10" t="s">
-        <v>383</v>
       </c>
       <c r="D146" s="10"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C147" s="10" t="s">
         <v>384</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>385</v>
       </c>
       <c r="D147" s="10"/>
       <c r="E147" s="10"/>
       <c r="F147" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C148" s="10" t="s">
         <v>387</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C148" s="10" t="s">
-        <v>388</v>
       </c>
       <c r="D148" s="10"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C149" s="10" t="s">
         <v>389</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C149" s="10" t="s">
-        <v>390</v>
       </c>
       <c r="D149" s="10"/>
       <c r="E149" s="10"/>
       <c r="F149" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C150" s="10" t="s">
         <v>391</v>
-      </c>
-      <c r="B150" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>392</v>
       </c>
       <c r="D150" s="10"/>
       <c r="E150" s="10"/>
       <c r="F150" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C151" s="10" t="s">
         <v>393</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C151" s="10" t="s">
-        <v>394</v>
       </c>
       <c r="D151" s="10"/>
       <c r="E151" s="10"/>
       <c r="F151" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>395</v>
-      </c>
-      <c r="B152" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>396</v>
       </c>
       <c r="D152" s="10"/>
       <c r="E152" s="10"/>
       <c r="F152" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C153" s="10" t="s">
         <v>397</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>398</v>
       </c>
       <c r="D153" s="10"/>
       <c r="E153" s="10"/>
       <c r="F153" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C154" s="10" t="s">
         <v>400</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C154" s="10" t="s">
-        <v>401</v>
       </c>
       <c r="D154" s="10"/>
       <c r="E154" s="10"/>
       <c r="F154" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
       <c r="F155" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C156" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C156" s="10" t="s">
-        <v>405</v>
       </c>
       <c r="D156" s="10"/>
       <c r="E156" s="10"/>
       <c r="F156" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C157" s="10" t="s">
         <v>406</v>
-      </c>
-      <c r="B157" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C157" s="10" t="s">
-        <v>407</v>
       </c>
       <c r="D157" s="10"/>
       <c r="E157" s="10"/>
       <c r="F157" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7F739C-ACAC-714B-B06E-4A9ADC9990DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC67686-FFA3-DC46-BF05-C91278C3C561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12720" yWindow="660" windowWidth="17520" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15160" yWindow="660" windowWidth="15080" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="514">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1581,6 +1581,9 @@
   </si>
   <si>
     <t>Logic and accuracy test</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -2403,11 +2406,15 @@
       <c r="B3" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>183</v>
+      </c>
       <c r="E3" s="6" t="str">
         <f>IF(D3="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C3="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0))=C3),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D3,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Recruitment and Retention</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="6"/>
@@ -2431,11 +2438,15 @@
       <c r="B4" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>183</v>
+      </c>
       <c r="E4" s="6" t="str">
         <f>IF(D4="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C4="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0))=C4),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D4,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Recruitment and Retention</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="6"/>
@@ -2459,11 +2470,15 @@
       <c r="B5" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>183</v>
+      </c>
       <c r="E5" s="6" t="str">
         <f>IF(D5="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C5="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0))=C5),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D5,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Recruitment and Retention</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="6"/>
@@ -2485,11 +2500,15 @@
         <v>447</v>
       </c>
       <c r="B6" s="18"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>183</v>
+      </c>
       <c r="E6" s="6" t="str">
         <f>IF(D6="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C6="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0))=C6),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D6,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Recruitment and Retention</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6"/>
@@ -2985,11 +3004,15 @@
       <c r="B18" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>319</v>
+      </c>
       <c r="E18" s="6" t="str">
         <f>IF(D18="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D18,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C18="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D18,'Dashboard Items'!$A$2:$A$500,0))=C18),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D18,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Circulation Services</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="6" t="str">
@@ -3016,11 +3039,15 @@
       <c r="B19" s="16" t="s">
         <v>499</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>319</v>
+      </c>
       <c r="E19" s="6" t="str">
         <f>IF(D19="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D19,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C19="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D19,'Dashboard Items'!$A$2:$A$500,0))=C19),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D19,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Circulation Services</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="6" t="str">
@@ -3047,11 +3074,15 @@
       <c r="B20" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>319</v>
+      </c>
       <c r="E20" s="6" t="str">
         <f>IF(D20="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D20,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C20="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D20,'Dashboard Items'!$A$2:$A$500,0))=C20),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D20,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Circulation Services</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="6" t="str">
@@ -3133,11 +3164,15 @@
       <c r="B22" s="17" t="s">
         <v>501</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>331</v>
+      </c>
       <c r="E22" s="6" t="str">
         <f>IF(D22="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D22,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C22="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D22,'Dashboard Items'!$A$2:$A$500,0))=C22),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D22,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Community Space</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="6" t="str">
@@ -3164,11 +3199,15 @@
       <c r="B23" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>321</v>
+      </c>
       <c r="E23" s="6" t="str">
         <f>IF(D23="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D23,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C23="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D23,'Dashboard Items'!$A$2:$A$500,0))=C23),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D23,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Digital Learning</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="6" t="str">
@@ -3195,11 +3234,15 @@
       <c r="B24" s="17" t="s">
         <v>503</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>321</v>
+      </c>
       <c r="E24" s="6" t="str">
         <f>IF(D24="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D24,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C24="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D24,'Dashboard Items'!$A$2:$A$500,0))=C24),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D24,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Digital Learning</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="6" t="str">
@@ -3226,11 +3269,15 @@
       <c r="B25" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="E25" s="6" t="str">
         <f>IF(D25="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D25,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C25="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D25,'Dashboard Items'!$A$2:$A$500,0))=C25),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D25,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Cultural Programming</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="6" t="str">
@@ -3257,11 +3304,15 @@
       <c r="B26" s="17" t="s">
         <v>505</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="E26" s="6" t="str">
         <f>IF(D26="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D26,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C26="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D26,'Dashboard Items'!$A$2:$A$500,0))=C26),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D26,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Cultural Programming</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="6" t="str">
@@ -3288,11 +3339,15 @@
       <c r="B27" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="E27" s="6" t="str">
         <f>IF(D27="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D27,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C27="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D27,'Dashboard Items'!$A$2:$A$500,0))=C27),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D27,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Cultural Programming</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="6" t="str">
@@ -3319,11 +3374,15 @@
       <c r="B28" s="16" t="s">
         <v>507</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="E28" s="6" t="str">
         <f>IF(D28="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D28,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C28="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D28,'Dashboard Items'!$A$2:$A$500,0))=C28),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D28,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Cultural Programming</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="6" t="str">
@@ -3350,11 +3409,15 @@
       <c r="B29" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>327</v>
+      </c>
       <c r="E29" s="6" t="str">
         <f>IF(D29="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D29,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C29="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D29,'Dashboard Items'!$A$2:$A$500,0))=C29),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D29,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Cultural Programming</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="6" t="str">
@@ -11078,7 +11141,7 @@
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Level" error="Choose Work System, Key Service or Program." sqref="C2:C311" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Level" error="Choose Work System, Key Service or Program." sqref="C2:C22 C23:D24 C25:C311" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Work System,Key Service,Program"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -12179,7 +12242,9 @@
       <c r="A59" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="B59" s="14"/>
+      <c r="B59" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -12190,7 +12255,9 @@
       <c r="A60" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="B60" s="9"/>
+      <c r="B60" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8">
@@ -12203,7 +12270,9 @@
       <c r="A61" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="B61" s="9"/>
+      <c r="B61" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8">
@@ -12216,7 +12285,9 @@
       <c r="A62" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="B62" s="9"/>
+      <c r="B62" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8">
@@ -12229,7 +12300,9 @@
       <c r="A63" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="B63" s="9"/>
+      <c r="B63" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -12240,7 +12313,9 @@
       <c r="A64" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="B64" s="9"/>
+      <c r="B64" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -12251,7 +12326,9 @@
       <c r="A65" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="B65" s="9"/>
+      <c r="B65" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -12262,7 +12339,9 @@
       <c r="A66" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="B66" s="9"/>
+      <c r="B66" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -12273,7 +12352,9 @@
       <c r="A67" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="B67" s="9"/>
+      <c r="B67" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -12284,7 +12365,9 @@
       <c r="A68" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="B68" s="9"/>
+      <c r="B68" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -12295,7 +12378,9 @@
       <c r="A69" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="B69" s="9"/>
+      <c r="B69" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
@@ -12306,7 +12391,9 @@
       <c r="A70" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="B70" s="9"/>
+      <c r="B70" s="14" t="s">
+        <v>513</v>
+      </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC67686-FFA3-DC46-BF05-C91278C3C561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA953B49-6729-BF4B-B7E4-10DD7F60519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15160" yWindow="660" windowWidth="15080" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15160" yWindow="660" windowWidth="15080" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="515">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1584,6 +1584,9 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Job clickthrough rate</t>
   </si>
 </sst>
 </file>
@@ -2495,11 +2498,13 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="18" t="s">
+        <v>514</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>73</v>
       </c>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA953B49-6729-BF4B-B7E4-10DD7F60519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62575A8D-B11C-F549-885B-6D3F8BDEAEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15160" yWindow="660" windowWidth="15080" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15580" yWindow="660" windowWidth="14660" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="523">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1587,6 +1587,30 @@
   </si>
   <si>
     <t>Job clickthrough rate</t>
+  </si>
+  <si>
+    <t>PIO-ENGRATE</t>
+  </si>
+  <si>
+    <t>Social media engagement rate</t>
+  </si>
+  <si>
+    <t>Public Information Officer</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>Instagram, Facebook, LinkedIn, TikTok</t>
   </si>
 </sst>
 </file>
@@ -3732,7 +3756,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" ht="28" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>490</v>
       </c>
@@ -3756,27 +3780,55 @@
         <f>IF(F38="","",IF(ISNUMBER(SEARCH(",",F38)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F38,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F38,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
         <v>Key Service: Municipal Court</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
+      <c r="H38" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="2">
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" s="2">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2">
+        <v>15</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="P38" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q38" s="12" t="s">
+        <v>522</v>
+      </c>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="A39" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>159</v>
+      </c>
       <c r="E39" s="6" t="str">
         <f>IF(D39="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C39="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0))=C39),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v/>
+        <v>Public Outreach</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="6" t="str">
@@ -11162,7 +11214,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G996"/>
+  <dimension ref="A1:G995"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -12406,156 +12458,360 @@
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
+      <c r="A71" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D71" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="F71" s="8">
+        <v>2.6</v>
+      </c>
       <c r="G71" s="2"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
+      <c r="A72" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D72" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="E72" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="F72" s="8">
+        <v>2.6</v>
+      </c>
       <c r="G72" s="2"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
+      <c r="A73" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D73" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E73" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="F73" s="8">
+        <v>2.6</v>
+      </c>
       <c r="G73" s="2"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
+      <c r="A74" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D74" s="8">
+        <v>5.7</v>
+      </c>
+      <c r="E74" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="F74" s="8">
+        <v>2.6</v>
+      </c>
       <c r="G74" s="2"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
+      <c r="A75" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="D75" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="F75" s="8">
+        <v>3.5</v>
+      </c>
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
+      <c r="A76" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D76" s="8">
+        <v>8.4</v>
+      </c>
+      <c r="E76" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F76" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
+      <c r="A77" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D77" s="8">
+        <v>6.9</v>
+      </c>
+      <c r="E77" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F77" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
+      <c r="A78" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D78" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="E78" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F78" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="A79" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D79" s="8">
+        <v>6.3</v>
+      </c>
+      <c r="E79" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F79" s="8">
+        <v>2.5</v>
+      </c>
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
+      <c r="A80" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D80" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="E80" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F80" s="8">
+        <v>3.2</v>
+      </c>
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="A81" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D81" s="8">
+        <v>8</v>
+      </c>
+      <c r="E81" s="8">
+        <v>21.2</v>
+      </c>
+      <c r="F81" s="8">
+        <v>2.7</v>
+      </c>
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
+      <c r="A82" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D82" s="8">
+        <v>16.8</v>
+      </c>
+      <c r="E82" s="8">
+        <v>21.2</v>
+      </c>
+      <c r="F82" s="8">
+        <v>2.7</v>
+      </c>
       <c r="G82" s="2"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="A83" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D83" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="E83" s="8">
+        <v>21.2</v>
+      </c>
+      <c r="F83" s="8">
+        <v>2.7</v>
+      </c>
       <c r="G83" s="2"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
+      <c r="A84" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="D84" s="8">
+        <v>14.34</v>
+      </c>
+      <c r="E84" s="8">
+        <v>21.2</v>
+      </c>
+      <c r="F84" s="8">
+        <v>3.1</v>
+      </c>
       <c r="G84" s="2"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="A85" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D85" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="E85" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="F85" s="8">
+        <v>1.6</v>
+      </c>
       <c r="G85" s="2"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
+      <c r="A86" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D86" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E86" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="F86" s="8">
+        <v>1.6</v>
+      </c>
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
+      <c r="A87" s="12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D87" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="E87" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="F87" s="8">
+        <v>1.6</v>
+      </c>
       <c r="G87" s="2"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -20729,15 +20985,6 @@
       <c r="E995" s="8"/>
       <c r="F995" s="8"/>
       <c r="G995" s="2"/>
-    </row>
-    <row r="996" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A996" s="8"/>
-      <c r="B996" s="9"/>
-      <c r="C996" s="8"/>
-      <c r="D996" s="8"/>
-      <c r="E996" s="8"/>
-      <c r="F996" s="8"/>
-      <c r="G996" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62575A8D-B11C-F549-885B-6D3F8BDEAEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE528B8-680F-8F45-A01E-A3142412D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15580" yWindow="660" windowWidth="14660" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="660" windowWidth="27000" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="523">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -3824,16 +3824,18 @@
         <v>73</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E39" s="6" t="str">
         <f>IF(D39="","",IFERROR(IF(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0))="Objective","Objectives go in the next column",IF(OR(C39="",INDEX('Dashboard Items'!$B$2:$B$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0))=C39),INDEX('Dashboard Items'!$C$2:$C$500,MATCH(D39,'Dashboard Items'!$A$2:$A$500,0)),"Level does not match ID")),"ID not found"))</f>
-        <v>Public Outreach</v>
-      </c>
-      <c r="F39" s="7"/>
+        <v>Social Media</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>108</v>
+      </c>
       <c r="G39" s="6" t="str">
         <f>IF(F39="","",IF(ISNUMBER(SEARCH(",",F39)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$500,MATCH(F39,'Dashboard Items'!$A$2:$A$500,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$500,MATCH(F39,'Dashboard Items'!$A$2:$A$500,0)),"ID not found")))</f>
-        <v/>
+        <v>Key Service: Public Information &amp; Community Engagement</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -3813,7 +3813,7 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" ht="28" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>515</v>
       </c>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE528B8-680F-8F45-A01E-A3142412D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19FFA7C-656C-8245-B05E-75F560D77559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="660" windowWidth="27000" windowHeight="18980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35080" yWindow="1360" windowWidth="27000" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B954BF5D-F4E6-D54E-950F-30B9B3C1D474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC532635-3796-C94F-BAEF-8580074E06FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71100" yWindow="-7380" windowWidth="30240" windowHeight="19000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="510">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -11369,7 +11369,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G1002"/>
+  <dimension ref="A1:G997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -12864,15 +12864,17 @@
       <c r="B82" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="C82" s="49"/>
+      <c r="C82" s="51" t="s">
+        <v>507</v>
+      </c>
       <c r="D82" s="49">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E82" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F82" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G82" s="30"/>
     </row>
@@ -12883,15 +12885,17 @@
       <c r="B83" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="C83" s="49"/>
+      <c r="C83" s="51" t="s">
+        <v>507</v>
+      </c>
       <c r="D83" s="49">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E83" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F83" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G83" s="30"/>
     </row>
@@ -12902,15 +12906,17 @@
       <c r="B84" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="C84" s="49"/>
+      <c r="C84" s="51" t="s">
+        <v>507</v>
+      </c>
       <c r="D84" s="49">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E84" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F84" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G84" s="30"/>
     </row>
@@ -12921,15 +12927,17 @@
       <c r="B85" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C85" s="49"/>
+      <c r="C85" s="51" t="s">
+        <v>507</v>
+      </c>
       <c r="D85" s="49">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E85" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F85" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G85" s="30"/>
     </row>
@@ -12940,15 +12948,17 @@
       <c r="B86" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="49"/>
+      <c r="C86" s="51" t="s">
+        <v>507</v>
+      </c>
       <c r="D86" s="49">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="E86" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F86" s="49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G86" s="30"/>
     </row>
@@ -12960,10 +12970,10 @@
         <v>84</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D87" s="49">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="E87" s="49">
         <v>50</v>
@@ -12981,10 +12991,10 @@
         <v>77</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D88" s="49">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="E88" s="49">
         <v>50</v>
@@ -13002,10 +13012,10 @@
         <v>85</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D89" s="49">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="E89" s="49">
         <v>50</v>
@@ -13023,10 +13033,10 @@
         <v>79</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D90" s="49">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E90" s="49">
         <v>50</v>
@@ -13044,10 +13054,10 @@
         <v>86</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D91" s="49">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E91" s="49">
         <v>50</v>
@@ -13059,112 +13069,72 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B92" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C92" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D92" s="49">
-        <v>50</v>
-      </c>
-      <c r="E92" s="49">
-        <v>50</v>
-      </c>
-      <c r="F92" s="49">
-        <v>50</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="B92" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C92" s="49"/>
+      <c r="D92" s="49"/>
+      <c r="E92" s="49"/>
+      <c r="F92" s="49"/>
       <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B93" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C93" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D93" s="49">
-        <v>50</v>
-      </c>
-      <c r="E93" s="49">
-        <v>50</v>
-      </c>
-      <c r="F93" s="49">
-        <v>50</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="B93" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C93" s="49"/>
+      <c r="D93" s="49"/>
+      <c r="E93" s="49"/>
+      <c r="F93" s="49"/>
       <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B94" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C94" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D94" s="49">
-        <v>50</v>
-      </c>
-      <c r="E94" s="49">
-        <v>50</v>
-      </c>
-      <c r="F94" s="49">
-        <v>50</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="B94" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C94" s="49"/>
+      <c r="D94" s="49"/>
+      <c r="E94" s="49"/>
+      <c r="F94" s="49"/>
       <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B95" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C95" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D95" s="49">
-        <v>50</v>
-      </c>
-      <c r="E95" s="49">
-        <v>50</v>
-      </c>
-      <c r="F95" s="49">
-        <v>50</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="B95" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C95" s="49"/>
+      <c r="D95" s="49"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
       <c r="G95" s="30"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B96" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C96" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D96" s="49">
-        <v>50</v>
-      </c>
-      <c r="E96" s="49">
-        <v>50</v>
-      </c>
-      <c r="F96" s="49">
-        <v>50</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="B96" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C96" s="49"/>
+      <c r="D96" s="49"/>
+      <c r="E96" s="49"/>
+      <c r="F96" s="49"/>
       <c r="G96" s="30"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="28" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B97" s="49" t="s">
         <v>489</v>
@@ -13177,7 +13147,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="28" t="s">
-        <v>506</v>
+        <v>458</v>
       </c>
       <c r="B98" s="49" t="s">
         <v>489</v>
@@ -13190,182 +13160,162 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="28" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B99" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C99" s="49"/>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="49"/>
+        <v>83</v>
+      </c>
+      <c r="C99" s="33"/>
+      <c r="D99" s="49">
+        <v>65014</v>
+      </c>
+      <c r="E99" s="49">
+        <v>71834</v>
+      </c>
+      <c r="F99" s="49">
+        <v>62464</v>
+      </c>
       <c r="G99" s="30"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B100" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C100" s="49"/>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
-      <c r="F100" s="49"/>
+        <v>452</v>
+      </c>
+      <c r="B100" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C100" s="33"/>
+      <c r="D100" s="49">
+        <v>103774</v>
+      </c>
+      <c r="E100" s="49">
+        <v>102033</v>
+      </c>
+      <c r="F100" s="49">
+        <v>88724</v>
+      </c>
       <c r="G100" s="30"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="B101" s="49" t="s">
-        <v>489</v>
+        <v>452</v>
+      </c>
+      <c r="B101" s="50" t="s">
+        <v>77</v>
       </c>
       <c r="C101" s="49"/>
-      <c r="D101" s="49"/>
-      <c r="E101" s="49"/>
-      <c r="F101" s="49"/>
+      <c r="D101" s="49">
+        <v>211580</v>
+      </c>
+      <c r="E101" s="49">
+        <v>150513</v>
+      </c>
+      <c r="F101" s="49">
+        <v>130881</v>
+      </c>
       <c r="G101" s="30"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="28" t="s">
-        <v>457</v>
-      </c>
-      <c r="B102" s="49" t="s">
-        <v>489</v>
+        <v>452</v>
+      </c>
+      <c r="B102" s="50" t="s">
+        <v>85</v>
       </c>
       <c r="C102" s="49"/>
-      <c r="D102" s="49"/>
-      <c r="E102" s="49"/>
-      <c r="F102" s="49"/>
+      <c r="D102" s="49">
+        <v>280116</v>
+      </c>
+      <c r="E102" s="49">
+        <v>173234</v>
+      </c>
+      <c r="F102" s="49">
+        <v>150638</v>
+      </c>
       <c r="G102" s="30"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="B103" s="49" t="s">
-        <v>489</v>
+        <v>452</v>
+      </c>
+      <c r="B103" s="50" t="s">
+        <v>79</v>
       </c>
       <c r="C103" s="49"/>
-      <c r="D103" s="49"/>
-      <c r="E103" s="49"/>
-      <c r="F103" s="49"/>
+      <c r="D103" s="49">
+        <v>287958</v>
+      </c>
+      <c r="E103" s="49">
+        <v>197111</v>
+      </c>
+      <c r="F103" s="33">
+        <v>171401</v>
+      </c>
       <c r="G103" s="30"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="28" t="s">
         <v>452</v>
       </c>
-      <c r="B104" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C104" s="33"/>
+      <c r="B104" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C104" s="49"/>
       <c r="D104" s="49">
-        <v>65014</v>
+        <v>293189</v>
       </c>
       <c r="E104" s="49">
-        <v>71834</v>
+        <v>201250</v>
       </c>
       <c r="F104" s="49">
-        <v>62464</v>
+        <v>175000</v>
       </c>
       <c r="G104" s="30"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B105" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C105" s="33"/>
-      <c r="D105" s="49">
-        <v>103774</v>
-      </c>
-      <c r="E105" s="49">
-        <v>102033</v>
-      </c>
-      <c r="F105" s="49">
-        <v>88724</v>
-      </c>
-      <c r="G105" s="30"/>
+      <c r="A105" s="8"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="2"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B106" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C106" s="49"/>
-      <c r="D106" s="49">
-        <v>211580</v>
-      </c>
-      <c r="E106" s="49">
-        <v>150513</v>
-      </c>
-      <c r="F106" s="49">
-        <v>130881</v>
-      </c>
-      <c r="G106" s="30"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="2"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B107" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C107" s="49"/>
-      <c r="D107" s="49">
-        <v>280116</v>
-      </c>
-      <c r="E107" s="49">
-        <v>173234</v>
-      </c>
-      <c r="F107" s="49">
-        <v>150638</v>
-      </c>
-      <c r="G107" s="30"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="2"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B108" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C108" s="49"/>
-      <c r="D108" s="49">
-        <v>287958</v>
-      </c>
-      <c r="E108" s="49">
-        <v>197111</v>
-      </c>
-      <c r="F108" s="33">
-        <v>171401</v>
-      </c>
-      <c r="G108" s="30"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="2"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B109" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C109" s="49"/>
-      <c r="D109" s="49">
-        <v>293189</v>
-      </c>
-      <c r="E109" s="49">
-        <v>201250</v>
-      </c>
-      <c r="F109" s="49">
-        <v>175000</v>
-      </c>
-      <c r="G109" s="30"/>
+      <c r="A109" s="8"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="2"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="8"/>
@@ -21358,51 +21308,6 @@
       <c r="E997" s="8"/>
       <c r="F997" s="8"/>
       <c r="G997" s="2"/>
-    </row>
-    <row r="998" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A998" s="8"/>
-      <c r="B998" s="9"/>
-      <c r="C998" s="8"/>
-      <c r="D998" s="8"/>
-      <c r="E998" s="8"/>
-      <c r="F998" s="8"/>
-      <c r="G998" s="2"/>
-    </row>
-    <row r="999" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A999" s="8"/>
-      <c r="B999" s="9"/>
-      <c r="C999" s="8"/>
-      <c r="D999" s="8"/>
-      <c r="E999" s="8"/>
-      <c r="F999" s="8"/>
-      <c r="G999" s="2"/>
-    </row>
-    <row r="1000" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1000" s="8"/>
-      <c r="B1000" s="9"/>
-      <c r="C1000" s="8"/>
-      <c r="D1000" s="8"/>
-      <c r="E1000" s="8"/>
-      <c r="F1000" s="8"/>
-      <c r="G1000" s="2"/>
-    </row>
-    <row r="1001" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1001" s="8"/>
-      <c r="B1001" s="9"/>
-      <c r="C1001" s="8"/>
-      <c r="D1001" s="8"/>
-      <c r="E1001" s="8"/>
-      <c r="F1001" s="8"/>
-      <c r="G1001" s="2"/>
-    </row>
-    <row r="1002" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1002" s="8"/>
-      <c r="B1002" s="9"/>
-      <c r="C1002" s="8"/>
-      <c r="D1002" s="8"/>
-      <c r="E1002" s="8"/>
-      <c r="F1002" s="8"/>
-      <c r="G1002" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC532635-3796-C94F-BAEF-8580074E06FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAF88F9-1BBE-B44B-A068-D2652178AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71100" yWindow="-7380" windowWidth="30240" windowHeight="19000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="511">
   <si>
     <t>KPI tracking workbook</t>
   </si>
@@ -1572,6 +1572,9 @@
   </si>
   <si>
     <t>LIB-CIRCULATION</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -11369,7 +11372,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G997"/>
+  <dimension ref="A1:G1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -12865,16 +12868,16 @@
         <v>84</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D82" s="49">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="E82" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F82" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G82" s="30"/>
     </row>
@@ -12886,16 +12889,16 @@
         <v>77</v>
       </c>
       <c r="C83" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D83" s="49">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="E83" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F83" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G83" s="30"/>
     </row>
@@ -12907,16 +12910,16 @@
         <v>85</v>
       </c>
       <c r="C84" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D84" s="49">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E84" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F84" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G84" s="30"/>
     </row>
@@ -12928,16 +12931,16 @@
         <v>79</v>
       </c>
       <c r="C85" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D85" s="49">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E85" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F85" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G85" s="30"/>
     </row>
@@ -12949,16 +12952,16 @@
         <v>86</v>
       </c>
       <c r="C86" s="51" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D86" s="49">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="E86" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F86" s="49">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G86" s="30"/>
     </row>
@@ -12970,10 +12973,10 @@
         <v>84</v>
       </c>
       <c r="C87" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D87" s="49">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="E87" s="49">
         <v>50</v>
@@ -12991,10 +12994,10 @@
         <v>77</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D88" s="49">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="E88" s="49">
         <v>50</v>
@@ -13012,10 +13015,10 @@
         <v>85</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D89" s="49">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E89" s="49">
         <v>50</v>
@@ -13033,10 +13036,10 @@
         <v>79</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D90" s="49">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E90" s="49">
         <v>50</v>
@@ -13054,10 +13057,10 @@
         <v>86</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D91" s="49">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E91" s="49">
         <v>50</v>
@@ -13069,72 +13072,112 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="28" t="s">
-        <v>453</v>
-      </c>
-      <c r="B92" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C92" s="49"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="49"/>
-      <c r="F92" s="49"/>
+        <v>509</v>
+      </c>
+      <c r="B92" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D92" s="49">
+        <v>88</v>
+      </c>
+      <c r="E92" s="49">
+        <v>50</v>
+      </c>
+      <c r="F92" s="49">
+        <v>50</v>
+      </c>
       <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="B93" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C93" s="49"/>
-      <c r="D93" s="49"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="49"/>
+        <v>509</v>
+      </c>
+      <c r="B93" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D93" s="49">
+        <v>98</v>
+      </c>
+      <c r="E93" s="49">
+        <v>50</v>
+      </c>
+      <c r="F93" s="49">
+        <v>50</v>
+      </c>
       <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="B94" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C94" s="49"/>
-      <c r="D94" s="49"/>
-      <c r="E94" s="49"/>
-      <c r="F94" s="49"/>
+        <v>509</v>
+      </c>
+      <c r="B94" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C94" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D94" s="49">
+        <v>22</v>
+      </c>
+      <c r="E94" s="49">
+        <v>50</v>
+      </c>
+      <c r="F94" s="49">
+        <v>50</v>
+      </c>
       <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="B95" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C95" s="49"/>
-      <c r="D95" s="49"/>
-      <c r="E95" s="49"/>
-      <c r="F95" s="49"/>
+        <v>509</v>
+      </c>
+      <c r="B95" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D95" s="49">
+        <v>54</v>
+      </c>
+      <c r="E95" s="49">
+        <v>50</v>
+      </c>
+      <c r="F95" s="49">
+        <v>50</v>
+      </c>
       <c r="G95" s="30"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="B96" s="49" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" s="49"/>
-      <c r="D96" s="49"/>
-      <c r="E96" s="49"/>
-      <c r="F96" s="49"/>
+        <v>509</v>
+      </c>
+      <c r="B96" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="D96" s="49">
+        <v>58</v>
+      </c>
+      <c r="E96" s="49">
+        <v>50</v>
+      </c>
+      <c r="F96" s="49">
+        <v>50</v>
+      </c>
       <c r="G96" s="30"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="28" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B97" s="49" t="s">
         <v>489</v>
@@ -13147,7 +13190,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="28" t="s">
-        <v>458</v>
+        <v>506</v>
       </c>
       <c r="B98" s="49" t="s">
         <v>489</v>
@@ -13160,162 +13203,182 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="28" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B99" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" s="33"/>
-      <c r="D99" s="49">
-        <v>65014</v>
-      </c>
-      <c r="E99" s="49">
-        <v>71834</v>
-      </c>
-      <c r="F99" s="49">
-        <v>62464</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C99" s="49"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
       <c r="G99" s="30"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B100" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C100" s="33"/>
-      <c r="D100" s="49">
-        <v>103774</v>
-      </c>
-      <c r="E100" s="49">
-        <v>102033</v>
-      </c>
-      <c r="F100" s="49">
-        <v>88724</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="B100" s="49" t="s">
+        <v>489</v>
+      </c>
+      <c r="C100" s="49"/>
+      <c r="D100" s="49"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="49"/>
       <c r="G100" s="30"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B101" s="50" t="s">
-        <v>77</v>
+        <v>456</v>
+      </c>
+      <c r="B101" s="49" t="s">
+        <v>489</v>
       </c>
       <c r="C101" s="49"/>
-      <c r="D101" s="49">
-        <v>211580</v>
-      </c>
-      <c r="E101" s="49">
-        <v>150513</v>
-      </c>
-      <c r="F101" s="49">
-        <v>130881</v>
-      </c>
+      <c r="D101" s="49"/>
+      <c r="E101" s="49"/>
+      <c r="F101" s="49"/>
       <c r="G101" s="30"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B102" s="50" t="s">
-        <v>85</v>
+        <v>457</v>
+      </c>
+      <c r="B102" s="49" t="s">
+        <v>489</v>
       </c>
       <c r="C102" s="49"/>
-      <c r="D102" s="49">
-        <v>280116</v>
-      </c>
-      <c r="E102" s="49">
-        <v>173234</v>
-      </c>
-      <c r="F102" s="49">
-        <v>150638</v>
-      </c>
+      <c r="D102" s="49"/>
+      <c r="E102" s="49"/>
+      <c r="F102" s="49"/>
       <c r="G102" s="30"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="B103" s="50" t="s">
-        <v>79</v>
+        <v>458</v>
+      </c>
+      <c r="B103" s="49" t="s">
+        <v>489</v>
       </c>
       <c r="C103" s="49"/>
-      <c r="D103" s="49">
-        <v>287958</v>
-      </c>
-      <c r="E103" s="49">
-        <v>197111</v>
-      </c>
-      <c r="F103" s="33">
-        <v>171401</v>
-      </c>
+      <c r="D103" s="49"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
       <c r="G103" s="30"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="28" t="s">
         <v>452</v>
       </c>
-      <c r="B104" s="50" t="s">
+      <c r="B104" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C104" s="33"/>
+      <c r="D104" s="49">
+        <v>65014</v>
+      </c>
+      <c r="E104" s="49">
+        <v>71834</v>
+      </c>
+      <c r="F104" s="49">
+        <v>62464</v>
+      </c>
+      <c r="G104" s="30"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B105" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C105" s="33"/>
+      <c r="D105" s="49">
+        <v>103774</v>
+      </c>
+      <c r="E105" s="49">
+        <v>102033</v>
+      </c>
+      <c r="F105" s="49">
+        <v>88724</v>
+      </c>
+      <c r="G105" s="30"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A106" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C106" s="49"/>
+      <c r="D106" s="49">
+        <v>211580</v>
+      </c>
+      <c r="E106" s="49">
+        <v>150513</v>
+      </c>
+      <c r="F106" s="49">
+        <v>130881</v>
+      </c>
+      <c r="G106" s="30"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A107" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B107" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49">
+        <v>280116</v>
+      </c>
+      <c r="E107" s="49">
+        <v>173234</v>
+      </c>
+      <c r="F107" s="49">
+        <v>150638</v>
+      </c>
+      <c r="G107" s="30"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A108" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B108" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49">
+        <v>287958</v>
+      </c>
+      <c r="E108" s="49">
+        <v>197111</v>
+      </c>
+      <c r="F108" s="33">
+        <v>171401</v>
+      </c>
+      <c r="G108" s="30"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A109" s="28" t="s">
+        <v>452</v>
+      </c>
+      <c r="B109" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="C104" s="49"/>
-      <c r="D104" s="49">
+      <c r="C109" s="49"/>
+      <c r="D109" s="49">
         <v>293189</v>
       </c>
-      <c r="E104" s="49">
+      <c r="E109" s="49">
         <v>201250</v>
       </c>
-      <c r="F104" s="49">
+      <c r="F109" s="49">
         <v>175000</v>
       </c>
-      <c r="G104" s="30"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="8"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="8"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="8"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="8"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="8"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="2"/>
+      <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="8"/>
@@ -21308,6 +21371,51 @@
       <c r="E997" s="8"/>
       <c r="F997" s="8"/>
       <c r="G997" s="2"/>
+    </row>
+    <row r="998" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A998" s="8"/>
+      <c r="B998" s="9"/>
+      <c r="C998" s="8"/>
+      <c r="D998" s="8"/>
+      <c r="E998" s="8"/>
+      <c r="F998" s="8"/>
+      <c r="G998" s="2"/>
+    </row>
+    <row r="999" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A999" s="8"/>
+      <c r="B999" s="9"/>
+      <c r="C999" s="8"/>
+      <c r="D999" s="8"/>
+      <c r="E999" s="8"/>
+      <c r="F999" s="8"/>
+      <c r="G999" s="2"/>
+    </row>
+    <row r="1000" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1000" s="8"/>
+      <c r="B1000" s="9"/>
+      <c r="C1000" s="8"/>
+      <c r="D1000" s="8"/>
+      <c r="E1000" s="8"/>
+      <c r="F1000" s="8"/>
+      <c r="G1000" s="2"/>
+    </row>
+    <row r="1001" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1001" s="8"/>
+      <c r="B1001" s="9"/>
+      <c r="C1001" s="8"/>
+      <c r="D1001" s="8"/>
+      <c r="E1001" s="8"/>
+      <c r="F1001" s="8"/>
+      <c r="G1001" s="2"/>
+    </row>
+    <row r="1002" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1002" s="8"/>
+      <c r="B1002" s="9"/>
+      <c r="C1002" s="8"/>
+      <c r="D1002" s="8"/>
+      <c r="E1002" s="8"/>
+      <c r="F1002" s="8"/>
+      <c r="G1002" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAF88F9-1BBE-B44B-A068-D2652178AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71100" yWindow="-7380" windowWidth="30240" windowHeight="19000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71100" yWindow="-7380" windowWidth="30240" windowHeight="19000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to use" sheetId="1" r:id="rId1"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47EA541-579D-0E4F-9D14-02DC71898CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9195E5CB-8A3B-7B4B-9F73-20D74FC561B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71100" yWindow="-7380" windowWidth="30240" windowHeight="19000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dashboard Items'!$A$1:$F$154</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KPI Data'!$A$1:$H$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KPI Data'!$A$1:$H$128</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -48,7 +48,7 @@
     <author>Lord, Mary Cathryn</author>
   </authors>
   <commentList>
-    <comment ref="F137" authorId="0" shapeId="0" xr:uid="{2372AC8A-A149-E648-AB2F-3DB88113104E}">
+    <comment ref="F133" authorId="0" shapeId="0" xr:uid="{2372AC8A-A149-E648-AB2F-3DB88113104E}">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F138" authorId="0" shapeId="0" xr:uid="{6B7F036F-8F03-5148-BCE6-FD6FA0D833A8}">
+    <comment ref="F134" authorId="0" shapeId="0" xr:uid="{6B7F036F-8F03-5148-BCE6-FD6FA0D833A8}">
       <text>
         <r>
           <rPr>
@@ -114,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F139" authorId="0" shapeId="0" xr:uid="{11BC8C69-E118-F448-8EF0-52C3DFEE3D09}">
+    <comment ref="F135" authorId="0" shapeId="0" xr:uid="{11BC8C69-E118-F448-8EF0-52C3DFEE3D09}">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="0" shapeId="0" xr:uid="{901BC63C-8AEB-2D47-A6B4-1DB3B0A2A21E}">
+    <comment ref="F140" authorId="0" shapeId="0" xr:uid="{901BC63C-8AEB-2D47-A6B4-1DB3B0A2A21E}">
       <text>
         <r>
           <rPr>
@@ -180,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F146" authorId="0" shapeId="0" xr:uid="{723B65F1-1A4C-8A45-99E1-F641626DE184}">
+    <comment ref="F142" authorId="0" shapeId="0" xr:uid="{723B65F1-1A4C-8A45-99E1-F641626DE184}">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="630">
   <si>
     <t>Level</t>
   </si>
@@ -1646,16 +1646,7 @@
     <t>Dept</t>
   </si>
   <si>
-    <t>HR-DOTCOMP</t>
-  </si>
-  <si>
     <t>HR-EMOD</t>
-  </si>
-  <si>
-    <t>HR-ACCIDENTREV</t>
-  </si>
-  <si>
-    <t>HR-TRAININGS</t>
   </si>
   <si>
     <t>CLERK-SPECCOURT</t>
@@ -2391,7 +2382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2659,6 +2650,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3032,27 +3026,27 @@
         <v>467</v>
       </c>
       <c r="B1" s="89" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C1" s="88" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D1" s="88" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E1" s="88" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F1" s="88" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G1" s="88" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="90" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B2" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A2)</f>
@@ -3062,7 +3056,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="90" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B3" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A3)</f>
@@ -3072,7 +3066,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="90" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B4" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A4)</f>
@@ -3081,7 +3075,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="90" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B5" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A5)</f>
@@ -3100,7 +3094,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="90" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B7" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A7)</f>
@@ -3109,7 +3103,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="90" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B8" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A8)</f>
@@ -3118,7 +3112,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="90" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B9" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A9)</f>
@@ -3127,7 +3121,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="90" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B10" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A10)</f>
@@ -3136,7 +3130,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="90" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B11" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A11)</f>
@@ -3145,7 +3139,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="90" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B12" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A12)</f>
@@ -3154,7 +3148,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="90" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B13" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A13)</f>
@@ -3163,7 +3157,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="90" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B14" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A14)</f>
@@ -3172,7 +3166,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="90" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B15" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A15)</f>
@@ -3181,7 +3175,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="90" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B16" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A16)</f>
@@ -3190,7 +3184,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="90" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B17" s="94">
         <f>COUNTIF('KPI Catalog'!A:A, A17)</f>
@@ -3368,7 +3362,7 @@
         <v>391</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>26</v>
@@ -3408,10 +3402,10 @@
         <v>HR</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D4" s="34" t="s">
         <v>26</v>
@@ -3449,10 +3443,10 @@
         <v>HR</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D5" s="34" t="s">
         <v>36</v>
@@ -3488,10 +3482,10 @@
         <v>HR</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D6" s="34" t="s">
         <v>36</v>
@@ -3527,10 +3521,10 @@
         <v>HR</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>36</v>
@@ -3566,10 +3560,10 @@
         <v>HR</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>36</v>
@@ -3609,10 +3603,10 @@
         <v>HR</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>36</v>
@@ -3650,10 +3644,10 @@
         <v>HR</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D10" s="34" t="s">
         <v>36</v>
@@ -3691,10 +3685,10 @@
         <v>HR</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>36</v>
@@ -3734,10 +3728,10 @@
         <v>HR</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>36</v>
@@ -3777,10 +3771,10 @@
         <v>HR</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D13" s="34" t="s">
         <v>36</v>
@@ -3816,10 +3810,10 @@
         <v>HR</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D14" s="34" t="s">
         <v>36</v>
@@ -3855,10 +3849,10 @@
         <v>HR</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D15" s="34" t="s">
         <v>36</v>
@@ -3893,11 +3887,11 @@
         <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>503</v>
+      <c r="B16" s="95" t="s">
+        <v>500</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>36</v>
@@ -3932,11 +3926,11 @@
         <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B17" s="32" t="s">
-        <v>469</v>
+      <c r="B17" s="5" t="s">
+        <v>468</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>36</v>
@@ -3971,11 +3965,11 @@
         <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B18" s="32" t="s">
-        <v>504</v>
+      <c r="B18" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>36</v>
@@ -4010,11 +4004,11 @@
         <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>505</v>
+      <c r="B19" s="5" t="s">
+        <v>502</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D19" s="34" t="s">
         <v>36</v>
@@ -4050,10 +4044,10 @@
         <v>HR</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D20" s="34" t="s">
         <v>36</v>
@@ -4089,10 +4083,10 @@
         <v>HR</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D21" s="34" t="s">
         <v>36</v>
@@ -5211,7 +5205,7 @@
         <v>CLERK</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C43" s="54" t="s">
         <v>416</v>
@@ -5311,10 +5305,10 @@
         <v>PIO</v>
       </c>
       <c r="B45" s="60" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C45" s="60" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D45" s="61" t="s">
         <v>36</v>
@@ -5356,10 +5350,10 @@
         <v>PIO</v>
       </c>
       <c r="B46" s="60" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D46" s="61" t="s">
         <v>36</v>
@@ -5401,10 +5395,10 @@
         <v>PIO</v>
       </c>
       <c r="B47" s="60" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C47" s="60" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D47" s="61" t="s">
         <v>36</v>
@@ -5446,10 +5440,10 @@
         <v>PIO</v>
       </c>
       <c r="B48" s="60" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D48" s="61" t="s">
         <v>36</v>
@@ -5486,10 +5480,10 @@
         <v>PIO</v>
       </c>
       <c r="B49" s="60" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C49" s="60" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D49" s="61" t="s">
         <v>36</v>
@@ -5913,10 +5907,10 @@
         <v>PROS</v>
       </c>
       <c r="B57" s="72" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C57" s="73" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D57" s="74" t="s">
         <v>36</v>
@@ -5958,12 +5952,12 @@
         <v>39</v>
       </c>
       <c r="Q57" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R57" s="74"/>
       <c r="S57" s="74"/>
       <c r="T57" s="72" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:20" s="71" customFormat="1" ht="16" x14ac:dyDescent="0.2">
@@ -5972,10 +5966,10 @@
         <v>PROS</v>
       </c>
       <c r="B58" s="72" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C58" s="73" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D58" s="74" t="s">
         <v>36</v>
@@ -6017,7 +6011,7 @@
         <v>39</v>
       </c>
       <c r="Q58" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R58" s="74"/>
       <c r="S58" s="74"/>
@@ -6029,10 +6023,10 @@
         <v>PROS</v>
       </c>
       <c r="B59" s="72" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C59" s="73" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D59" s="74" t="s">
         <v>26</v>
@@ -6076,7 +6070,7 @@
         <v>39</v>
       </c>
       <c r="Q59" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R59" s="74"/>
       <c r="S59" s="74"/>
@@ -6088,10 +6082,10 @@
         <v>PROS</v>
       </c>
       <c r="B60" s="72" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C60" s="73" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D60" s="74" t="s">
         <v>36</v>
@@ -6133,7 +6127,7 @@
         <v>39</v>
       </c>
       <c r="Q60" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R60" s="74"/>
       <c r="S60" s="74"/>
@@ -6145,10 +6139,10 @@
         <v>PROS</v>
       </c>
       <c r="B61" s="72" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C61" s="73" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D61" s="74" t="s">
         <v>36</v>
@@ -6190,7 +6184,7 @@
         <v>39</v>
       </c>
       <c r="Q61" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R61" s="74"/>
       <c r="S61" s="74"/>
@@ -6202,10 +6196,10 @@
         <v>PROS</v>
       </c>
       <c r="B62" s="72" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C62" s="73" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D62" s="74" t="s">
         <v>26</v>
@@ -6249,7 +6243,7 @@
         <v>39</v>
       </c>
       <c r="Q62" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R62" s="74"/>
       <c r="S62" s="74"/>
@@ -6261,10 +6255,10 @@
         <v>PROS</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C63" s="73" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D63" s="74" t="s">
         <v>26</v>
@@ -6308,7 +6302,7 @@
         <v>39</v>
       </c>
       <c r="Q63" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R63" s="74"/>
       <c r="S63" s="74"/>
@@ -6320,10 +6314,10 @@
         <v>PROS</v>
       </c>
       <c r="B64" s="72" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C64" s="73" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D64" s="74" t="s">
         <v>36</v>
@@ -6365,7 +6359,7 @@
         <v>39</v>
       </c>
       <c r="Q64" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R64" s="74"/>
       <c r="S64" s="74"/>
@@ -6377,10 +6371,10 @@
         <v>PROS</v>
       </c>
       <c r="B65" s="72" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C65" s="73" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D65" s="74" t="s">
         <v>36</v>
@@ -6422,7 +6416,7 @@
         <v>39</v>
       </c>
       <c r="Q65" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R65" s="74"/>
       <c r="S65" s="74"/>
@@ -6434,10 +6428,10 @@
         <v>PROS</v>
       </c>
       <c r="B66" s="72" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C66" s="73" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D66" s="74" t="s">
         <v>36</v>
@@ -6479,7 +6473,7 @@
         <v>39</v>
       </c>
       <c r="Q66" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R66" s="74"/>
       <c r="S66" s="74"/>
@@ -6491,10 +6485,10 @@
         <v>PROS</v>
       </c>
       <c r="B67" s="72" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C67" s="73" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D67" s="74" t="s">
         <v>26</v>
@@ -6538,7 +6532,7 @@
         <v>39</v>
       </c>
       <c r="Q67" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R67" s="74"/>
       <c r="S67" s="74"/>
@@ -6550,10 +6544,10 @@
         <v>PROS</v>
       </c>
       <c r="B68" s="72" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C68" s="73" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D68" s="74" t="s">
         <v>36</v>
@@ -6595,7 +6589,7 @@
         <v>39</v>
       </c>
       <c r="Q68" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R68" s="74"/>
       <c r="S68" s="74"/>
@@ -6607,10 +6601,10 @@
         <v>PROS</v>
       </c>
       <c r="B69" s="72" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C69" s="73" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D69" s="74" t="s">
         <v>36</v>
@@ -6652,7 +6646,7 @@
         <v>39</v>
       </c>
       <c r="Q69" s="72" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R69" s="74"/>
       <c r="S69" s="74"/>
@@ -6664,10 +6658,10 @@
         <v>PD</v>
       </c>
       <c r="B70" s="82" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C70" s="83" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D70" s="84" t="s">
         <v>26</v>
@@ -6709,7 +6703,7 @@
         <v>39</v>
       </c>
       <c r="Q70" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R70" s="84"/>
       <c r="S70" s="84"/>
@@ -6721,10 +6715,10 @@
         <v>PD</v>
       </c>
       <c r="B71" s="82" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C71" s="83" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D71" s="84" t="s">
         <v>26</v>
@@ -6766,7 +6760,7 @@
         <v>39</v>
       </c>
       <c r="Q71" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R71" s="84"/>
       <c r="S71" s="84"/>
@@ -6778,10 +6772,10 @@
         <v>PD</v>
       </c>
       <c r="B72" s="82" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C72" s="83" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D72" s="84" t="s">
         <v>26</v>
@@ -6823,7 +6817,7 @@
         <v>39</v>
       </c>
       <c r="Q72" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R72" s="84"/>
       <c r="S72" s="84"/>
@@ -6835,10 +6829,10 @@
         <v>PD</v>
       </c>
       <c r="B73" s="82" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C73" s="83" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D73" s="84" t="s">
         <v>26</v>
@@ -6851,7 +6845,7 @@
         <v>Public Safety Services</v>
       </c>
       <c r="G73" s="87" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="H73" s="85" t="str">
         <f>IF(G73="","",IF(ISNUMBER(SEARCH(",",G73)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$497,MATCH(G73,'Dashboard Items'!$A$2:$A$497,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$497,MATCH(G73,'Dashboard Items'!$A$2:$A$497,0)),"ID not found")))</f>
@@ -6882,7 +6876,7 @@
         <v>39</v>
       </c>
       <c r="Q73" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R73" s="84"/>
       <c r="S73" s="84"/>
@@ -6894,10 +6888,10 @@
         <v>PD</v>
       </c>
       <c r="B74" s="82" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C74" s="83" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D74" s="84" t="s">
         <v>26</v>
@@ -6939,7 +6933,7 @@
         <v>39</v>
       </c>
       <c r="Q74" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R74" s="84"/>
       <c r="S74" s="84"/>
@@ -6951,10 +6945,10 @@
         <v>PD</v>
       </c>
       <c r="B75" s="82" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C75" s="83" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D75" s="84" t="s">
         <v>26</v>
@@ -6996,7 +6990,7 @@
         <v>39</v>
       </c>
       <c r="Q75" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R75" s="84"/>
       <c r="S75" s="84"/>
@@ -7008,10 +7002,10 @@
         <v>PD</v>
       </c>
       <c r="B76" s="82" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C76" s="83" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D76" s="84" t="s">
         <v>36</v>
@@ -7053,7 +7047,7 @@
         <v>39</v>
       </c>
       <c r="Q76" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R76" s="84"/>
       <c r="S76" s="84"/>
@@ -7065,10 +7059,10 @@
         <v>PD</v>
       </c>
       <c r="B77" s="82" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C77" s="83" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D77" s="84" t="s">
         <v>36</v>
@@ -7110,7 +7104,7 @@
         <v>39</v>
       </c>
       <c r="Q77" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R77" s="84"/>
       <c r="S77" s="84"/>
@@ -7122,10 +7116,10 @@
         <v>PD</v>
       </c>
       <c r="B78" s="82" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C78" s="83" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D78" s="84" t="s">
         <v>36</v>
@@ -7167,7 +7161,7 @@
         <v>39</v>
       </c>
       <c r="Q78" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R78" s="84"/>
       <c r="S78" s="84"/>
@@ -7179,10 +7173,10 @@
         <v>PD</v>
       </c>
       <c r="B79" s="82" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C79" s="83" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D79" s="84" t="s">
         <v>36</v>
@@ -7224,7 +7218,7 @@
         <v>39</v>
       </c>
       <c r="Q79" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R79" s="84"/>
       <c r="S79" s="84"/>
@@ -7236,10 +7230,10 @@
         <v>PD</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C80" s="83" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D80" s="84" t="s">
         <v>36</v>
@@ -7281,7 +7275,7 @@
         <v>39</v>
       </c>
       <c r="Q80" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R80" s="84"/>
       <c r="S80" s="84"/>
@@ -7293,10 +7287,10 @@
         <v>PD</v>
       </c>
       <c r="B81" s="82" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C81" s="83" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D81" s="84" t="s">
         <v>36</v>
@@ -7338,7 +7332,7 @@
         <v>39</v>
       </c>
       <c r="Q81" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R81" s="84"/>
       <c r="S81" s="84"/>
@@ -7350,10 +7344,10 @@
         <v>PD</v>
       </c>
       <c r="B82" s="82" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C82" s="83" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D82" s="84" t="s">
         <v>36</v>
@@ -7395,7 +7389,7 @@
         <v>39</v>
       </c>
       <c r="Q82" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R82" s="84"/>
       <c r="S82" s="84"/>
@@ -7407,10 +7401,10 @@
         <v>PD</v>
       </c>
       <c r="B83" s="82" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C83" s="83" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D83" s="84" t="s">
         <v>36</v>
@@ -7452,7 +7446,7 @@
         <v>39</v>
       </c>
       <c r="Q83" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R83" s="84"/>
       <c r="S83" s="84"/>
@@ -7464,10 +7458,10 @@
         <v>PD</v>
       </c>
       <c r="B84" s="82" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C84" s="83" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D84" s="84" t="s">
         <v>36</v>
@@ -7509,7 +7503,7 @@
         <v>39</v>
       </c>
       <c r="Q84" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R84" s="84"/>
       <c r="S84" s="84"/>
@@ -7521,10 +7515,10 @@
         <v>PD</v>
       </c>
       <c r="B85" s="82" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C85" s="83" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D85" s="84" t="s">
         <v>36</v>
@@ -7566,7 +7560,7 @@
         <v>39</v>
       </c>
       <c r="Q85" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R85" s="84"/>
       <c r="S85" s="84"/>
@@ -7578,10 +7572,10 @@
         <v>PD</v>
       </c>
       <c r="B86" s="82" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C86" s="83" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D86" s="84" t="s">
         <v>36</v>
@@ -7623,7 +7617,7 @@
         <v>39</v>
       </c>
       <c r="Q86" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R86" s="84"/>
       <c r="S86" s="84"/>
@@ -7635,10 +7629,10 @@
         <v>PD</v>
       </c>
       <c r="B87" s="82" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C87" s="83" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D87" s="84" t="s">
         <v>36</v>
@@ -7680,7 +7674,7 @@
         <v>39</v>
       </c>
       <c r="Q87" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R87" s="84"/>
       <c r="S87" s="84"/>
@@ -7692,10 +7686,10 @@
         <v>PD</v>
       </c>
       <c r="B88" s="82" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C88" s="83" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D88" s="84" t="s">
         <v>36</v>
@@ -7737,7 +7731,7 @@
         <v>39</v>
       </c>
       <c r="Q88" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R88" s="84"/>
       <c r="S88" s="84"/>
@@ -7749,10 +7743,10 @@
         <v>PD</v>
       </c>
       <c r="B89" s="82" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C89" s="83" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D89" s="84" t="s">
         <v>36</v>
@@ -7794,7 +7788,7 @@
         <v>39</v>
       </c>
       <c r="Q89" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R89" s="84"/>
       <c r="S89" s="84"/>
@@ -7806,10 +7800,10 @@
         <v>PD</v>
       </c>
       <c r="B90" s="82" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C90" s="83" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D90" s="84" t="s">
         <v>36</v>
@@ -7851,7 +7845,7 @@
         <v>39</v>
       </c>
       <c r="Q90" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R90" s="84"/>
       <c r="S90" s="84"/>
@@ -7863,10 +7857,10 @@
         <v>PD</v>
       </c>
       <c r="B91" s="82" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C91" s="83" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D91" s="84" t="s">
         <v>36</v>
@@ -7908,7 +7902,7 @@
         <v>39</v>
       </c>
       <c r="Q91" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R91" s="84"/>
       <c r="S91" s="84"/>
@@ -7920,10 +7914,10 @@
         <v>PD</v>
       </c>
       <c r="B92" s="82" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C92" s="83" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D92" s="84" t="s">
         <v>36</v>
@@ -7965,7 +7959,7 @@
         <v>39</v>
       </c>
       <c r="Q92" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R92" s="84"/>
       <c r="S92" s="84"/>
@@ -7977,10 +7971,10 @@
         <v>PD</v>
       </c>
       <c r="B93" s="82" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C93" s="83" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D93" s="84" t="s">
         <v>36</v>
@@ -8022,7 +8016,7 @@
         <v>39</v>
       </c>
       <c r="Q93" s="82" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R93" s="84"/>
       <c r="S93" s="84"/>
@@ -8034,10 +8028,10 @@
         <v>911</v>
       </c>
       <c r="B94" s="32" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C94" s="91" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D94" s="34" t="s">
         <v>26</v>
@@ -8081,7 +8075,7 @@
         <v>39</v>
       </c>
       <c r="Q94" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R94" s="34"/>
       <c r="S94" s="34"/>
@@ -8093,10 +8087,10 @@
         <v>911</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C95" s="91" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D95" s="34" t="s">
         <v>36</v>
@@ -8140,7 +8134,7 @@
         <v>39</v>
       </c>
       <c r="Q95" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R95" s="34"/>
       <c r="S95" s="34"/>
@@ -8152,10 +8146,10 @@
         <v>911</v>
       </c>
       <c r="B96" s="32" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C96" s="91" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D96" s="34" t="s">
         <v>36</v>
@@ -8197,7 +8191,7 @@
         <v>39</v>
       </c>
       <c r="Q96" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R96" s="34"/>
       <c r="S96" s="34"/>
@@ -8209,10 +8203,10 @@
         <v>911</v>
       </c>
       <c r="B97" s="32" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C97" s="91" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D97" s="34" t="s">
         <v>36</v>
@@ -8254,7 +8248,7 @@
         <v>39</v>
       </c>
       <c r="Q97" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R97" s="34"/>
       <c r="S97" s="34"/>
@@ -8266,10 +8260,10 @@
         <v>911</v>
       </c>
       <c r="B98" s="32" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C98" s="92" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D98" s="34" t="s">
         <v>36</v>
@@ -8313,7 +8307,7 @@
         <v>39</v>
       </c>
       <c r="Q98" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R98" s="34"/>
       <c r="S98" s="34"/>
@@ -8325,10 +8319,10 @@
         <v>911</v>
       </c>
       <c r="B99" s="32" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C99" s="92" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D99" s="34" t="s">
         <v>36</v>
@@ -8370,7 +8364,7 @@
         <v>39</v>
       </c>
       <c r="Q99" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R99" s="34"/>
       <c r="S99" s="34"/>
@@ -8382,10 +8376,10 @@
         <v>911</v>
       </c>
       <c r="B100" s="32" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C100" s="92" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D100" s="34" t="s">
         <v>26</v>
@@ -8427,7 +8421,7 @@
         <v>39</v>
       </c>
       <c r="Q100" s="34" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="R100" s="34"/>
       <c r="S100" s="34"/>
@@ -13801,7 +13795,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H1018"/>
+  <dimension ref="A1:H1014"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
@@ -13840,7 +13834,7 @@
     </row>
     <row r="2" spans="1:8" s="7" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="str">
-        <f t="shared" ref="A2:A33" si="0">LEFT(B2, FIND("-", B2) - 1)</f>
+        <f t="shared" ref="A2:A29" si="0">LEFT(B2, FIND("-", B2) - 1)</f>
         <v>CLERK</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -14078,11 +14072,9 @@
         <v>HR</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>430</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
@@ -14094,16 +14086,12 @@
         <v>HR</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>430</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C16" s="14"/>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
+      <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -14112,16 +14100,12 @@
         <v>HR</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>430</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="14">
-        <v>2</v>
-      </c>
+      <c r="F17" s="14"/>
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -14130,16 +14114,12 @@
         <v>HR</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>430</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
-      <c r="F18" s="14">
-        <v>90</v>
-      </c>
+      <c r="F18" s="14"/>
       <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -14148,7 +14128,7 @@
         <v>HR</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>392</v>
+        <v>483</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -14162,7 +14142,7 @@
         <v>HR</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>391</v>
+        <v>484</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -14176,7 +14156,7 @@
         <v>HR</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -14190,7 +14170,7 @@
         <v>HR</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -14204,7 +14184,7 @@
         <v>HR</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -14218,7 +14198,7 @@
         <v>HR</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -14232,7 +14212,7 @@
         <v>HR</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -14245,8 +14225,8 @@
         <f t="shared" si="0"/>
         <v>HR</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>489</v>
+      <c r="B26" s="96" t="s">
+        <v>490</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -14260,7 +14240,7 @@
         <v>HR</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -14274,7 +14254,7 @@
         <v>HR</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -14287,8 +14267,8 @@
         <f t="shared" si="0"/>
         <v>HR</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>492</v>
+      <c r="B29" s="95" t="s">
+        <v>500</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -14298,11 +14278,11 @@
     </row>
     <row r="30" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A30:A61" si="1">LEFT(B30, FIND("-", B30) - 1)</f>
         <v>HR</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -14312,11 +14292,11 @@
     </row>
     <row r="31" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>HR</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -14326,11 +14306,11 @@
     </row>
     <row r="32" spans="1:7" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>HR</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -14340,10 +14320,10 @@
     </row>
     <row r="33" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="32" t="s">
         <v>503</v>
       </c>
       <c r="C33" s="14"/>
@@ -14354,11 +14334,11 @@
     </row>
     <row r="34" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="str">
-        <f t="shared" ref="A34:A65" si="1">LEFT(B34, FIND("-", B34) - 1)</f>
+        <f t="shared" si="1"/>
         <v>HR</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>469</v>
+      <c r="B34" s="32" t="s">
+        <v>504</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -14366,61 +14346,97 @@
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="str">
+    <row r="35" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>HR</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="str">
+        <v>IT</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16">
+        <v>99.89</v>
+      </c>
+      <c r="F35" s="16">
+        <v>99.99</v>
+      </c>
+      <c r="G35" s="16">
+        <v>99.998999999999995</v>
+      </c>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>HR</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="str">
+        <v>IT</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16">
+        <v>99.98</v>
+      </c>
+      <c r="F36" s="16">
+        <v>99.99</v>
+      </c>
+      <c r="G36" s="16">
+        <v>99.998999999999995</v>
+      </c>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>HR</v>
-      </c>
-      <c r="B37" s="32" t="s">
-        <v>506</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-    </row>
-    <row r="38" spans="1:8" s="5" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="str">
+        <v>IT</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16">
+        <v>99.92</v>
+      </c>
+      <c r="F37" s="16">
+        <v>99.99</v>
+      </c>
+      <c r="G37" s="16">
+        <v>99.998999999999995</v>
+      </c>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>HR</v>
-      </c>
-      <c r="B38" s="32" t="s">
-        <v>507</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+        <v>IT</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16">
+        <v>99.91</v>
+      </c>
+      <c r="F38" s="16">
+        <v>99.99</v>
+      </c>
+      <c r="G38" s="16">
+        <v>99.998999999999995</v>
+      </c>
+      <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="str">
@@ -14431,11 +14447,11 @@
         <v>34</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D39" s="16"/>
       <c r="E39" s="16">
-        <v>99.89</v>
+        <v>99.79</v>
       </c>
       <c r="F39" s="16">
         <v>99.99</v>
@@ -14454,11 +14470,11 @@
         <v>34</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16">
-        <v>99.98</v>
+        <v>99.85</v>
       </c>
       <c r="F40" s="16">
         <v>99.99</v>
@@ -14474,21 +14490,19 @@
         <v>IT</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>40</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16">
-        <v>99.92</v>
+        <v>80</v>
       </c>
       <c r="F41" s="16">
-        <v>99.99</v>
-      </c>
-      <c r="G41" s="16">
-        <v>99.998999999999995</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G41" s="16"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14497,21 +14511,19 @@
         <v>IT</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>48</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16">
-        <v>99.91</v>
+        <v>89.86</v>
       </c>
       <c r="F42" s="16">
-        <v>99.99</v>
-      </c>
-      <c r="G42" s="16">
-        <v>99.998999999999995</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G42" s="16"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14520,21 +14532,19 @@
         <v>IT</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>42</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16">
-        <v>99.79</v>
+        <v>85.71</v>
       </c>
       <c r="F43" s="16">
-        <v>99.99</v>
-      </c>
-      <c r="G43" s="16">
-        <v>99.998999999999995</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G43" s="16"/>
       <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14543,21 +14553,19 @@
         <v>IT</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C44" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>49</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16">
-        <v>99.85</v>
+        <v>89.97</v>
       </c>
       <c r="F44" s="16">
-        <v>99.99</v>
-      </c>
-      <c r="G44" s="16">
-        <v>99.998999999999995</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="G44" s="16"/>
       <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14566,19 +14574,21 @@
         <v>IT</v>
       </c>
       <c r="B45" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16">
-        <v>80</v>
-      </c>
+      <c r="D45" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="E45" s="16"/>
       <c r="F45" s="16">
-        <v>85</v>
-      </c>
-      <c r="G45" s="16"/>
+        <v>95</v>
+      </c>
+      <c r="G45" s="16">
+        <v>100</v>
+      </c>
       <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14587,19 +14597,21 @@
         <v>IT</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16">
-        <v>89.86</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="E46" s="16"/>
       <c r="F46" s="16">
-        <v>85</v>
-      </c>
-      <c r="G46" s="16"/>
+        <v>95</v>
+      </c>
+      <c r="G46" s="16">
+        <v>100</v>
+      </c>
       <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14608,19 +14620,21 @@
         <v>IT</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16">
-        <v>85.71</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="E47" s="16"/>
       <c r="F47" s="16">
-        <v>85</v>
-      </c>
-      <c r="G47" s="16"/>
+        <v>95</v>
+      </c>
+      <c r="G47" s="16">
+        <v>100</v>
+      </c>
       <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14629,19 +14643,21 @@
         <v>IT</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16">
-        <v>89.97</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="E48" s="16"/>
       <c r="F48" s="16">
-        <v>85</v>
-      </c>
-      <c r="G48" s="16"/>
+        <v>95</v>
+      </c>
+      <c r="G48" s="16">
+        <v>100</v>
+      </c>
       <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14653,7 +14669,7 @@
         <v>395</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>358</v>
@@ -14676,7 +14692,7 @@
         <v>395</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>361</v>
@@ -14699,7 +14715,7 @@
         <v>395</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>359</v>
@@ -14722,7 +14738,7 @@
         <v>395</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>360</v>
@@ -14745,7 +14761,7 @@
         <v>395</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>358</v>
@@ -14768,7 +14784,7 @@
         <v>395</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>361</v>
@@ -14791,7 +14807,7 @@
         <v>395</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>359</v>
@@ -14814,7 +14830,7 @@
         <v>395</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>360</v>
@@ -14837,7 +14853,7 @@
         <v>395</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>358</v>
@@ -14860,7 +14876,7 @@
         <v>395</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>361</v>
@@ -14883,7 +14899,7 @@
         <v>395</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>359</v>
@@ -14906,7 +14922,7 @@
         <v>395</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D60" s="20" t="s">
         <v>360</v>
@@ -14926,139 +14942,135 @@
         <v>IT</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="E61" s="16"/>
+        <v>365</v>
+      </c>
+      <c r="D61" s="15"/>
+      <c r="E61" s="16">
+        <v>8.9</v>
+      </c>
       <c r="F61" s="16">
-        <v>95</v>
+        <v>3.9</v>
       </c>
       <c r="G61" s="16">
-        <v>100</v>
+        <v>3.9</v>
       </c>
       <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A62:A93" si="2">LEFT(B62, FIND("-", B62) - 1)</f>
         <v>IT</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="E62" s="16"/>
+        <v>366</v>
+      </c>
+      <c r="D62" s="15"/>
+      <c r="E62" s="16">
+        <v>2.4</v>
+      </c>
       <c r="F62" s="16">
-        <v>95</v>
+        <v>3.9</v>
       </c>
       <c r="G62" s="16">
-        <v>100</v>
+        <v>3.9</v>
       </c>
       <c r="H62" s="6"/>
     </row>
-    <row r="63" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="str">
-        <f t="shared" si="1"/>
+    <row r="63" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A63" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>IT</v>
       </c>
-      <c r="B63" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16">
-        <v>95</v>
-      </c>
-      <c r="G63" s="16">
-        <v>100</v>
-      </c>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="10" t="str">
-        <f t="shared" si="1"/>
+      <c r="B63" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18">
+        <v>1.05</v>
+      </c>
+      <c r="F63" s="18">
+        <v>3.9</v>
+      </c>
+      <c r="G63" s="18">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A64" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>IT</v>
       </c>
-      <c r="B64" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16">
-        <v>95</v>
-      </c>
-      <c r="G64" s="16">
-        <v>100</v>
-      </c>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="str">
-        <f t="shared" si="1"/>
+      <c r="B64" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18">
+        <v>0.9</v>
+      </c>
+      <c r="F64" s="18">
+        <v>3.9</v>
+      </c>
+      <c r="G64" s="18">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A65" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>IT</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="C65" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="D65" s="15"/>
-      <c r="E65" s="16">
-        <v>8.9</v>
-      </c>
-      <c r="F65" s="16">
+      <c r="C65" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18">
+        <v>0.63333333333333297</v>
+      </c>
+      <c r="F65" s="18">
         <v>3.9</v>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="18">
         <v>3.9</v>
       </c>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="10" t="str">
-        <f t="shared" ref="A66:A97" si="2">LEFT(B66, FIND("-", B66) - 1)</f>
+    </row>
+    <row r="66" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A66" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>IT</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B66" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="C66" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="D66" s="15"/>
-      <c r="E66" s="16">
-        <v>2.4</v>
-      </c>
-      <c r="F66" s="16">
+      <c r="C66" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18">
+        <v>0.7</v>
+      </c>
+      <c r="F66" s="18">
         <v>3.9</v>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="18">
         <v>3.9</v>
       </c>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15067,11 +15079,11 @@
         <v>396</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18">
-        <v>1.05</v>
+        <v>1.13333333333333</v>
       </c>
       <c r="F67" s="18">
         <v>3.9</v>
@@ -15080,7 +15092,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15089,11 +15101,11 @@
         <v>396</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D68" s="18"/>
       <c r="E68" s="18">
-        <v>0.9</v>
+        <v>0.56666666666666698</v>
       </c>
       <c r="F68" s="18">
         <v>3.9</v>
@@ -15102,7 +15114,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15111,11 +15123,11 @@
         <v>396</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="18">
-        <v>0.63333333333333297</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F69" s="18">
         <v>3.9</v>
@@ -15124,7 +15136,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="70" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15133,11 +15145,11 @@
         <v>396</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D70" s="18"/>
       <c r="E70" s="18">
-        <v>0.7</v>
+        <v>1.5333333333333301</v>
       </c>
       <c r="F70" s="18">
         <v>3.9</v>
@@ -15146,7 +15158,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15155,11 +15167,11 @@
         <v>396</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18">
-        <v>1.13333333333333</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F71" s="18">
         <v>3.9</v>
@@ -15168,7 +15180,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15177,11 +15189,11 @@
         <v>396</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="18">
-        <v>0.56666666666666698</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="F72" s="18">
         <v>3.9</v>
@@ -15190,7 +15202,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15199,11 +15211,11 @@
         <v>396</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18">
-        <v>0.83333333333333304</v>
+        <v>0.73333333333333295</v>
       </c>
       <c r="F73" s="18">
         <v>3.9</v>
@@ -15212,7 +15224,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15221,11 +15233,11 @@
         <v>396</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="18">
-        <v>1.5333333333333301</v>
+        <v>0.75</v>
       </c>
       <c r="F74" s="18">
         <v>3.9</v>
@@ -15234,7 +15246,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="75" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15243,11 +15255,11 @@
         <v>396</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18">
-        <v>1.1000000000000001</v>
+        <v>8.3666666666666707</v>
       </c>
       <c r="F75" s="18">
         <v>3.9</v>
@@ -15256,7 +15268,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15265,11 +15277,11 @@
         <v>396</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D76" s="18"/>
       <c r="E76" s="18">
-        <v>0.66666666666666696</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="F76" s="18">
         <v>3.9</v>
@@ -15278,7 +15290,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15287,11 +15299,11 @@
         <v>396</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D77" s="18"/>
       <c r="E77" s="18">
-        <v>0.73333333333333295</v>
+        <v>10.5666666666667</v>
       </c>
       <c r="F77" s="18">
         <v>3.9</v>
@@ -15300,7 +15312,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15309,11 +15321,11 @@
         <v>396</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18">
-        <v>0.75</v>
+        <v>1.7</v>
       </c>
       <c r="F78" s="18">
         <v>3.9</v>
@@ -15322,7 +15334,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="79" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15331,11 +15343,11 @@
         <v>396</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D79" s="18"/>
       <c r="E79" s="18">
-        <v>8.3666666666666707</v>
+        <v>0.73333333333333295</v>
       </c>
       <c r="F79" s="18">
         <v>3.9</v>
@@ -15344,7 +15356,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="80" spans="1:8" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="str">
         <f t="shared" si="2"/>
         <v>IT</v>
@@ -15353,11 +15365,11 @@
         <v>396</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D80" s="18"/>
       <c r="E80" s="18">
-        <v>9.6999999999999993</v>
+        <v>0.76666666666666705</v>
       </c>
       <c r="F80" s="18">
         <v>3.9</v>
@@ -15366,92 +15378,100 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="str">
+    <row r="81" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A81" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>IT</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18">
-        <v>10.5666666666667</v>
-      </c>
-      <c r="F81" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="G81" s="18">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="str">
+        <v>LIB</v>
+      </c>
+      <c r="B81" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="E81" s="24">
+        <v>143</v>
+      </c>
+      <c r="F81" s="24">
+        <v>150</v>
+      </c>
+      <c r="G81" s="24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A82" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>IT</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18">
-        <v>1.7</v>
-      </c>
-      <c r="F82" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="G82" s="18">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="str">
+        <v>LIB</v>
+      </c>
+      <c r="B82" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D82" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="E82" s="24">
+        <v>146</v>
+      </c>
+      <c r="F82" s="24">
+        <v>150</v>
+      </c>
+      <c r="G82" s="24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A83" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>IT</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18">
-        <v>0.73333333333333295</v>
-      </c>
-      <c r="F83" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="G83" s="18">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="6" customFormat="1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="str">
+        <v>LIB</v>
+      </c>
+      <c r="B83" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="E83" s="24">
+        <v>47</v>
+      </c>
+      <c r="F83" s="24">
+        <v>150</v>
+      </c>
+      <c r="G83" s="24">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A84" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>IT</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18">
-        <v>0.76666666666666705</v>
-      </c>
-      <c r="F84" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="G84" s="18">
-        <v>3.9</v>
+        <v>LIB</v>
+      </c>
+      <c r="B84" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="E84" s="24">
+        <v>122</v>
+      </c>
+      <c r="F84" s="24">
+        <v>150</v>
+      </c>
+      <c r="G84" s="24">
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15463,13 +15483,13 @@
         <v>449</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D85" s="24" t="s">
         <v>450</v>
       </c>
       <c r="E85" s="24">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="F85" s="24">
         <v>150</v>
@@ -15487,19 +15507,19 @@
         <v>449</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E86" s="24">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F86" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G86" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15511,19 +15531,19 @@
         <v>449</v>
       </c>
       <c r="C87" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="E87" s="24">
         <v>48</v>
       </c>
-      <c r="D87" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="E87" s="24">
-        <v>47</v>
-      </c>
       <c r="F87" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G87" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15535,19 +15555,19 @@
         <v>449</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E88" s="24">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="F88" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G88" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15559,19 +15579,19 @@
         <v>449</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E89" s="24">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="F89" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G89" s="24">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15583,13 +15603,13 @@
         <v>449</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D90" s="24" t="s">
         <v>447</v>
       </c>
       <c r="E90" s="24">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F90" s="24">
         <v>50</v>
@@ -15607,13 +15627,13 @@
         <v>449</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E91" s="24">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F91" s="24">
         <v>50</v>
@@ -15631,13 +15651,13 @@
         <v>449</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E92" s="24">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="F92" s="24">
         <v>50</v>
@@ -15655,13 +15675,13 @@
         <v>449</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E93" s="24">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="F93" s="24">
         <v>50</v>
@@ -15672,17 +15692,17 @@
     </row>
     <row r="94" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A94" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A94:A125" si="3">LEFT(B94, FIND("-", B94) - 1)</f>
         <v>LIB</v>
       </c>
       <c r="B94" s="29" t="s">
         <v>449</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E94" s="24">
         <v>54</v>
@@ -15696,20 +15716,20 @@
     </row>
     <row r="95" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A95" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>LIB</v>
       </c>
       <c r="B95" s="29" t="s">
         <v>449</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D95" s="24" t="s">
         <v>448</v>
       </c>
       <c r="E95" s="24">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F95" s="24">
         <v>50</v>
@@ -15720,75 +15740,51 @@
     </row>
     <row r="96" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A96" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>LIB</v>
       </c>
       <c r="B96" s="29" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D96" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="E96" s="24">
-        <v>98</v>
-      </c>
-      <c r="F96" s="24">
-        <v>50</v>
-      </c>
-      <c r="G96" s="24">
-        <v>50</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
     </row>
     <row r="97" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A97" s="29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>LIB</v>
       </c>
       <c r="B97" s="29" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D97" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="E97" s="24">
-        <v>22</v>
-      </c>
-      <c r="F97" s="24">
-        <v>50</v>
-      </c>
-      <c r="G97" s="24">
-        <v>50</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
     </row>
     <row r="98" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A98" s="29" t="str">
-        <f t="shared" ref="A98:A129" si="3">LEFT(B98, FIND("-", B98) - 1)</f>
+        <f t="shared" si="3"/>
         <v>LIB</v>
       </c>
       <c r="B98" s="29" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D98" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="E98" s="24">
-        <v>54</v>
-      </c>
-      <c r="F98" s="24">
-        <v>50</v>
-      </c>
-      <c r="G98" s="24">
-        <v>50</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
     </row>
     <row r="99" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A99" s="29" t="str">
@@ -15796,23 +15792,15 @@
         <v>LIB</v>
       </c>
       <c r="B99" s="29" t="s">
-        <v>449</v>
+        <v>400</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D99" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="E99" s="24">
-        <v>58</v>
-      </c>
-      <c r="F99" s="24">
-        <v>50</v>
-      </c>
-      <c r="G99" s="24">
-        <v>50</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="D99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
     </row>
     <row r="100" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A100" s="29" t="str">
@@ -15820,7 +15808,7 @@
         <v>LIB</v>
       </c>
       <c r="B100" s="29" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C100" s="24" t="s">
         <v>430</v>
@@ -15836,7 +15824,7 @@
         <v>LIB</v>
       </c>
       <c r="B101" s="29" t="s">
-        <v>446</v>
+        <v>402</v>
       </c>
       <c r="C101" s="24" t="s">
         <v>430</v>
@@ -15852,7 +15840,7 @@
         <v>LIB</v>
       </c>
       <c r="B102" s="29" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C102" s="24" t="s">
         <v>430</v>
@@ -15868,15 +15856,21 @@
         <v>LIB</v>
       </c>
       <c r="B103" s="29" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>430</v>
+        <v>46</v>
       </c>
       <c r="D103" s="24"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="24"/>
+      <c r="E103" s="24">
+        <v>65014</v>
+      </c>
+      <c r="F103" s="24">
+        <v>71834</v>
+      </c>
+      <c r="G103" s="24">
+        <v>62464</v>
+      </c>
     </row>
     <row r="104" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A104" s="29" t="str">
@@ -15884,15 +15878,21 @@
         <v>LIB</v>
       </c>
       <c r="B104" s="29" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C104" s="24" t="s">
-        <v>430</v>
+        <v>47</v>
       </c>
       <c r="D104" s="24"/>
-      <c r="E104" s="24"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="24"/>
+      <c r="E104" s="24">
+        <v>103774</v>
+      </c>
+      <c r="F104" s="24">
+        <v>102033</v>
+      </c>
+      <c r="G104" s="24">
+        <v>88724</v>
+      </c>
     </row>
     <row r="105" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A105" s="29" t="str">
@@ -15900,15 +15900,21 @@
         <v>LIB</v>
       </c>
       <c r="B105" s="29" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C105" s="24" t="s">
-        <v>430</v>
+        <v>40</v>
       </c>
       <c r="D105" s="24"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="24"/>
+      <c r="E105" s="24">
+        <v>211580</v>
+      </c>
+      <c r="F105" s="24">
+        <v>150513</v>
+      </c>
+      <c r="G105" s="24">
+        <v>130881</v>
+      </c>
     </row>
     <row r="106" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A106" s="29" t="str">
@@ -15916,15 +15922,21 @@
         <v>LIB</v>
       </c>
       <c r="B106" s="29" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C106" s="24" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
       <c r="D106" s="24"/>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
+      <c r="E106" s="24">
+        <v>280116</v>
+      </c>
+      <c r="F106" s="24">
+        <v>173234</v>
+      </c>
+      <c r="G106" s="24">
+        <v>150638</v>
+      </c>
     </row>
     <row r="107" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A107" s="29" t="str">
@@ -15935,17 +15947,17 @@
         <v>397</v>
       </c>
       <c r="C107" s="24" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D107" s="24"/>
       <c r="E107" s="24">
-        <v>65014</v>
+        <v>287958</v>
       </c>
       <c r="F107" s="24">
-        <v>71834</v>
+        <v>197111</v>
       </c>
       <c r="G107" s="24">
-        <v>62464</v>
+        <v>171401</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -15957,105 +15969,113 @@
         <v>397</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D108" s="24"/>
       <c r="E108" s="24">
-        <v>103774</v>
+        <v>293189</v>
       </c>
       <c r="F108" s="24">
-        <v>102033</v>
+        <v>201250</v>
       </c>
       <c r="G108" s="24">
-        <v>88724</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A109" s="29" t="str">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A109" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>LIB</v>
-      </c>
-      <c r="B109" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="C109" s="24" t="s">
+        <v>PIO</v>
+      </c>
+      <c r="B109" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="E109" s="25">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F109" s="25">
+        <v>5.9</v>
+      </c>
+      <c r="G109" s="25">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A110" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>PIO</v>
+      </c>
+      <c r="B110" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="C110" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D109" s="24"/>
-      <c r="E109" s="24">
-        <v>211580</v>
-      </c>
-      <c r="F109" s="24">
-        <v>150513</v>
-      </c>
-      <c r="G109" s="24">
-        <v>130881</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A110" s="29" t="str">
+      <c r="D110" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="E110" s="25">
+        <v>4.2</v>
+      </c>
+      <c r="F110" s="25">
+        <v>5.9</v>
+      </c>
+      <c r="G110" s="25">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A111" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>LIB</v>
-      </c>
-      <c r="B110" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="C110" s="24" t="s">
+        <v>PIO</v>
+      </c>
+      <c r="B111" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="C111" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D110" s="24"/>
-      <c r="E110" s="24">
-        <v>280116</v>
-      </c>
-      <c r="F110" s="24">
-        <v>173234</v>
-      </c>
-      <c r="G110" s="24">
-        <v>150638</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A111" s="29" t="str">
+      <c r="D111" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="E111" s="25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F111" s="25">
+        <v>5.9</v>
+      </c>
+      <c r="G111" s="25">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
+      <c r="A112" s="30" t="str">
         <f t="shared" si="3"/>
-        <v>LIB</v>
-      </c>
-      <c r="B111" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="C111" s="24" t="s">
+        <v>PIO</v>
+      </c>
+      <c r="B112" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="C112" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D111" s="24"/>
-      <c r="E111" s="24">
-        <v>287958</v>
-      </c>
-      <c r="F111" s="24">
-        <v>197111</v>
-      </c>
-      <c r="G111" s="24">
-        <v>171401</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" s="29" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A112" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>LIB</v>
-      </c>
-      <c r="B112" s="29" t="s">
-        <v>397</v>
-      </c>
-      <c r="C112" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D112" s="24"/>
-      <c r="E112" s="24">
-        <v>293189</v>
-      </c>
-      <c r="F112" s="24">
-        <v>201250</v>
-      </c>
-      <c r="G112" s="24">
-        <v>175000</v>
+      <c r="D112" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="E112" s="25">
+        <v>5.7</v>
+      </c>
+      <c r="F112" s="25">
+        <v>5.9</v>
+      </c>
+      <c r="G112" s="25">
+        <v>2.6</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16067,19 +16087,19 @@
         <v>431</v>
       </c>
       <c r="C113" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D113" s="25" t="s">
         <v>434</v>
       </c>
       <c r="E113" s="25">
-        <v>4.1100000000000003</v>
+        <v>3.5</v>
       </c>
       <c r="F113" s="25">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="G113" s="25">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16091,19 +16111,19 @@
         <v>431</v>
       </c>
       <c r="C114" s="25" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D114" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E114" s="25">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="F114" s="25">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="G114" s="25">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16115,19 +16135,19 @@
         <v>431</v>
       </c>
       <c r="C115" s="25" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D115" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E115" s="25">
-        <v>5.0999999999999996</v>
+        <v>6.9</v>
       </c>
       <c r="F115" s="25">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="G115" s="25">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16139,19 +16159,19 @@
         <v>431</v>
       </c>
       <c r="C116" s="25" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D116" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E116" s="25">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="F116" s="25">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="G116" s="25">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16163,19 +16183,19 @@
         <v>431</v>
       </c>
       <c r="C117" s="25" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D117" s="25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E117" s="25">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F117" s="25">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="G117" s="25">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16187,19 +16207,19 @@
         <v>431</v>
       </c>
       <c r="C118" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D118" s="25" t="s">
         <v>435</v>
       </c>
       <c r="E118" s="25">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="F118" s="25">
         <v>6.5</v>
       </c>
       <c r="G118" s="25">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16214,16 +16234,16 @@
         <v>40</v>
       </c>
       <c r="D119" s="25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E119" s="25">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="F119" s="25">
-        <v>6.5</v>
+        <v>21.2</v>
       </c>
       <c r="G119" s="25">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16238,16 +16258,16 @@
         <v>48</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E120" s="25">
-        <v>7.7</v>
+        <v>16.8</v>
       </c>
       <c r="F120" s="25">
-        <v>6.5</v>
+        <v>21.2</v>
       </c>
       <c r="G120" s="25">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16262,16 +16282,16 @@
         <v>42</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E121" s="25">
-        <v>6.3</v>
+        <v>20.6</v>
       </c>
       <c r="F121" s="25">
-        <v>6.5</v>
+        <v>21.2</v>
       </c>
       <c r="G121" s="25">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16286,16 +16306,16 @@
         <v>49</v>
       </c>
       <c r="D122" s="25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E122" s="25">
-        <v>7.9</v>
+        <v>14.34</v>
       </c>
       <c r="F122" s="25">
-        <v>6.5</v>
+        <v>21.2</v>
       </c>
       <c r="G122" s="25">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16307,19 +16327,19 @@
         <v>431</v>
       </c>
       <c r="C123" s="25" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D123" s="25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E123" s="25">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="F123" s="25">
-        <v>21.2</v>
+        <v>4.7</v>
       </c>
       <c r="G123" s="25">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16331,19 +16351,19 @@
         <v>431</v>
       </c>
       <c r="C124" s="25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D124" s="25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E124" s="25">
-        <v>16.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F124" s="25">
-        <v>21.2</v>
+        <v>4.7</v>
       </c>
       <c r="G124" s="25">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
@@ -16355,131 +16375,97 @@
         <v>431</v>
       </c>
       <c r="C125" s="25" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D125" s="25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E125" s="25">
-        <v>20.6</v>
+        <v>5.4</v>
       </c>
       <c r="F125" s="25">
-        <v>21.2</v>
+        <v>4.7</v>
       </c>
       <c r="G125" s="25">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A126" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>PIO</v>
-      </c>
-      <c r="B126" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D126" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="E126" s="25">
-        <v>14.34</v>
-      </c>
-      <c r="F126" s="25">
-        <v>21.2</v>
-      </c>
-      <c r="G126" s="25">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A127" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>PIO</v>
-      </c>
-      <c r="B127" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C127" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D127" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="E127" s="25">
-        <v>3.7</v>
-      </c>
-      <c r="F127" s="25">
-        <v>4.7</v>
-      </c>
-      <c r="G127" s="25">
         <v>1.6</v>
       </c>
     </row>
-    <row r="128" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A128" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>PIO</v>
-      </c>
-      <c r="B128" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C128" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D128" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="E128" s="25">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F128" s="25">
-        <v>4.7</v>
-      </c>
-      <c r="G128" s="25">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" s="30" customFormat="1" ht="14" x14ac:dyDescent="0.15">
-      <c r="A129" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>PIO</v>
-      </c>
-      <c r="B129" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C129" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D129" s="25" t="s">
-        <v>437</v>
-      </c>
-      <c r="E129" s="25">
-        <v>5.4</v>
-      </c>
-      <c r="F129" s="25">
-        <v>4.7</v>
-      </c>
-      <c r="G129" s="25">
-        <v>1.6</v>
-      </c>
+    <row r="126" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A126" s="9" t="str">
+        <f t="shared" ref="A126:A132" si="4">LEFT(B126, FIND("-", B126) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C126" s="21"/>
+      <c r="D126" s="21"/>
+      <c r="E126" s="21"/>
+      <c r="F126" s="21">
+        <v>85</v>
+      </c>
+      <c r="G126" s="21"/>
+    </row>
+    <row r="127" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A127" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>TRAN</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C127" s="21"/>
+      <c r="D127" s="21"/>
+      <c r="E127" s="21"/>
+      <c r="F127" s="21">
+        <v>100</v>
+      </c>
+      <c r="G127" s="21">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A128" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>TRAN</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="C128" s="21"/>
+      <c r="D128" s="21"/>
+      <c r="E128" s="21"/>
+      <c r="F128" s="21"/>
+      <c r="G128" s="21"/>
+    </row>
+    <row r="129" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A129" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>TRAN</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C129" s="21"/>
+      <c r="D129" s="21"/>
+      <c r="E129" s="21"/>
+      <c r="F129" s="21">
+        <v>100</v>
+      </c>
+      <c r="G129" s="21"/>
     </row>
     <row r="130" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A130" s="9" t="str">
-        <f t="shared" ref="A130:A161" si="4">LEFT(B130, FIND("-", B130) - 1)</f>
+        <f t="shared" si="4"/>
         <v>TRAN</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C130" s="21"/>
       <c r="D130" s="21"/>
       <c r="E130" s="21"/>
-      <c r="F130" s="21">
-        <v>85</v>
-      </c>
+      <c r="F130" s="21"/>
       <c r="G130" s="21"/>
     </row>
     <row r="131" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16488,17 +16474,13 @@
         <v>TRAN</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C131" s="21"/>
       <c r="D131" s="21"/>
       <c r="E131" s="21"/>
-      <c r="F131" s="21">
-        <v>100</v>
-      </c>
-      <c r="G131" s="21">
-        <v>95</v>
-      </c>
+      <c r="F131" s="21"/>
+      <c r="G131" s="21"/>
     </row>
     <row r="132" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A132" s="9" t="str">
@@ -16506,7 +16488,7 @@
         <v>TRAN</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C132" s="21"/>
       <c r="D132" s="21"/>
@@ -16514,78 +16496,73 @@
       <c r="F132" s="21"/>
       <c r="G132" s="21"/>
     </row>
-    <row r="133" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A133" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>TRAN</v>
-      </c>
-      <c r="B133" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21">
-        <v>100</v>
-      </c>
-      <c r="G133" s="21"/>
-    </row>
-    <row r="134" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A134" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>TRAN</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-    </row>
-    <row r="135" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A135" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>TRAN</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-    </row>
-    <row r="136" spans="1:7" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A136" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>TRAN</v>
-      </c>
-      <c r="B136" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="21"/>
-      <c r="G136" s="21"/>
+    <row r="133" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A133" s="72" t="str">
+        <f t="shared" ref="A133:A176" si="5">LEFT(B133, FIND("-", B133) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B133" s="72" t="s">
+        <v>509</v>
+      </c>
+      <c r="F133" s="72" t="str" cm="1">
+        <f t="array" ref="F133">IFERROR(_xlfn.XLOOKUP(B2&amp;"|"&amp;(C2-1)&amp;"|"&amp;D2, $B$2:$B$496&amp;"|"&amp;$C$2:$C$496&amp;"|"&amp;$D$2:$D$496, $E$2:$E$496), "")</f>
+        <v/>
+      </c>
+      <c r="G133" s="72">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A134" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>PROS</v>
+      </c>
+      <c r="B134" s="72" t="s">
+        <v>510</v>
+      </c>
+      <c r="F134" s="72" t="str" cm="1">
+        <f t="array" ref="F134">IFERROR(_xlfn.XLOOKUP(B3&amp;"|"&amp;(C3-1)&amp;"|"&amp;D3, $B$2:$B$496&amp;"|"&amp;$C$2:$C$496&amp;"|"&amp;$D$2:$D$496, $E$2:$E$496), "")</f>
+        <v/>
+      </c>
+      <c r="G134" s="72">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A135" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>PROS</v>
+      </c>
+      <c r="B135" s="72" t="s">
+        <v>511</v>
+      </c>
+      <c r="F135" s="72" t="str" cm="1">
+        <f t="array" ref="F135">IFERROR(_xlfn.XLOOKUP(B4&amp;"|"&amp;(C4-1)&amp;"|"&amp;D4, $B$2:$B$496&amp;"|"&amp;$C$2:$C$496&amp;"|"&amp;$D$2:$D$496, $E$2:$E$496), "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A136" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>PROS</v>
+      </c>
+      <c r="B136" s="72" t="s">
+        <v>519</v>
+      </c>
+      <c r="F136" s="72">
+        <v>96</v>
+      </c>
     </row>
     <row r="137" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A137" s="72" t="str">
-        <f t="shared" ref="A137:A180" si="5">LEFT(B137, FIND("-", B137) - 1)</f>
+        <f t="shared" si="5"/>
         <v>PROS</v>
       </c>
       <c r="B137" s="72" t="s">
-        <v>512</v>
-      </c>
-      <c r="F137" s="72" t="str" cm="1">
-        <f t="array" ref="F137">IFERROR(_xlfn.XLOOKUP(B2&amp;"|"&amp;(C2-1)&amp;"|"&amp;D2, $B$2:$B$500&amp;"|"&amp;$C$2:$C$500&amp;"|"&amp;$D$2:$D$500, $E$2:$E$500), "")</f>
-        <v/>
-      </c>
-      <c r="G137" s="72">
-        <v>99</v>
+        <v>520</v>
+      </c>
+      <c r="F137" s="72">
+        <v>368438</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16594,14 +16571,7 @@
         <v>PROS</v>
       </c>
       <c r="B138" s="72" t="s">
-        <v>513</v>
-      </c>
-      <c r="F138" s="72" t="str" cm="1">
-        <f t="array" ref="F138">IFERROR(_xlfn.XLOOKUP(B3&amp;"|"&amp;(C3-1)&amp;"|"&amp;D3, $B$2:$B$500&amp;"|"&amp;$C$2:$C$500&amp;"|"&amp;$D$2:$D$500, $E$2:$E$500), "")</f>
-        <v/>
-      </c>
-      <c r="G138" s="72">
-        <v>606</v>
+        <v>521</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16610,11 +16580,10 @@
         <v>PROS</v>
       </c>
       <c r="B139" s="72" t="s">
-        <v>514</v>
-      </c>
-      <c r="F139" s="72" t="str" cm="1">
-        <f t="array" ref="F139">IFERROR(_xlfn.XLOOKUP(B4&amp;"|"&amp;(C4-1)&amp;"|"&amp;D4, $B$2:$B$500&amp;"|"&amp;$C$2:$C$500&amp;"|"&amp;$D$2:$D$500, $E$2:$E$500), "")</f>
-        <v/>
+        <v>522</v>
+      </c>
+      <c r="F139" s="72">
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16623,10 +16592,11 @@
         <v>PROS</v>
       </c>
       <c r="B140" s="72" t="s">
-        <v>522</v>
-      </c>
-      <c r="F140" s="72">
-        <v>96</v>
+        <v>523</v>
+      </c>
+      <c r="F140" s="72" t="str" cm="1">
+        <f t="array" ref="F140">IFERROR(_xlfn.XLOOKUP(B3&amp;"|"&amp;(C3-1)&amp;"|"&amp;D3, $B$2:$B$496&amp;"|"&amp;$C$2:$C$496&amp;"|"&amp;$D$2:$D$496, $E$2:$E$496) * 1.01, "")</f>
+        <v/>
       </c>
     </row>
     <row r="141" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16635,10 +16605,10 @@
         <v>PROS</v>
       </c>
       <c r="B141" s="72" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F141" s="72">
-        <v>368438</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="142" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16647,7 +16617,11 @@
         <v>PROS</v>
       </c>
       <c r="B142" s="72" t="s">
-        <v>524</v>
+        <v>525</v>
+      </c>
+      <c r="F142" s="72" t="str" cm="1">
+        <f t="array" ref="F142">IFERROR(_xlfn.XLOOKUP(B2&amp;"|"&amp;(C2-1)&amp;"|"&amp;D2, $B$2:$B$496&amp;"|"&amp;$C$2:$C$496&amp;"|"&amp;$D$2:$D$496, $E$2:$E$496) * 1.02, "")</f>
+        <v/>
       </c>
     </row>
     <row r="143" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16656,10 +16630,10 @@
         <v>PROS</v>
       </c>
       <c r="B143" s="72" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F143" s="72">
-        <v>65</v>
+        <v>190</v>
       </c>
     </row>
     <row r="144" spans="1:7" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16668,168 +16642,154 @@
         <v>PROS</v>
       </c>
       <c r="B144" s="72" t="s">
-        <v>526</v>
-      </c>
-      <c r="F144" s="72" t="str" cm="1">
-        <f t="array" ref="F144">IFERROR(_xlfn.XLOOKUP(B3&amp;"|"&amp;(C3-1)&amp;"|"&amp;D3, $B$2:$B$500&amp;"|"&amp;$C$2:$C$500&amp;"|"&amp;$D$2:$D$500, $E$2:$E$500) * 1.01, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+      <c r="F144" s="72">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A145" s="72" t="str">
         <f t="shared" si="5"/>
         <v>PROS</v>
       </c>
       <c r="B145" s="72" t="s">
-        <v>527</v>
-      </c>
-      <c r="F145" s="72">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A146" s="72" t="str">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A146" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>PROS</v>
-      </c>
-      <c r="B146" s="72" t="s">
-        <v>528</v>
-      </c>
-      <c r="F146" s="72" t="str" cm="1">
-        <f t="array" ref="F146">IFERROR(_xlfn.XLOOKUP(B2&amp;"|"&amp;(C2-1)&amp;"|"&amp;D2, $B$2:$B$500&amp;"|"&amp;$C$2:$C$500&amp;"|"&amp;$D$2:$D$500, $E$2:$E$500) * 1.02, "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A147" s="72" t="str">
+        <v>PD</v>
+      </c>
+      <c r="B146" s="82" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A147" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>PROS</v>
-      </c>
-      <c r="B147" s="72" t="s">
-        <v>532</v>
-      </c>
-      <c r="F147" s="72">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A148" s="72" t="str">
+        <v>PD</v>
+      </c>
+      <c r="B147" s="82" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A148" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>PROS</v>
-      </c>
-      <c r="B148" s="72" t="s">
-        <v>533</v>
-      </c>
-      <c r="F148" s="72">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" s="72" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A149" s="72" t="str">
+        <v>PD</v>
+      </c>
+      <c r="B148" s="82" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A149" s="82" t="str">
         <f t="shared" si="5"/>
-        <v>PROS</v>
-      </c>
-      <c r="B149" s="72" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>PD</v>
+      </c>
+      <c r="B149" s="82" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A150" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B150" s="82" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A151" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B151" s="82" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A152" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B152" s="82" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A153" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B153" s="82" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A154" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B154" s="82" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A155" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B155" s="82" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A156" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B156" s="82" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A157" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B157" s="82" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A158" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B158" s="82" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A159" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B159" s="82" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
       <c r="A160" s="82" t="str">
         <f t="shared" si="5"/>
         <v>PD</v>
       </c>
       <c r="B160" s="82" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="161" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16838,7 +16798,7 @@
         <v>PD</v>
       </c>
       <c r="B161" s="82" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="162" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16847,7 +16807,7 @@
         <v>PD</v>
       </c>
       <c r="B162" s="82" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="163" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16856,7 +16816,7 @@
         <v>PD</v>
       </c>
       <c r="B163" s="82" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="164" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16865,7 +16825,7 @@
         <v>PD</v>
       </c>
       <c r="B164" s="82" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="165" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16874,7 +16834,7 @@
         <v>PD</v>
       </c>
       <c r="B165" s="82" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="166" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16883,7 +16843,7 @@
         <v>PD</v>
       </c>
       <c r="B166" s="82" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="167" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16892,7 +16852,7 @@
         <v>PD</v>
       </c>
       <c r="B167" s="82" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="168" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16901,7 +16861,7 @@
         <v>PD</v>
       </c>
       <c r="B168" s="82" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="169" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16910,43 +16870,43 @@
         <v>PD</v>
       </c>
       <c r="B169" s="82" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A170" s="82" t="str">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A170" s="32" t="str">
         <f t="shared" si="5"/>
-        <v>PD</v>
-      </c>
-      <c r="B170" s="82" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A171" s="82" t="str">
+        <v>911</v>
+      </c>
+      <c r="B170" s="32" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A171" s="32" t="str">
         <f t="shared" si="5"/>
-        <v>PD</v>
-      </c>
-      <c r="B171" s="82" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A172" s="82" t="str">
+        <v>911</v>
+      </c>
+      <c r="B171" s="32" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A172" s="32" t="str">
         <f t="shared" si="5"/>
-        <v>PD</v>
-      </c>
-      <c r="B172" s="82" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" s="82" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A173" s="82" t="str">
+        <v>911</v>
+      </c>
+      <c r="B172" s="32" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
+      <c r="A173" s="32" t="str">
         <f t="shared" si="5"/>
-        <v>PD</v>
-      </c>
-      <c r="B173" s="82" t="s">
-        <v>583</v>
+        <v>911</v>
+      </c>
+      <c r="B173" s="32" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="174" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16955,7 +16915,7 @@
         <v>911</v>
       </c>
       <c r="B174" s="32" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="175" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16964,7 +16924,7 @@
         <v>911</v>
       </c>
       <c r="B175" s="32" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="176" spans="1:2" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
@@ -16973,46 +16933,46 @@
         <v>911</v>
       </c>
       <c r="B176" s="32" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A177" s="32" t="str">
-        <f t="shared" si="5"/>
-        <v>911</v>
-      </c>
-      <c r="B177" s="32" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="178" spans="1:8" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A178" s="32" t="str">
-        <f t="shared" si="5"/>
-        <v>911</v>
-      </c>
-      <c r="B178" s="32" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A179" s="32" t="str">
-        <f t="shared" si="5"/>
-        <v>911</v>
-      </c>
-      <c r="B179" s="32" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" s="32" customFormat="1" ht="13" x14ac:dyDescent="0.2">
-      <c r="A180" s="32" t="str">
-        <f t="shared" si="5"/>
-        <v>911</v>
-      </c>
-      <c r="B180" s="32" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B177" s="3"/>
+      <c r="C177" s="23"/>
+      <c r="D177" s="22"/>
+      <c r="E177" s="22"/>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
+      <c r="H177" s="1"/>
+    </row>
+    <row r="178" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B178" s="3"/>
+      <c r="C178" s="23"/>
+      <c r="D178" s="22"/>
+      <c r="E178" s="22"/>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22"/>
+      <c r="H178" s="1"/>
+    </row>
+    <row r="179" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B179" s="3"/>
+      <c r="C179" s="23"/>
+      <c r="D179" s="22"/>
+      <c r="E179" s="22"/>
+      <c r="F179" s="22"/>
+      <c r="G179" s="22"/>
+      <c r="H179" s="1"/>
+    </row>
+    <row r="180" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B180" s="3"/>
+      <c r="C180" s="23"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="22"/>
+      <c r="F180" s="22"/>
+      <c r="G180" s="22"/>
+      <c r="H180" s="1"/>
+    </row>
+    <row r="181" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B181" s="3"/>
       <c r="C181" s="23"/>
       <c r="D181" s="22"/>
@@ -17021,7 +16981,7 @@
       <c r="G181" s="22"/>
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B182" s="3"/>
       <c r="C182" s="23"/>
       <c r="D182" s="22"/>
@@ -17030,7 +16990,7 @@
       <c r="G182" s="22"/>
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B183" s="3"/>
       <c r="C183" s="23"/>
       <c r="D183" s="22"/>
@@ -17039,7 +16999,7 @@
       <c r="G183" s="22"/>
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B184" s="3"/>
       <c r="C184" s="23"/>
       <c r="D184" s="22"/>
@@ -17048,7 +17008,7 @@
       <c r="G184" s="22"/>
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B185" s="3"/>
       <c r="C185" s="23"/>
       <c r="D185" s="22"/>
@@ -17057,7 +17017,7 @@
       <c r="G185" s="22"/>
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B186" s="3"/>
       <c r="C186" s="23"/>
       <c r="D186" s="22"/>
@@ -17066,7 +17026,7 @@
       <c r="G186" s="22"/>
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B187" s="3"/>
       <c r="C187" s="23"/>
       <c r="D187" s="22"/>
@@ -17075,7 +17035,7 @@
       <c r="G187" s="22"/>
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B188" s="3"/>
       <c r="C188" s="23"/>
       <c r="D188" s="22"/>
@@ -17084,7 +17044,7 @@
       <c r="G188" s="22"/>
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B189" s="3"/>
       <c r="C189" s="23"/>
       <c r="D189" s="22"/>
@@ -17093,7 +17053,7 @@
       <c r="G189" s="22"/>
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B190" s="3"/>
       <c r="C190" s="23"/>
       <c r="D190" s="22"/>
@@ -17102,7 +17062,7 @@
       <c r="G190" s="22"/>
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B191" s="3"/>
       <c r="C191" s="23"/>
       <c r="D191" s="22"/>
@@ -17111,7 +17071,7 @@
       <c r="G191" s="22"/>
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B192" s="3"/>
       <c r="C192" s="23"/>
       <c r="D192" s="22"/>
@@ -24518,46 +24478,10 @@
       <c r="G1014" s="22"/>
       <c r="H1014" s="1"/>
     </row>
-    <row r="1015" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1015" s="3"/>
-      <c r="C1015" s="23"/>
-      <c r="D1015" s="22"/>
-      <c r="E1015" s="22"/>
-      <c r="F1015" s="22"/>
-      <c r="G1015" s="22"/>
-      <c r="H1015" s="1"/>
-    </row>
-    <row r="1016" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1016" s="3"/>
-      <c r="C1016" s="23"/>
-      <c r="D1016" s="22"/>
-      <c r="E1016" s="22"/>
-      <c r="F1016" s="22"/>
-      <c r="G1016" s="22"/>
-      <c r="H1016" s="1"/>
-    </row>
-    <row r="1017" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1017" s="3"/>
-      <c r="C1017" s="23"/>
-      <c r="D1017" s="22"/>
-      <c r="E1017" s="22"/>
-      <c r="F1017" s="22"/>
-      <c r="G1017" s="22"/>
-      <c r="H1017" s="1"/>
-    </row>
-    <row r="1018" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1018" s="3"/>
-      <c r="C1018" s="23"/>
-      <c r="D1018" s="22"/>
-      <c r="E1018" s="22"/>
-      <c r="F1018" s="22"/>
-      <c r="G1018" s="22"/>
-      <c r="H1018" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H132" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H136">
-      <sortCondition ref="A1:A136"/>
+  <autoFilter ref="A1:H128" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H132">
+      <sortCondition ref="A1:A132"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -25894,7 +25818,7 @@
         <v>36</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>87</v>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MaryCathryn.Lord/Desktop/CoD_PerformanceDash_External/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F614F3E8678A308FC923DE7420A52097798EB40D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257D06A5-B221-7642-8903-F0E3C8B16BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KPI Catalog'!$A$1:$U$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'KPI Data'!$A$1:$H$129</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -261,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="951">
   <si>
     <t>Dept</t>
   </si>
@@ -3149,6 +3149,18 @@
   </si>
   <si>
     <t>Goal (auto)</t>
+  </si>
+  <si>
+    <t>PC and Desktops Replaced within lifecycle</t>
+  </si>
+  <si>
+    <t>total regulated affordable housing units</t>
+  </si>
+  <si>
+    <t>building permits issued under prop 123</t>
+  </si>
+  <si>
+    <t>total residential building permits</t>
   </si>
 </sst>
 </file>
@@ -4944,7 +4956,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="22" customWidth="1"/>
@@ -5283,9 +5295,7 @@
       <c r="D18" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="33" t="s">
-        <v>77</v>
-      </c>
+      <c r="E18" s="33"/>
       <c r="F18" s="31"/>
       <c r="G18" s="31"/>
       <c r="H18" s="31"/>
@@ -5298,9 +5308,7 @@
       <c r="B19" s="188"/>
       <c r="C19" s="190"/>
       <c r="D19" s="35"/>
-      <c r="E19" s="33" t="s">
-        <v>78</v>
-      </c>
+      <c r="E19" s="33"/>
       <c r="F19" s="36"/>
       <c r="G19" s="36"/>
       <c r="H19" s="36"/>
@@ -5313,9 +5321,7 @@
       <c r="B20" s="188"/>
       <c r="C20" s="190"/>
       <c r="D20" s="35"/>
-      <c r="E20" s="33" t="s">
-        <v>79</v>
-      </c>
+      <c r="E20" s="33"/>
       <c r="F20" s="36"/>
       <c r="G20" s="36"/>
       <c r="H20" s="36"/>
@@ -6116,7 +6122,7 @@
         <v>167</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>168</v>
+        <v>948</v>
       </c>
       <c r="F68" s="42"/>
       <c r="G68" s="42"/>
@@ -6131,7 +6137,7 @@
       <c r="C69" s="197"/>
       <c r="D69" s="40"/>
       <c r="E69" s="41" t="s">
-        <v>159</v>
+        <v>949</v>
       </c>
       <c r="F69" s="42"/>
       <c r="G69" s="42"/>
@@ -6146,7 +6152,7 @@
       <c r="C70" s="197"/>
       <c r="D70" s="40"/>
       <c r="E70" s="41" t="s">
-        <v>168</v>
+        <v>950</v>
       </c>
       <c r="F70" s="42"/>
       <c r="G70" s="42"/>
@@ -6161,7 +6167,7 @@
       <c r="C71" s="197"/>
       <c r="D71" s="40"/>
       <c r="E71" s="41" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F71" s="42"/>
       <c r="G71" s="42"/>
@@ -6172,15 +6178,11 @@
     </row>
     <row r="72" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="194"/>
-      <c r="B72" s="195"/>
-      <c r="C72" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="D72" s="40" t="s">
-        <v>170</v>
-      </c>
+      <c r="B72" s="194"/>
+      <c r="C72" s="197"/>
+      <c r="D72" s="40"/>
       <c r="E72" s="41" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F72" s="42"/>
       <c r="G72" s="42"/>
@@ -6189,19 +6191,13 @@
       <c r="J72" s="42"/>
       <c r="K72" s="42"/>
     </row>
-    <row r="73" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="194"/>
-      <c r="B73" s="195" t="s">
-        <v>172</v>
-      </c>
-      <c r="C73" s="197" t="s">
-        <v>173</v>
-      </c>
-      <c r="D73" s="40" t="s">
-        <v>174</v>
-      </c>
+      <c r="B73" s="194"/>
+      <c r="C73" s="197"/>
+      <c r="D73" s="40"/>
       <c r="E73" s="41" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F73" s="42"/>
       <c r="G73" s="42"/>
@@ -6210,13 +6206,17 @@
       <c r="J73" s="42"/>
       <c r="K73" s="42"/>
     </row>
-    <row r="74" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="194"/>
-      <c r="B74" s="194"/>
-      <c r="C74" s="197"/>
-      <c r="D74" s="40"/>
+      <c r="B74" s="195"/>
+      <c r="C74" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="D74" s="40" t="s">
+        <v>170</v>
+      </c>
       <c r="E74" s="41" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F74" s="42"/>
       <c r="G74" s="42"/>
@@ -6225,17 +6225,19 @@
       <c r="J74" s="42"/>
       <c r="K74" s="42"/>
     </row>
-    <row r="75" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="194"/>
-      <c r="B75" s="194"/>
-      <c r="C75" s="43" t="s">
-        <v>177</v>
+      <c r="B75" s="195" t="s">
+        <v>172</v>
+      </c>
+      <c r="C75" s="197" t="s">
+        <v>173</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E75" s="41" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F75" s="42"/>
       <c r="G75" s="42"/>
@@ -6244,17 +6246,13 @@
       <c r="J75" s="42"/>
       <c r="K75" s="42"/>
     </row>
-    <row r="76" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="194"/>
       <c r="B76" s="194"/>
-      <c r="C76" s="197" t="s">
-        <v>180</v>
-      </c>
-      <c r="D76" s="40" t="s">
-        <v>181</v>
-      </c>
+      <c r="C76" s="197"/>
+      <c r="D76" s="40"/>
       <c r="E76" s="41" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F76" s="42"/>
       <c r="G76" s="42"/>
@@ -6266,10 +6264,14 @@
     <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="194"/>
       <c r="B77" s="194"/>
-      <c r="C77" s="197"/>
-      <c r="D77" s="40"/>
+      <c r="C77" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>178</v>
+      </c>
       <c r="E77" s="41" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F77" s="42"/>
       <c r="G77" s="42"/>
@@ -6281,10 +6283,14 @@
     <row r="78" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="194"/>
       <c r="B78" s="194"/>
-      <c r="C78" s="197"/>
-      <c r="D78" s="40"/>
+      <c r="C78" s="197" t="s">
+        <v>180</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>181</v>
+      </c>
       <c r="E78" s="41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F78" s="42"/>
       <c r="G78" s="42"/>
@@ -6295,11 +6301,11 @@
     </row>
     <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="194"/>
-      <c r="B79" s="195"/>
+      <c r="B79" s="194"/>
       <c r="C79" s="197"/>
       <c r="D79" s="40"/>
       <c r="E79" s="41" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F79" s="42"/>
       <c r="G79" s="42"/>
@@ -6310,16 +6316,12 @@
     </row>
     <row r="80" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="194"/>
-      <c r="B80" s="195" t="s">
-        <v>186</v>
-      </c>
-      <c r="C80" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="D80" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="E80" s="41"/>
+      <c r="B80" s="194"/>
+      <c r="C80" s="197"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="41" t="s">
+        <v>184</v>
+      </c>
       <c r="F80" s="42"/>
       <c r="G80" s="42"/>
       <c r="H80" s="42"/>
@@ -6329,14 +6331,12 @@
     </row>
     <row r="81" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="194"/>
-      <c r="B81" s="194"/>
-      <c r="C81" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="D81" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="E81" s="41"/>
+      <c r="B81" s="195"/>
+      <c r="C81" s="197"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="41" t="s">
+        <v>185</v>
+      </c>
       <c r="F81" s="42"/>
       <c r="G81" s="42"/>
       <c r="H81" s="42"/>
@@ -6346,12 +6346,14 @@
     </row>
     <row r="82" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="194"/>
-      <c r="B82" s="194"/>
+      <c r="B82" s="195" t="s">
+        <v>186</v>
+      </c>
       <c r="C82" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E82" s="41"/>
       <c r="F82" s="42"/>
@@ -6365,10 +6367,10 @@
       <c r="A83" s="194"/>
       <c r="B83" s="194"/>
       <c r="C83" s="42" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E83" s="41"/>
       <c r="F83" s="42"/>
@@ -6380,12 +6382,12 @@
     </row>
     <row r="84" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="194"/>
-      <c r="B84" s="195"/>
+      <c r="B84" s="194"/>
       <c r="C84" s="42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E84" s="41"/>
       <c r="F84" s="42"/>
@@ -6396,50 +6398,54 @@
       <c r="K84" s="42"/>
     </row>
     <row r="85" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="198" t="s">
+      <c r="A85" s="194"/>
+      <c r="B85" s="194"/>
+      <c r="C85" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="D85" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="41"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
+    </row>
+    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="194"/>
+      <c r="B86" s="195"/>
+      <c r="C86" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" s="41"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="40"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="42"/>
+    </row>
+    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="198" t="s">
         <v>197</v>
       </c>
-      <c r="B85" s="199" t="s">
+      <c r="B87" s="199" t="s">
         <v>198</v>
       </c>
-      <c r="C85" s="200" t="s">
+      <c r="C87" s="200" t="s">
         <v>199</v>
       </c>
-      <c r="D85" s="44" t="s">
+      <c r="D87" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="E85" s="45" t="s">
+      <c r="E87" s="45" t="s">
         <v>201</v>
-      </c>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
-      <c r="H85" s="46"/>
-      <c r="I85" s="44"/>
-      <c r="J85" s="46"/>
-      <c r="K85" s="46"/>
-    </row>
-    <row r="86" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="198"/>
-      <c r="B86" s="198"/>
-      <c r="C86" s="200"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="45" t="s">
-        <v>202</v>
-      </c>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="46"/>
-      <c r="K86" s="46"/>
-    </row>
-    <row r="87" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="198"/>
-      <c r="B87" s="198"/>
-      <c r="C87" s="200"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="45" t="s">
-        <v>203</v>
       </c>
       <c r="F87" s="46"/>
       <c r="G87" s="46"/>
@@ -6454,7 +6460,7 @@
       <c r="C88" s="200"/>
       <c r="D88" s="44"/>
       <c r="E88" s="45" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F88" s="46"/>
       <c r="G88" s="46"/>
@@ -6469,7 +6475,7 @@
       <c r="C89" s="200"/>
       <c r="D89" s="44"/>
       <c r="E89" s="45" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F89" s="46"/>
       <c r="G89" s="46"/>
@@ -6481,14 +6487,10 @@
     <row r="90" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="198"/>
       <c r="B90" s="198"/>
-      <c r="C90" s="201" t="s">
-        <v>206</v>
-      </c>
-      <c r="D90" s="44" t="s">
-        <v>207</v>
-      </c>
+      <c r="C90" s="200"/>
+      <c r="D90" s="44"/>
       <c r="E90" s="45" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F90" s="46"/>
       <c r="G90" s="46"/>
@@ -6500,10 +6502,10 @@
     <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="198"/>
       <c r="B91" s="198"/>
-      <c r="C91" s="201"/>
+      <c r="C91" s="200"/>
       <c r="D91" s="44"/>
       <c r="E91" s="45" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F91" s="46"/>
       <c r="G91" s="46"/>
@@ -6515,10 +6517,14 @@
     <row r="92" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="198"/>
       <c r="B92" s="198"/>
-      <c r="C92" s="201"/>
-      <c r="D92" s="44"/>
+      <c r="C92" s="201" t="s">
+        <v>206</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>207</v>
+      </c>
       <c r="E92" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F92" s="46"/>
       <c r="G92" s="46"/>
@@ -6530,14 +6536,10 @@
     <row r="93" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="198"/>
       <c r="B93" s="198"/>
-      <c r="C93" s="201" t="s">
-        <v>211</v>
-      </c>
-      <c r="D93" s="44" t="s">
-        <v>212</v>
-      </c>
+      <c r="C93" s="201"/>
+      <c r="D93" s="44"/>
       <c r="E93" s="45" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F93" s="46"/>
       <c r="G93" s="46"/>
@@ -6552,7 +6554,7 @@
       <c r="C94" s="201"/>
       <c r="D94" s="44"/>
       <c r="E94" s="45" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F94" s="46"/>
       <c r="G94" s="46"/>
@@ -6564,10 +6566,14 @@
     <row r="95" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="198"/>
       <c r="B95" s="198"/>
-      <c r="C95" s="201"/>
-      <c r="D95" s="44"/>
+      <c r="C95" s="201" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>212</v>
+      </c>
       <c r="E95" s="45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F95" s="46"/>
       <c r="G95" s="46"/>
@@ -6579,14 +6585,10 @@
     <row r="96" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="198"/>
       <c r="B96" s="198"/>
-      <c r="C96" s="201" t="s">
-        <v>216</v>
-      </c>
-      <c r="D96" s="44" t="s">
-        <v>217</v>
-      </c>
+      <c r="C96" s="201"/>
+      <c r="D96" s="44"/>
       <c r="E96" s="45" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F96" s="46"/>
       <c r="G96" s="46"/>
@@ -6601,7 +6603,7 @@
       <c r="C97" s="201"/>
       <c r="D97" s="44"/>
       <c r="E97" s="45" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F97" s="46"/>
       <c r="G97" s="46"/>
@@ -6613,10 +6615,14 @@
     <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="198"/>
       <c r="B98" s="198"/>
-      <c r="C98" s="201"/>
-      <c r="D98" s="44"/>
+      <c r="C98" s="201" t="s">
+        <v>216</v>
+      </c>
+      <c r="D98" s="44" t="s">
+        <v>217</v>
+      </c>
       <c r="E98" s="45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F98" s="46"/>
       <c r="G98" s="46"/>
@@ -6631,7 +6637,7 @@
       <c r="C99" s="201"/>
       <c r="D99" s="44"/>
       <c r="E99" s="45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F99" s="46"/>
       <c r="G99" s="46"/>
@@ -6646,7 +6652,7 @@
       <c r="C100" s="201"/>
       <c r="D100" s="44"/>
       <c r="E100" s="45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F100" s="46"/>
       <c r="G100" s="46"/>
@@ -6661,7 +6667,7 @@
       <c r="C101" s="201"/>
       <c r="D101" s="44"/>
       <c r="E101" s="45" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="F101" s="46"/>
       <c r="G101" s="46"/>
@@ -6676,7 +6682,7 @@
       <c r="C102" s="201"/>
       <c r="D102" s="44"/>
       <c r="E102" s="45" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F102" s="46"/>
       <c r="G102" s="46"/>
@@ -6691,7 +6697,7 @@
       <c r="C103" s="201"/>
       <c r="D103" s="44"/>
       <c r="E103" s="45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F103" s="46"/>
       <c r="G103" s="46"/>
@@ -6706,7 +6712,7 @@
       <c r="C104" s="201"/>
       <c r="D104" s="44"/>
       <c r="E104" s="45" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F104" s="46"/>
       <c r="G104" s="46"/>
@@ -6718,14 +6724,10 @@
     <row r="105" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="198"/>
       <c r="B105" s="198"/>
-      <c r="C105" s="201" t="s">
-        <v>224</v>
-      </c>
-      <c r="D105" s="44" t="s">
-        <v>225</v>
-      </c>
+      <c r="C105" s="201"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="45" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F105" s="46"/>
       <c r="G105" s="46"/>
@@ -6740,7 +6742,7 @@
       <c r="C106" s="201"/>
       <c r="D106" s="44"/>
       <c r="E106" s="45" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F106" s="46"/>
       <c r="G106" s="46"/>
@@ -6752,10 +6754,14 @@
     <row r="107" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="198"/>
       <c r="B107" s="198"/>
-      <c r="C107" s="201"/>
-      <c r="D107" s="44"/>
+      <c r="C107" s="201" t="s">
+        <v>224</v>
+      </c>
+      <c r="D107" s="44" t="s">
+        <v>225</v>
+      </c>
       <c r="E107" s="45" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F107" s="46"/>
       <c r="G107" s="46"/>
@@ -6770,7 +6776,7 @@
       <c r="C108" s="201"/>
       <c r="D108" s="44"/>
       <c r="E108" s="45" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F108" s="46"/>
       <c r="G108" s="46"/>
@@ -6785,7 +6791,7 @@
       <c r="C109" s="201"/>
       <c r="D109" s="44"/>
       <c r="E109" s="45" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F109" s="46"/>
       <c r="G109" s="46"/>
@@ -6800,7 +6806,7 @@
       <c r="C110" s="201"/>
       <c r="D110" s="44"/>
       <c r="E110" s="45" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F110" s="46"/>
       <c r="G110" s="46"/>
@@ -6809,17 +6815,13 @@
       <c r="J110" s="46"/>
       <c r="K110" s="46"/>
     </row>
-    <row r="111" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="198"/>
       <c r="B111" s="198"/>
-      <c r="C111" s="201" t="s">
-        <v>232</v>
-      </c>
-      <c r="D111" s="44" t="s">
-        <v>233</v>
-      </c>
+      <c r="C111" s="201"/>
+      <c r="D111" s="44"/>
       <c r="E111" s="45" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F111" s="46"/>
       <c r="G111" s="46"/>
@@ -6834,7 +6836,7 @@
       <c r="C112" s="201"/>
       <c r="D112" s="44"/>
       <c r="E112" s="45" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F112" s="46"/>
       <c r="G112" s="46"/>
@@ -6843,36 +6845,32 @@
       <c r="J112" s="46"/>
       <c r="K112" s="46"/>
     </row>
-    <row r="113" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="198"/>
-      <c r="B113" s="199"/>
-      <c r="C113" s="46" t="s">
-        <v>236</v>
+      <c r="B113" s="198"/>
+      <c r="C113" s="201" t="s">
+        <v>232</v>
       </c>
       <c r="D113" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="E113" s="45"/>
+        <v>233</v>
+      </c>
+      <c r="E113" s="45" t="s">
+        <v>234</v>
+      </c>
       <c r="F113" s="46"/>
       <c r="G113" s="46"/>
       <c r="H113" s="46"/>
       <c r="I113" s="44"/>
-      <c r="J113" s="47"/>
-      <c r="K113" s="47"/>
+      <c r="J113" s="46"/>
+      <c r="K113" s="46"/>
     </row>
     <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="198"/>
-      <c r="B114" s="199" t="s">
-        <v>238</v>
-      </c>
-      <c r="C114" s="201" t="s">
-        <v>239</v>
-      </c>
-      <c r="D114" s="44" t="s">
-        <v>240</v>
-      </c>
+      <c r="B114" s="198"/>
+      <c r="C114" s="201"/>
+      <c r="D114" s="44"/>
       <c r="E114" s="45" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F114" s="46"/>
       <c r="G114" s="46"/>
@@ -6883,26 +6881,34 @@
     </row>
     <row r="115" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="198"/>
-      <c r="B115" s="198"/>
-      <c r="C115" s="201"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="45" t="s">
-        <v>242</v>
-      </c>
+      <c r="B115" s="199"/>
+      <c r="C115" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D115" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E115" s="45"/>
       <c r="F115" s="46"/>
       <c r="G115" s="46"/>
       <c r="H115" s="46"/>
       <c r="I115" s="44"/>
-      <c r="J115" s="46"/>
-      <c r="K115" s="46"/>
+      <c r="J115" s="47"/>
+      <c r="K115" s="47"/>
     </row>
     <row r="116" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="198"/>
-      <c r="B116" s="198"/>
-      <c r="C116" s="201"/>
-      <c r="D116" s="44"/>
+      <c r="B116" s="199" t="s">
+        <v>238</v>
+      </c>
+      <c r="C116" s="201" t="s">
+        <v>239</v>
+      </c>
+      <c r="D116" s="44" t="s">
+        <v>240</v>
+      </c>
       <c r="E116" s="45" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F116" s="46"/>
       <c r="G116" s="46"/>
@@ -6914,14 +6920,10 @@
     <row r="117" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="198"/>
       <c r="B117" s="198"/>
-      <c r="C117" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="D117" s="44" t="s">
-        <v>245</v>
-      </c>
+      <c r="C117" s="201"/>
+      <c r="D117" s="44"/>
       <c r="E117" s="45" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F117" s="46"/>
       <c r="G117" s="46"/>
@@ -6932,67 +6934,67 @@
     </row>
     <row r="118" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="198"/>
-      <c r="B118" s="199"/>
-      <c r="C118" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="D118" s="44" t="s">
-        <v>248</v>
-      </c>
-      <c r="E118" s="45"/>
+      <c r="B118" s="198"/>
+      <c r="C118" s="201"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="45" t="s">
+        <v>243</v>
+      </c>
       <c r="F118" s="46"/>
       <c r="G118" s="46"/>
       <c r="H118" s="46"/>
       <c r="I118" s="44"/>
-      <c r="J118" s="47"/>
-      <c r="K118" s="47"/>
+      <c r="J118" s="46"/>
+      <c r="K118" s="46"/>
     </row>
     <row r="119" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="202" t="s">
+      <c r="A119" s="198"/>
+      <c r="B119" s="198"/>
+      <c r="C119" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="D119" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="E119" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="F119" s="46"/>
+      <c r="G119" s="46"/>
+      <c r="H119" s="46"/>
+      <c r="I119" s="44"/>
+      <c r="J119" s="46"/>
+      <c r="K119" s="46"/>
+    </row>
+    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="198"/>
+      <c r="B120" s="199"/>
+      <c r="C120" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="D120" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="E120" s="45"/>
+      <c r="F120" s="46"/>
+      <c r="G120" s="46"/>
+      <c r="H120" s="46"/>
+      <c r="I120" s="44"/>
+      <c r="J120" s="47"/>
+      <c r="K120" s="47"/>
+    </row>
+    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="202" t="s">
         <v>249</v>
       </c>
-      <c r="B119" s="203" t="s">
+      <c r="B121" s="203" t="s">
         <v>250</v>
       </c>
-      <c r="C119" s="48" t="s">
+      <c r="C121" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="D119" s="49" t="s">
+      <c r="D121" s="49" t="s">
         <v>252</v>
-      </c>
-      <c r="E119" s="50"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="48"/>
-      <c r="H119" s="48"/>
-      <c r="I119" s="49"/>
-      <c r="J119" s="48"/>
-      <c r="K119" s="48"/>
-    </row>
-    <row r="120" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="202"/>
-      <c r="B120" s="202"/>
-      <c r="C120" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="D120" s="49" t="s">
-        <v>254</v>
-      </c>
-      <c r="E120" s="50"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="48"/>
-      <c r="I120" s="49"/>
-      <c r="J120" s="48"/>
-      <c r="K120" s="48"/>
-    </row>
-    <row r="121" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="202"/>
-      <c r="B121" s="202"/>
-      <c r="C121" s="48" t="s">
-        <v>255</v>
-      </c>
-      <c r="D121" s="49" t="s">
-        <v>256</v>
       </c>
       <c r="E121" s="50"/>
       <c r="F121" s="48"/>
@@ -7006,10 +7008,10 @@
       <c r="A122" s="202"/>
       <c r="B122" s="202"/>
       <c r="C122" s="48" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E122" s="50"/>
       <c r="F122" s="48"/>
@@ -7023,10 +7025,10 @@
       <c r="A123" s="202"/>
       <c r="B123" s="202"/>
       <c r="C123" s="48" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E123" s="50"/>
       <c r="F123" s="48"/>
@@ -7040,10 +7042,10 @@
       <c r="A124" s="202"/>
       <c r="B124" s="202"/>
       <c r="C124" s="48" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E124" s="50"/>
       <c r="F124" s="48"/>
@@ -7057,10 +7059,10 @@
       <c r="A125" s="202"/>
       <c r="B125" s="202"/>
       <c r="C125" s="48" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E125" s="50"/>
       <c r="F125" s="48"/>
@@ -7074,10 +7076,10 @@
       <c r="A126" s="202"/>
       <c r="B126" s="202"/>
       <c r="C126" s="48" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E126" s="50"/>
       <c r="F126" s="48"/>
@@ -7089,12 +7091,12 @@
     </row>
     <row r="127" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="202"/>
-      <c r="B127" s="203"/>
+      <c r="B127" s="202"/>
       <c r="C127" s="48" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E127" s="50"/>
       <c r="F127" s="48"/>
@@ -7106,18 +7108,14 @@
     </row>
     <row r="128" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="202"/>
-      <c r="B128" s="203" t="s">
-        <v>269</v>
-      </c>
-      <c r="C128" s="204" t="s">
-        <v>270</v>
+      <c r="B128" s="202"/>
+      <c r="C128" s="48" t="s">
+        <v>265</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="E128" s="50" t="s">
-        <v>272</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="E128" s="50"/>
       <c r="F128" s="48"/>
       <c r="G128" s="48"/>
       <c r="H128" s="48"/>
@@ -7127,12 +7125,14 @@
     </row>
     <row r="129" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="202"/>
-      <c r="B129" s="202"/>
-      <c r="C129" s="204"/>
-      <c r="D129" s="49"/>
-      <c r="E129" s="50" t="s">
-        <v>273</v>
-      </c>
+      <c r="B129" s="203"/>
+      <c r="C129" s="48" t="s">
+        <v>267</v>
+      </c>
+      <c r="D129" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="E129" s="50"/>
       <c r="F129" s="48"/>
       <c r="G129" s="48"/>
       <c r="H129" s="48"/>
@@ -7142,11 +7142,17 @@
     </row>
     <row r="130" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="202"/>
-      <c r="B130" s="202"/>
-      <c r="C130" s="204"/>
-      <c r="D130" s="49"/>
+      <c r="B130" s="203" t="s">
+        <v>269</v>
+      </c>
+      <c r="C130" s="204" t="s">
+        <v>270</v>
+      </c>
+      <c r="D130" s="49" t="s">
+        <v>271</v>
+      </c>
       <c r="E130" s="50" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F130" s="48"/>
       <c r="G130" s="48"/>
@@ -7158,18 +7164,14 @@
     <row r="131" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="202"/>
       <c r="B131" s="202"/>
-      <c r="C131" s="48" t="s">
-        <v>275</v>
-      </c>
-      <c r="D131" s="49" t="s">
-        <v>276</v>
-      </c>
+      <c r="C131" s="204"/>
+      <c r="D131" s="49"/>
       <c r="E131" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="F131" s="50"/>
-      <c r="G131" s="50"/>
-      <c r="H131" s="50"/>
+        <v>273</v>
+      </c>
+      <c r="F131" s="48"/>
+      <c r="G131" s="48"/>
+      <c r="H131" s="48"/>
       <c r="I131" s="49"/>
       <c r="J131" s="48"/>
       <c r="K131" s="48"/>
@@ -7177,14 +7179,10 @@
     <row r="132" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="202"/>
       <c r="B132" s="202"/>
-      <c r="C132" s="204" t="s">
-        <v>278</v>
-      </c>
-      <c r="D132" s="49" t="s">
-        <v>279</v>
-      </c>
+      <c r="C132" s="204"/>
+      <c r="D132" s="49"/>
       <c r="E132" s="50" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F132" s="48"/>
       <c r="G132" s="48"/>
@@ -7196,14 +7194,18 @@
     <row r="133" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="202"/>
       <c r="B133" s="202"/>
-      <c r="C133" s="204"/>
-      <c r="D133" s="49"/>
+      <c r="C133" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="D133" s="49" t="s">
+        <v>276</v>
+      </c>
       <c r="E133" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="F133" s="48"/>
-      <c r="G133" s="48"/>
-      <c r="H133" s="48"/>
+        <v>277</v>
+      </c>
+      <c r="F133" s="50"/>
+      <c r="G133" s="50"/>
+      <c r="H133" s="50"/>
       <c r="I133" s="49"/>
       <c r="J133" s="48"/>
       <c r="K133" s="48"/>
@@ -7211,10 +7213,14 @@
     <row r="134" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="202"/>
       <c r="B134" s="202"/>
-      <c r="C134" s="204"/>
-      <c r="D134" s="49"/>
+      <c r="C134" s="204" t="s">
+        <v>278</v>
+      </c>
+      <c r="D134" s="49" t="s">
+        <v>279</v>
+      </c>
       <c r="E134" s="50" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F134" s="48"/>
       <c r="G134" s="48"/>
@@ -7226,14 +7232,10 @@
     <row r="135" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="202"/>
       <c r="B135" s="202"/>
-      <c r="C135" s="204" t="s">
-        <v>283</v>
-      </c>
-      <c r="D135" s="49" t="s">
-        <v>284</v>
-      </c>
+      <c r="C135" s="204"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="50" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F135" s="48"/>
       <c r="G135" s="48"/>
@@ -7248,7 +7250,7 @@
       <c r="C136" s="204"/>
       <c r="D136" s="49"/>
       <c r="E136" s="50" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F136" s="48"/>
       <c r="G136" s="48"/>
@@ -7260,14 +7262,14 @@
     <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="202"/>
       <c r="B137" s="202"/>
-      <c r="C137" s="48" t="s">
-        <v>287</v>
+      <c r="C137" s="204" t="s">
+        <v>283</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E137" s="50" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F137" s="48"/>
       <c r="G137" s="48"/>
@@ -7279,14 +7281,10 @@
     <row r="138" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="202"/>
       <c r="B138" s="202"/>
-      <c r="C138" s="204" t="s">
-        <v>290</v>
-      </c>
-      <c r="D138" s="49" t="s">
-        <v>291</v>
-      </c>
+      <c r="C138" s="204"/>
+      <c r="D138" s="49"/>
       <c r="E138" s="50" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F138" s="48"/>
       <c r="G138" s="48"/>
@@ -7298,10 +7296,14 @@
     <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="202"/>
       <c r="B139" s="202"/>
-      <c r="C139" s="204"/>
-      <c r="D139" s="49"/>
+      <c r="C139" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="D139" s="49" t="s">
+        <v>288</v>
+      </c>
       <c r="E139" s="50" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F139" s="48"/>
       <c r="G139" s="48"/>
@@ -7314,13 +7316,13 @@
       <c r="A140" s="202"/>
       <c r="B140" s="202"/>
       <c r="C140" s="204" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E140" s="50" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F140" s="48"/>
       <c r="G140" s="48"/>
@@ -7335,7 +7337,7 @@
       <c r="C141" s="204"/>
       <c r="D141" s="49"/>
       <c r="E141" s="50" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F141" s="48"/>
       <c r="G141" s="48"/>
@@ -7347,10 +7349,14 @@
     <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="202"/>
       <c r="B142" s="202"/>
-      <c r="C142" s="204"/>
-      <c r="D142" s="49"/>
+      <c r="C142" s="204" t="s">
+        <v>294</v>
+      </c>
+      <c r="D142" s="49" t="s">
+        <v>295</v>
+      </c>
       <c r="E142" s="50" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F142" s="48"/>
       <c r="G142" s="48"/>
@@ -7361,11 +7367,11 @@
     </row>
     <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="202"/>
-      <c r="B143" s="203"/>
+      <c r="B143" s="202"/>
       <c r="C143" s="204"/>
       <c r="D143" s="49"/>
       <c r="E143" s="50" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F143" s="48"/>
       <c r="G143" s="48"/>
@@ -7376,16 +7382,12 @@
     </row>
     <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="202"/>
-      <c r="B144" s="203" t="s">
-        <v>300</v>
-      </c>
-      <c r="C144" s="48" t="s">
-        <v>301</v>
-      </c>
-      <c r="D144" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="E144" s="50"/>
+      <c r="B144" s="202"/>
+      <c r="C144" s="204"/>
+      <c r="D144" s="49"/>
+      <c r="E144" s="50" t="s">
+        <v>298</v>
+      </c>
       <c r="F144" s="48"/>
       <c r="G144" s="48"/>
       <c r="H144" s="48"/>
@@ -7395,29 +7397,29 @@
     </row>
     <row r="145" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="202"/>
-      <c r="B145" s="202"/>
-      <c r="C145" s="48" t="s">
-        <v>303</v>
-      </c>
-      <c r="D145" s="49" t="s">
-        <v>304</v>
-      </c>
-      <c r="E145" s="50"/>
+      <c r="B145" s="203"/>
+      <c r="C145" s="204"/>
+      <c r="D145" s="49"/>
+      <c r="E145" s="50" t="s">
+        <v>299</v>
+      </c>
       <c r="F145" s="48"/>
       <c r="G145" s="48"/>
       <c r="H145" s="48"/>
       <c r="I145" s="49"/>
-      <c r="J145" s="51"/>
-      <c r="K145" s="51"/>
+      <c r="J145" s="48"/>
+      <c r="K145" s="48"/>
     </row>
     <row r="146" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="202"/>
-      <c r="B146" s="202"/>
+      <c r="B146" s="203" t="s">
+        <v>300</v>
+      </c>
       <c r="C146" s="48" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E146" s="50"/>
       <c r="F146" s="48"/>
@@ -7431,29 +7433,31 @@
       <c r="A147" s="202"/>
       <c r="B147" s="202"/>
       <c r="C147" s="48" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D147" s="49" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E147" s="50"/>
       <c r="F147" s="48"/>
       <c r="G147" s="48"/>
       <c r="H147" s="48"/>
       <c r="I147" s="49"/>
-      <c r="J147" s="48"/>
-      <c r="K147" s="48"/>
+      <c r="J147" s="51"/>
+      <c r="K147" s="51"/>
     </row>
     <row r="148" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="202"/>
       <c r="B148" s="202"/>
       <c r="C148" s="48" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D148" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="E148" s="50"/>
+        <v>306</v>
+      </c>
+      <c r="E148" s="50" t="s">
+        <v>947</v>
+      </c>
       <c r="F148" s="48"/>
       <c r="G148" s="48"/>
       <c r="H148" s="48"/>
@@ -7465,10 +7469,10 @@
       <c r="A149" s="202"/>
       <c r="B149" s="202"/>
       <c r="C149" s="48" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D149" s="49" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E149" s="50"/>
       <c r="F149" s="48"/>
@@ -7482,27 +7486,27 @@
       <c r="A150" s="202"/>
       <c r="B150" s="202"/>
       <c r="C150" s="48" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D150" s="49" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E150" s="50"/>
       <c r="F150" s="48"/>
       <c r="G150" s="48"/>
       <c r="H150" s="48"/>
       <c r="I150" s="49"/>
-      <c r="J150" s="51"/>
-      <c r="K150" s="51"/>
+      <c r="J150" s="48"/>
+      <c r="K150" s="48"/>
     </row>
     <row r="151" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="202"/>
       <c r="B151" s="202"/>
       <c r="C151" s="48" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D151" s="49" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E151" s="50"/>
       <c r="F151" s="48"/>
@@ -7516,27 +7520,27 @@
       <c r="A152" s="202"/>
       <c r="B152" s="202"/>
       <c r="C152" s="48" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D152" s="49" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E152" s="50"/>
       <c r="F152" s="48"/>
       <c r="G152" s="48"/>
       <c r="H152" s="48"/>
       <c r="I152" s="49"/>
-      <c r="J152" s="48"/>
-      <c r="K152" s="48"/>
+      <c r="J152" s="51"/>
+      <c r="K152" s="51"/>
     </row>
     <row r="153" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="202"/>
       <c r="B153" s="202"/>
       <c r="C153" s="48" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D153" s="49" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E153" s="50"/>
       <c r="F153" s="48"/>
@@ -7548,12 +7552,12 @@
     </row>
     <row r="154" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="202"/>
-      <c r="B154" s="203"/>
+      <c r="B154" s="202"/>
       <c r="C154" s="48" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D154" s="49" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E154" s="50"/>
       <c r="F154" s="48"/>
@@ -7565,14 +7569,12 @@
     </row>
     <row r="155" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="202"/>
-      <c r="B155" s="203" t="s">
-        <v>323</v>
-      </c>
+      <c r="B155" s="202"/>
       <c r="C155" s="48" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D155" s="49" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E155" s="50"/>
       <c r="F155" s="48"/>
@@ -7584,12 +7586,12 @@
     </row>
     <row r="156" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="202"/>
-      <c r="B156" s="202"/>
+      <c r="B156" s="203"/>
       <c r="C156" s="48" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D156" s="49" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E156" s="50"/>
       <c r="F156" s="48"/>
@@ -7601,87 +7603,89 @@
     </row>
     <row r="157" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="202"/>
-      <c r="B157" s="202"/>
+      <c r="B157" s="203" t="s">
+        <v>323</v>
+      </c>
       <c r="C157" s="48" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D157" s="49" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E157" s="50"/>
       <c r="F157" s="48"/>
       <c r="G157" s="48"/>
       <c r="H157" s="48"/>
       <c r="I157" s="49"/>
-      <c r="J157" s="51"/>
-      <c r="K157" s="51"/>
+      <c r="J157" s="48"/>
+      <c r="K157" s="48"/>
     </row>
     <row r="158" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="202"/>
-      <c r="B158" s="203"/>
+      <c r="B158" s="202"/>
       <c r="C158" s="48" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D158" s="49" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E158" s="50"/>
       <c r="F158" s="48"/>
       <c r="G158" s="48"/>
       <c r="H158" s="48"/>
       <c r="I158" s="49"/>
-      <c r="J158" s="51"/>
-      <c r="K158" s="51"/>
+      <c r="J158" s="48"/>
+      <c r="K158" s="48"/>
     </row>
     <row r="159" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="205" t="s">
+      <c r="A159" s="202"/>
+      <c r="B159" s="202"/>
+      <c r="C159" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="D159" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="E159" s="50"/>
+      <c r="F159" s="48"/>
+      <c r="G159" s="48"/>
+      <c r="H159" s="48"/>
+      <c r="I159" s="49"/>
+      <c r="J159" s="51"/>
+      <c r="K159" s="51"/>
+    </row>
+    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="202"/>
+      <c r="B160" s="203"/>
+      <c r="C160" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D160" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="E160" s="50"/>
+      <c r="F160" s="48"/>
+      <c r="G160" s="48"/>
+      <c r="H160" s="48"/>
+      <c r="I160" s="49"/>
+      <c r="J160" s="51"/>
+      <c r="K160" s="51"/>
+    </row>
+    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="205" t="s">
         <v>332</v>
       </c>
-      <c r="B159" s="206" t="s">
+      <c r="B161" s="206" t="s">
         <v>333</v>
       </c>
-      <c r="C159" s="52" t="s">
+      <c r="C161" s="52" t="s">
         <v>334</v>
       </c>
-      <c r="D159" s="53" t="s">
+      <c r="D161" s="53" t="s">
         <v>335</v>
       </c>
-      <c r="E159" s="54" t="s">
+      <c r="E161" s="54" t="s">
         <v>336</v>
-      </c>
-      <c r="F159" s="52"/>
-      <c r="G159" s="52"/>
-      <c r="H159" s="52"/>
-      <c r="I159" s="53"/>
-      <c r="J159" s="52"/>
-      <c r="K159" s="52"/>
-    </row>
-    <row r="160" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="205"/>
-      <c r="B160" s="205"/>
-      <c r="C160" s="207" t="s">
-        <v>337</v>
-      </c>
-      <c r="D160" s="53" t="s">
-        <v>338</v>
-      </c>
-      <c r="E160" s="54" t="s">
-        <v>339</v>
-      </c>
-      <c r="F160" s="52"/>
-      <c r="G160" s="52"/>
-      <c r="H160" s="52"/>
-      <c r="I160" s="53"/>
-      <c r="J160" s="52"/>
-      <c r="K160" s="52"/>
-    </row>
-    <row r="161" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="205"/>
-      <c r="B161" s="205"/>
-      <c r="C161" s="207"/>
-      <c r="D161" s="53"/>
-      <c r="E161" s="54" t="s">
-        <v>340</v>
       </c>
       <c r="F161" s="52"/>
       <c r="G161" s="52"/>
@@ -7693,10 +7697,14 @@
     <row r="162" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="205"/>
       <c r="B162" s="205"/>
-      <c r="C162" s="207"/>
-      <c r="D162" s="53"/>
+      <c r="C162" s="207" t="s">
+        <v>337</v>
+      </c>
+      <c r="D162" s="53" t="s">
+        <v>338</v>
+      </c>
       <c r="E162" s="54" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F162" s="52"/>
       <c r="G162" s="52"/>
@@ -7708,14 +7716,10 @@
     <row r="163" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="205"/>
       <c r="B163" s="205"/>
-      <c r="C163" s="52" t="s">
-        <v>342</v>
-      </c>
-      <c r="D163" s="53" t="s">
-        <v>343</v>
-      </c>
+      <c r="C163" s="207"/>
+      <c r="D163" s="53"/>
       <c r="E163" s="54" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F163" s="52"/>
       <c r="G163" s="52"/>
@@ -7727,14 +7731,10 @@
     <row r="164" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="205"/>
       <c r="B164" s="205"/>
-      <c r="C164" s="207" t="s">
-        <v>345</v>
-      </c>
-      <c r="D164" s="53" t="s">
-        <v>346</v>
-      </c>
+      <c r="C164" s="207"/>
+      <c r="D164" s="53"/>
       <c r="E164" s="54" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F164" s="52"/>
       <c r="G164" s="52"/>
@@ -7746,10 +7746,14 @@
     <row r="165" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="205"/>
       <c r="B165" s="205"/>
-      <c r="C165" s="207"/>
-      <c r="D165" s="53"/>
+      <c r="C165" s="52" t="s">
+        <v>342</v>
+      </c>
+      <c r="D165" s="53" t="s">
+        <v>343</v>
+      </c>
       <c r="E165" s="54" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F165" s="52"/>
       <c r="G165" s="52"/>
@@ -7761,10 +7765,14 @@
     <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="205"/>
       <c r="B166" s="205"/>
-      <c r="C166" s="207"/>
-      <c r="D166" s="53"/>
+      <c r="C166" s="207" t="s">
+        <v>345</v>
+      </c>
+      <c r="D166" s="53" t="s">
+        <v>346</v>
+      </c>
       <c r="E166" s="54" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F166" s="52"/>
       <c r="G166" s="52"/>
@@ -7775,11 +7783,11 @@
     </row>
     <row r="167" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="205"/>
-      <c r="B167" s="206"/>
+      <c r="B167" s="205"/>
       <c r="C167" s="207"/>
       <c r="D167" s="53"/>
       <c r="E167" s="54" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F167" s="52"/>
       <c r="G167" s="52"/>
@@ -7790,17 +7798,11 @@
     </row>
     <row r="168" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="205"/>
-      <c r="B168" s="208" t="s">
-        <v>351</v>
-      </c>
-      <c r="C168" s="207" t="s">
-        <v>352</v>
-      </c>
-      <c r="D168" s="53" t="s">
-        <v>353</v>
-      </c>
+      <c r="B168" s="205"/>
+      <c r="C168" s="207"/>
+      <c r="D168" s="53"/>
       <c r="E168" s="54" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F168" s="52"/>
       <c r="G168" s="52"/>
@@ -7811,11 +7813,11 @@
     </row>
     <row r="169" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="205"/>
-      <c r="B169" s="205"/>
+      <c r="B169" s="206"/>
       <c r="C169" s="207"/>
       <c r="D169" s="53"/>
       <c r="E169" s="54" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F169" s="52"/>
       <c r="G169" s="52"/>
@@ -7826,15 +7828,17 @@
     </row>
     <row r="170" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="205"/>
-      <c r="B170" s="205"/>
+      <c r="B170" s="208" t="s">
+        <v>351</v>
+      </c>
       <c r="C170" s="207" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D170" s="53" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E170" s="54" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F170" s="52"/>
       <c r="G170" s="52"/>
@@ -7849,7 +7853,7 @@
       <c r="C171" s="207"/>
       <c r="D171" s="53"/>
       <c r="E171" s="54" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F171" s="52"/>
       <c r="G171" s="52"/>
@@ -7861,14 +7865,14 @@
     <row r="172" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="205"/>
       <c r="B172" s="205"/>
-      <c r="C172" s="52" t="s">
-        <v>360</v>
+      <c r="C172" s="207" t="s">
+        <v>356</v>
       </c>
       <c r="D172" s="53" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E172" s="54" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F172" s="52"/>
       <c r="G172" s="52"/>
@@ -7880,14 +7884,10 @@
     <row r="173" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="205"/>
       <c r="B173" s="205"/>
-      <c r="C173" s="207" t="s">
-        <v>363</v>
-      </c>
-      <c r="D173" s="53" t="s">
-        <v>364</v>
-      </c>
+      <c r="C173" s="207"/>
+      <c r="D173" s="53"/>
       <c r="E173" s="54" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="F173" s="52"/>
       <c r="G173" s="52"/>
@@ -7899,10 +7899,14 @@
     <row r="174" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="205"/>
       <c r="B174" s="205"/>
-      <c r="C174" s="207"/>
-      <c r="D174" s="53"/>
+      <c r="C174" s="52" t="s">
+        <v>360</v>
+      </c>
+      <c r="D174" s="53" t="s">
+        <v>361</v>
+      </c>
       <c r="E174" s="54" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F174" s="52"/>
       <c r="G174" s="52"/>
@@ -7915,13 +7919,13 @@
       <c r="A175" s="205"/>
       <c r="B175" s="205"/>
       <c r="C175" s="207" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D175" s="53" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E175" s="54" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F175" s="52"/>
       <c r="G175" s="52"/>
@@ -7936,7 +7940,7 @@
       <c r="C176" s="207"/>
       <c r="D176" s="53"/>
       <c r="E176" s="54" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F176" s="52"/>
       <c r="G176" s="52"/>
@@ -7949,83 +7953,83 @@
       <c r="A177" s="205"/>
       <c r="B177" s="205"/>
       <c r="C177" s="207" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D177" s="53" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E177" s="54" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F177" s="52"/>
       <c r="G177" s="52"/>
       <c r="H177" s="52"/>
       <c r="I177" s="53"/>
-      <c r="J177" s="55"/>
-      <c r="K177" s="55"/>
+      <c r="J177" s="52"/>
+      <c r="K177" s="52"/>
     </row>
     <row r="178" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="205"/>
-      <c r="B178" s="208"/>
+      <c r="B178" s="205"/>
       <c r="C178" s="207"/>
       <c r="D178" s="53"/>
       <c r="E178" s="54" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F178" s="52"/>
       <c r="G178" s="52"/>
       <c r="H178" s="52"/>
       <c r="I178" s="53"/>
-      <c r="J178" s="55"/>
-      <c r="K178" s="55"/>
+      <c r="J178" s="52"/>
+      <c r="K178" s="52"/>
     </row>
     <row r="179" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="205"/>
-      <c r="B179" s="206" t="s">
-        <v>375</v>
-      </c>
+      <c r="B179" s="205"/>
       <c r="C179" s="207" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D179" s="53" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E179" s="54" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F179" s="52"/>
       <c r="G179" s="52"/>
       <c r="H179" s="52"/>
       <c r="I179" s="53"/>
-      <c r="J179" s="52"/>
-      <c r="K179" s="52"/>
+      <c r="J179" s="55"/>
+      <c r="K179" s="55"/>
     </row>
     <row r="180" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="205"/>
-      <c r="B180" s="205"/>
+      <c r="B180" s="208"/>
       <c r="C180" s="207"/>
       <c r="D180" s="53"/>
       <c r="E180" s="54" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F180" s="52"/>
       <c r="G180" s="52"/>
       <c r="H180" s="52"/>
       <c r="I180" s="53"/>
-      <c r="J180" s="52"/>
-      <c r="K180" s="52"/>
+      <c r="J180" s="55"/>
+      <c r="K180" s="55"/>
     </row>
     <row r="181" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="205"/>
-      <c r="B181" s="205"/>
-      <c r="C181" s="52" t="s">
-        <v>380</v>
+      <c r="B181" s="206" t="s">
+        <v>375</v>
+      </c>
+      <c r="C181" s="207" t="s">
+        <v>376</v>
       </c>
       <c r="D181" s="53" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E181" s="54" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F181" s="52"/>
       <c r="G181" s="52"/>
@@ -8037,14 +8041,10 @@
     <row r="182" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="205"/>
       <c r="B182" s="205"/>
-      <c r="C182" s="52" t="s">
-        <v>383</v>
-      </c>
-      <c r="D182" s="53" t="s">
-        <v>384</v>
-      </c>
+      <c r="C182" s="207"/>
+      <c r="D182" s="53"/>
       <c r="E182" s="54" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F182" s="52"/>
       <c r="G182" s="52"/>
@@ -8056,14 +8056,14 @@
     <row r="183" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="205"/>
       <c r="B183" s="205"/>
-      <c r="C183" s="207" t="s">
-        <v>386</v>
+      <c r="C183" s="52" t="s">
+        <v>380</v>
       </c>
       <c r="D183" s="53" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="E183" s="54" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F183" s="52"/>
       <c r="G183" s="52"/>
@@ -8075,10 +8075,14 @@
     <row r="184" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="205"/>
       <c r="B184" s="205"/>
-      <c r="C184" s="207"/>
-      <c r="D184" s="53"/>
+      <c r="C184" s="52" t="s">
+        <v>383</v>
+      </c>
+      <c r="D184" s="53" t="s">
+        <v>384</v>
+      </c>
       <c r="E184" s="54" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F184" s="52"/>
       <c r="G184" s="52"/>
@@ -8090,14 +8094,14 @@
     <row r="185" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="205"/>
       <c r="B185" s="205"/>
-      <c r="C185" s="52" t="s">
-        <v>390</v>
+      <c r="C185" s="207" t="s">
+        <v>386</v>
       </c>
       <c r="D185" s="53" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E185" s="54" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F185" s="52"/>
       <c r="G185" s="52"/>
@@ -8109,14 +8113,10 @@
     <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="205"/>
       <c r="B186" s="205"/>
-      <c r="C186" s="52" t="s">
-        <v>393</v>
-      </c>
-      <c r="D186" s="53" t="s">
-        <v>394</v>
-      </c>
+      <c r="C186" s="207"/>
+      <c r="D186" s="53"/>
       <c r="E186" s="54" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F186" s="52"/>
       <c r="G186" s="52"/>
@@ -8128,14 +8128,14 @@
     <row r="187" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="205"/>
       <c r="B187" s="205"/>
-      <c r="C187" s="207" t="s">
-        <v>396</v>
+      <c r="C187" s="52" t="s">
+        <v>390</v>
       </c>
       <c r="D187" s="53" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E187" s="54" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="F187" s="52"/>
       <c r="G187" s="52"/>
@@ -8147,10 +8147,14 @@
     <row r="188" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="205"/>
       <c r="B188" s="205"/>
-      <c r="C188" s="207"/>
-      <c r="D188" s="53"/>
+      <c r="C188" s="52" t="s">
+        <v>393</v>
+      </c>
+      <c r="D188" s="53" t="s">
+        <v>394</v>
+      </c>
       <c r="E188" s="54" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F188" s="52"/>
       <c r="G188" s="52"/>
@@ -8161,11 +8165,15 @@
     </row>
     <row r="189" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="205"/>
-      <c r="B189" s="206"/>
-      <c r="C189" s="207"/>
-      <c r="D189" s="53"/>
+      <c r="B189" s="205"/>
+      <c r="C189" s="207" t="s">
+        <v>396</v>
+      </c>
+      <c r="D189" s="53" t="s">
+        <v>397</v>
+      </c>
       <c r="E189" s="54" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F189" s="52"/>
       <c r="G189" s="52"/>
@@ -8174,51 +8182,81 @@
       <c r="J189" s="52"/>
       <c r="K189" s="52"/>
     </row>
+    <row r="190" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="205"/>
+      <c r="B190" s="205"/>
+      <c r="C190" s="207"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="F190" s="52"/>
+      <c r="G190" s="52"/>
+      <c r="H190" s="52"/>
+      <c r="I190" s="53"/>
+      <c r="J190" s="52"/>
+      <c r="K190" s="52"/>
+    </row>
+    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="205"/>
+      <c r="B191" s="206"/>
+      <c r="C191" s="207"/>
+      <c r="D191" s="53"/>
+      <c r="E191" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F191" s="52"/>
+      <c r="G191" s="52"/>
+      <c r="H191" s="52"/>
+      <c r="I191" s="53"/>
+      <c r="J191" s="52"/>
+      <c r="K191" s="52"/>
+    </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A159:A189"/>
-    <mergeCell ref="B159:B167"/>
-    <mergeCell ref="C160:C162"/>
-    <mergeCell ref="C164:C167"/>
-    <mergeCell ref="B168:B178"/>
-    <mergeCell ref="C168:C169"/>
+    <mergeCell ref="A161:A191"/>
+    <mergeCell ref="B161:B169"/>
+    <mergeCell ref="C162:C164"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="B170:B180"/>
     <mergeCell ref="C170:C171"/>
-    <mergeCell ref="C173:C174"/>
+    <mergeCell ref="C172:C173"/>
     <mergeCell ref="C175:C176"/>
     <mergeCell ref="C177:C178"/>
-    <mergeCell ref="B179:B189"/>
     <mergeCell ref="C179:C180"/>
-    <mergeCell ref="C183:C184"/>
-    <mergeCell ref="C187:C189"/>
-    <mergeCell ref="A119:A158"/>
-    <mergeCell ref="B119:B127"/>
-    <mergeCell ref="B128:B143"/>
-    <mergeCell ref="C128:C130"/>
-    <mergeCell ref="C132:C134"/>
-    <mergeCell ref="C135:C136"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="C140:C143"/>
-    <mergeCell ref="B144:B154"/>
-    <mergeCell ref="B155:B158"/>
-    <mergeCell ref="A85:A118"/>
-    <mergeCell ref="B85:B113"/>
-    <mergeCell ref="C85:C89"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="C96:C104"/>
-    <mergeCell ref="C105:C110"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="B114:B118"/>
-    <mergeCell ref="C114:C116"/>
-    <mergeCell ref="A61:A84"/>
-    <mergeCell ref="B61:B72"/>
+    <mergeCell ref="B181:B191"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="C185:C186"/>
+    <mergeCell ref="C189:C191"/>
+    <mergeCell ref="A121:A160"/>
+    <mergeCell ref="B121:B129"/>
+    <mergeCell ref="B130:B145"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="C134:C136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="C142:C145"/>
+    <mergeCell ref="B146:B156"/>
+    <mergeCell ref="B157:B160"/>
+    <mergeCell ref="A87:A120"/>
+    <mergeCell ref="B87:B115"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="C95:C97"/>
+    <mergeCell ref="C98:C106"/>
+    <mergeCell ref="C107:C112"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B116:B120"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="A61:A86"/>
+    <mergeCell ref="B61:B74"/>
     <mergeCell ref="C61:C63"/>
     <mergeCell ref="C64:C67"/>
-    <mergeCell ref="C68:C71"/>
-    <mergeCell ref="B73:B79"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="C76:C79"/>
-    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C68:C73"/>
+    <mergeCell ref="B75:B81"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="B82:B86"/>
     <mergeCell ref="A21:A60"/>
     <mergeCell ref="B21:B28"/>
     <mergeCell ref="B29:B43"/>
@@ -25868,7 +25906,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="136" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="130" t="str">
         <f t="shared" si="2"/>
         <v>PROS</v>
@@ -25876,10 +25914,18 @@
       <c r="B136" s="130" t="s">
         <v>680</v>
       </c>
-      <c r="F136" s="130" t="str">
-        <f t="array" ref="F136">IFERROR(_xlfn.XLOOKUP(B4&amp;"|"&amp;(C4-1)&amp;"|"&amp;D4, $B$2:$B$484&amp;"|"&amp;$C$2:$C$484&amp;"|"&amp;$D$2:$D$484, $E$2:$E$484), "")</f>
-        <v/>
-      </c>
+      <c r="C136" s="159" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D136" s="160"/>
+      <c r="E136" s="160">
+        <v>516</v>
+      </c>
+      <c r="F136" s="160"/>
+      <c r="G136" s="160"/>
+      <c r="H136" s="161"/>
     </row>
     <row r="137" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="130" t="str">
@@ -28641,19 +28687,47 @@
       <c r="H291" s="161"/>
     </row>
     <row r="292" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B292" s="163"/>
-      <c r="C292" s="159"/>
+      <c r="A292" s="130" t="str">
+        <f>LEFT(B292, FIND("-", B292) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B292" s="130" t="inlineStr">
+        <is>
+          <t>PROS-REGULATEDUNITS</t>
+        </is>
+      </c>
+      <c r="C292" s="159" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
       <c r="D292" s="160"/>
-      <c r="E292" s="160"/>
+      <c r="E292" s="160">
+        <v>516</v>
+      </c>
       <c r="F292" s="160"/>
       <c r="G292" s="160"/>
       <c r="H292" s="161"/>
     </row>
     <row r="293" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B293" s="163"/>
-      <c r="C293" s="159"/>
+      <c r="A293" s="130" t="str">
+        <f>LEFT(B293, FIND("-", B293) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B293" s="130" t="inlineStr">
+        <is>
+          <t>PROS-REGULATEDUNITS</t>
+        </is>
+      </c>
+      <c r="C293" s="159" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="D293" s="160"/>
-      <c r="E293" s="160"/>
+      <c r="E293" s="160">
+        <v>605</v>
+      </c>
       <c r="F293" s="160"/>
       <c r="G293" s="160"/>
       <c r="H293" s="161"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -15762,9 +15762,15 @@
         <f>IF(G93="","",IF(ISNUMBER(SEARCH(",",G93)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G93,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G93,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v/>
       </c>
-      <c r="I93" s="134"/>
-      <c r="J93" s="134"/>
-      <c r="K93" s="134"/>
+      <c r="I93" s="134" t="s">
+        <v>550</v>
+      </c>
+      <c r="J93" s="134">
+        <v>0</v>
+      </c>
+      <c r="K93" s="134" t="s">
+        <v>551</v>
+      </c>
       <c r="L93" s="134"/>
       <c r="M93" s="134"/>
       <c r="N93" s="134"/>
@@ -15772,9 +15778,21 @@
       <c r="P93" s="134" t="s">
         <v>589</v>
       </c>
-      <c r="Q93" s="134"/>
-      <c r="R93" s="134"/>
-      <c r="S93" s="134"/>
+      <c r="Q93" s="134" t="inlineStr">
+        <is>
+          <t>Multimodal Manager</t>
+        </is>
+      </c>
+      <c r="R93" s="134" t="inlineStr">
+        <is>
+          <t>City bike and pedestrian counts (Consolidated Count Data, 2009–2025)</t>
+        </is>
+      </c>
+      <c r="S93" s="134" t="inlineStr">
+        <is>
+          <t>Average number of people walking and biking at each count location during the morning (7–9 am) and afternoon (4–6 pm) peak counts, added up across all locations. Higher numbers mean more people are walking and biking.</t>
+        </is>
+      </c>
       <c r="T93" s="134" t="s">
         <v>694</v>
       </c>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -15073,11 +15073,13 @@
         <f>IF(G82="","",IF(ISNUMBER(SEARCH(",",G82)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G82,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G82,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v/>
       </c>
-      <c r="I82" s="130" t="s">
-        <v>550</v>
+      <c r="I82" s="130" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
       </c>
       <c r="J82" s="130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" s="130" t="s">
         <v>551</v>
@@ -15100,8 +15102,16 @@
       <c r="Q82" s="130" t="s">
         <v>668</v>
       </c>
-      <c r="R82" s="130"/>
-      <c r="S82" s="130"/>
+      <c r="R82" s="130" t="inlineStr">
+        <is>
+          <t>Submittable grant reimbursement forms (local spend reported), with some manual adjustments</t>
+        </is>
+      </c>
+      <c r="S82" s="130" t="inlineStr">
+        <is>
+          <t>Money spent locally by grant recipients, as reported on their reimbursement forms, for Lodgers' Tax Arts and Culture, Local Event Marketing, Re:New and Durango Creates! grants. Counted by the year of the grant round.</t>
+        </is>
+      </c>
       <c r="T82" s="130"/>
       <c r="U82" s="99" t="str">
         <f>IF(B82="","",IF(IF(D82&lt;&gt;"",D82,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E82,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O82="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D82&lt;&gt;"",D82,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E82,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G82)),IF(O82="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O82="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D82&lt;&gt;"",D82,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E82,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
@@ -15140,7 +15150,7 @@
         <v>550</v>
       </c>
       <c r="J83" s="130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K83" s="130" t="s">
         <v>551</v>
@@ -15164,8 +15174,16 @@
         <v>668</v>
       </c>
       <c r="R83" s="130"/>
-      <c r="S83" s="130"/>
-      <c r="T83" s="130"/>
+      <c r="S83" s="130" t="inlineStr">
+        <is>
+          <t>Room nights sold during the year to new tour companies, meeting planners and FIT (independent traveler) contracts, including nights booked now for stays in later years.</t>
+        </is>
+      </c>
+      <c r="T83" s="130" t="inlineStr">
+        <is>
+          <t>Counts new organizations only. Ongoing accounts are not included; for example, the two Tauck Tours series sold in 2024 bring about 400 room nights a year but are not in the 2026 count.</t>
+        </is>
+      </c>
       <c r="U83" s="99" t="str">
         <f>IF(B83="","",IF(IF(D83&lt;&gt;"",D83,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E83,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O83="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D83&lt;&gt;"",D83,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E83,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G83)),IF(O83="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O83="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D83&lt;&gt;"",D83,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E83,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Sets Program status chip</v>
@@ -25957,7 +25975,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="138" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="130" t="str">
         <f t="shared" si="2"/>
         <v>PROS</v>
@@ -25965,8 +25983,21 @@
       <c r="B138" s="130" t="s">
         <v>671</v>
       </c>
+      <c r="C138" s="130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E138" s="130">
+        <v>121350.25</v>
+      </c>
       <c r="F138" s="130">
         <v>368438</v>
+      </c>
+      <c r="H138" s="130" t="inlineStr">
+        <is>
+          <t>Year to date as of Oct 15, 2026; 2026 grant reimbursements are still coming in</t>
+        </is>
       </c>
     </row>
     <row r="139" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26003,7 +26034,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="130" t="str">
         <f t="shared" si="2"/>
         <v>PROS</v>
@@ -26011,8 +26042,21 @@
       <c r="B142" s="130" t="s">
         <v>672</v>
       </c>
+      <c r="C142" s="130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E142" s="130">
+        <v>1949</v>
+      </c>
       <c r="F142" s="130">
         <v>1000</v>
+      </c>
+      <c r="H142" s="130" t="inlineStr">
+        <is>
+          <t>Estimate as of Oct 21, 2026: nights already stayed plus nights booked for later stays (e.g., Model A Ford Club, June 2027)</t>
+        </is>
       </c>
     </row>
     <row r="143" spans="1:7" s="130" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28751,10 +28795,24 @@
       <c r="H293" s="161"/>
     </row>
     <row r="294" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B294" s="163"/>
-      <c r="C294" s="159"/>
+      <c r="A294" s="130" t="str">
+        <f>LEFT(B294, FIND("-", B294) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B294" s="130" t="inlineStr">
+        <is>
+          <t>PROS-LOCALSPEND</t>
+        </is>
+      </c>
+      <c r="C294" s="159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D294" s="160"/>
-      <c r="E294" s="160"/>
+      <c r="E294" s="160">
+        <v>342859.57</v>
+      </c>
       <c r="F294" s="160"/>
       <c r="G294" s="160"/>
       <c r="H294" s="161"/>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -11082,8 +11082,10 @@
       <c r="B4" s="81" t="s">
         <v>556</v>
       </c>
-      <c r="C4" s="82" t="s">
-        <v>557</v>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>911 Answer Times</t>
+        </is>
       </c>
       <c r="D4" s="81" t="s">
         <v>29</v>
@@ -11102,11 +11104,13 @@
         <f>IF(G4="","",IF(ISNUMBER(SEARCH(",",G4)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G4,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G4,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v>Program: 911 Emergency Services</v>
       </c>
-      <c r="I4" s="81" t="s">
-        <v>550</v>
+      <c r="I4" s="81" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
       </c>
       <c r="J4" s="81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="81" t="s">
         <v>551</v>
@@ -11123,15 +11127,31 @@
       <c r="O4" s="81" t="s">
         <v>551</v>
       </c>
-      <c r="P4" s="81" t="s">
-        <v>553</v>
-      </c>
-      <c r="Q4" s="81" t="s">
-        <v>554</v>
-      </c>
-      <c r="R4" s="81"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="81"/>
+      <c r="P4" s="81" t="inlineStr">
+        <is>
+          <t>Every Quarter</t>
+        </is>
+      </c>
+      <c r="Q4" s="81" t="inlineStr">
+        <is>
+          <t>911 Director</t>
+        </is>
+      </c>
+      <c r="R4" s="81" t="inlineStr">
+        <is>
+          <t>Intrado 911 call data, via the Powermetrics reporting module (automated)</t>
+        </is>
+      </c>
+      <c r="S4" s="81" t="inlineStr">
+        <is>
+          <t>Share of 911 calls answered within 15 seconds and within 20 seconds each fiscal year, each compared with its national standard.</t>
+        </is>
+      </c>
+      <c r="T4" s="81" t="inlineStr">
+        <is>
+          <t>Target and benchmark (NENA standard, as set by the 911 center): 95% of calls answered within 15 seconds and 90% within 20 seconds. The center has been at critical staffing since Q2 2021, which has lengthened answer times; results remain above the standard.</t>
+        </is>
+      </c>
       <c r="U4" s="85" t="str">
         <f>IF(B4="","",IF(IF(D4&lt;&gt;"",D4,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E4,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O4="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D4&lt;&gt;"",D4,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E4,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G4)),IF(O4="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O4="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D4&lt;&gt;"",D4,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E4,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -14879,14 +14899,18 @@
         <f>IF(G73="","",IF(ISNUMBER(SEARCH(",",G73)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G73,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G73,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v/>
       </c>
-      <c r="I73" s="108" t="s">
-        <v>550</v>
+      <c r="I73" s="108" t="inlineStr">
+        <is>
+          <t>per 1,000 residents</t>
+        </is>
       </c>
       <c r="J73" s="108">
-        <v>2</v>
-      </c>
-      <c r="K73" s="108" t="s">
-        <v>551</v>
+        <v>0</v>
+      </c>
+      <c r="K73" s="108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="L73" s="108" t="s">
         <v>552</v>
@@ -14907,8 +14931,16 @@
         <v>554</v>
       </c>
       <c r="R73" s="108"/>
-      <c r="S73" s="108"/>
-      <c r="T73" s="108"/>
+      <c r="S73" s="108" t="inlineStr">
+        <is>
+          <t>Part 1 crimes (violent and property crimes) in Durango per 1,000 residents each fiscal year.</t>
+        </is>
+      </c>
+      <c r="T73" s="108" t="inlineStr">
+        <is>
+          <t>Target: at least 10% below the Colorado average. Benchmark: Colorado's Part 1 crime rate, 36.4 per 1,000. Rates use Durango's resident population of about 19,000; they do not include the more than 30,000 tourists, workers and other visitors in Durango each day.</t>
+        </is>
+      </c>
       <c r="U73" s="85" t="str">
         <f>IF(B73="","",IF(IF(D73&lt;&gt;"",D73,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E73,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O73="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D73&lt;&gt;"",D73,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E73,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G73)),IF(O73="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O73="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D73&lt;&gt;"",D73,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E73,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -16275,10 +16307,12 @@
         <v>550</v>
       </c>
       <c r="J96" s="120">
-        <v>2</v>
-      </c>
-      <c r="K96" s="120" t="s">
-        <v>551</v>
+        <v>0</v>
+      </c>
+      <c r="K96" s="120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="L96" s="120" t="s">
         <v>552</v>
@@ -16299,8 +16333,16 @@
         <v>692</v>
       </c>
       <c r="R96" s="120"/>
-      <c r="S96" s="120"/>
-      <c r="T96" s="120"/>
+      <c r="S96" s="120" t="inlineStr">
+        <is>
+          <t>Number of traffic crashes in which someone was injured or killed each fiscal year, including crashes involving pedestrians.</t>
+        </is>
+      </c>
+      <c r="T96" s="120" t="inlineStr">
+        <is>
+          <t>Target: 10% fewer injury and fatal crashes than the previous year. Benchmark: 40.5 crashes, 10% below 2023. The approach follows Vision Zero principles: finding high-risk locations and underlying risk factors, and using proven fixes such as traffic calming, protected crossings and enforcement.</t>
+        </is>
+      </c>
       <c r="U96" s="85" t="str">
         <f>IF(B96="","",IF(IF(D96&lt;&gt;"",D96,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E96,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O96="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D96&lt;&gt;"",D96,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E96,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G96)),IF(O96="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O96="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D96&lt;&gt;"",D96,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E96,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge + sets Program chip</v>
@@ -26214,11 +26256,24 @@
       <c r="B132" s="143" t="s">
         <v>698</v>
       </c>
-      <c r="C132" s="144"/>
+      <c r="C132" s="144" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="D132" s="144"/>
-      <c r="E132" s="144"/>
+      <c r="E132" s="144">
+        <v>21</v>
+      </c>
       <c r="F132" s="144"/>
-      <c r="G132" s="144"/>
+      <c r="G132" s="144">
+        <v>40.5</v>
+      </c>
+      <c r="H132" s="144" t="inlineStr">
+        <is>
+          <t>Unusually low due to COVID restrictions; most people stayed home instead of driving</t>
+        </is>
+      </c>
     </row>
     <row r="133" spans="1:8" s="143" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="143" t="str">
@@ -26419,7 +26474,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="147" spans="1:6" s="108" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" s="108" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="108" t="str">
         <f t="shared" si="2"/>
         <v>PD</v>
@@ -26427,6 +26482,23 @@
       <c r="B147" s="108" t="s">
         <v>657</v>
       </c>
+      <c r="C147" s="108" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D147" s="108"/>
+      <c r="E147" s="108">
+        <v>56</v>
+      </c>
+      <c r="F147" s="108">
+        <f>ROUND(G147*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G147" s="108">
+        <v>36.4</v>
+      </c>
+      <c r="H147" s="108"/>
     </row>
     <row r="148" spans="1:6" s="108" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="108" t="str">
@@ -26635,7 +26707,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="171" spans="1:2" s="81" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" s="81" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="81" t="str">
         <f t="shared" si="2"/>
         <v>911</v>
@@ -26643,6 +26715,26 @@
       <c r="B171" s="81" t="s">
         <v>556</v>
       </c>
+      <c r="C171" s="81" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D171" s="81" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E171" s="81">
+        <v>99</v>
+      </c>
+      <c r="F171" s="81">
+        <v>95</v>
+      </c>
+      <c r="G171" s="81">
+        <v>95</v>
+      </c>
+      <c r="H171" s="81"/>
     </row>
     <row r="172" spans="1:2" s="81" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="81" t="str">
@@ -29273,192 +29365,624 @@
       <c r="H300" s="147"/>
     </row>
     <row r="301" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B301" s="149"/>
-      <c r="C301" s="145"/>
-      <c r="D301" s="146"/>
-      <c r="E301" s="146"/>
-      <c r="F301" s="146"/>
-      <c r="G301" s="146"/>
+      <c r="A301" s="116" t="str">
+        <f>LEFT(B301, FIND("-", B301) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B301" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C301" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D301" s="146" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E301" s="146">
+        <v>98</v>
+      </c>
+      <c r="F301" s="146">
+        <v>95</v>
+      </c>
+      <c r="G301" s="146">
+        <v>95</v>
+      </c>
       <c r="H301" s="147"/>
     </row>
     <row r="302" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B302" s="149"/>
-      <c r="C302" s="145"/>
-      <c r="D302" s="146"/>
-      <c r="E302" s="146"/>
-      <c r="F302" s="146"/>
-      <c r="G302" s="146"/>
+      <c r="A302" s="116" t="str">
+        <f>LEFT(B302, FIND("-", B302) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B302" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C302" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D302" s="146" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E302" s="146">
+        <v>97</v>
+      </c>
+      <c r="F302" s="146">
+        <v>95</v>
+      </c>
+      <c r="G302" s="146">
+        <v>95</v>
+      </c>
       <c r="H302" s="147"/>
     </row>
     <row r="303" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B303" s="149"/>
-      <c r="C303" s="145"/>
-      <c r="D303" s="146"/>
-      <c r="E303" s="146"/>
-      <c r="F303" s="146"/>
-      <c r="G303" s="146"/>
+      <c r="A303" s="116" t="str">
+        <f>LEFT(B303, FIND("-", B303) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B303" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C303" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D303" s="146" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E303" s="146">
+        <v>96</v>
+      </c>
+      <c r="F303" s="146">
+        <v>95</v>
+      </c>
+      <c r="G303" s="146">
+        <v>95</v>
+      </c>
       <c r="H303" s="147"/>
     </row>
     <row r="304" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B304" s="149"/>
-      <c r="C304" s="145"/>
-      <c r="D304" s="146"/>
-      <c r="E304" s="146"/>
-      <c r="F304" s="146"/>
-      <c r="G304" s="146"/>
+      <c r="A304" s="116" t="str">
+        <f>LEFT(B304, FIND("-", B304) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B304" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C304" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D304" s="146" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E304" s="146">
+        <v>97</v>
+      </c>
+      <c r="F304" s="146">
+        <v>95</v>
+      </c>
+      <c r="G304" s="146">
+        <v>95</v>
+      </c>
       <c r="H304" s="147"/>
     </row>
-    <row r="305" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B305" s="149"/>
-      <c r="C305" s="145"/>
-      <c r="D305" s="146"/>
-      <c r="E305" s="146"/>
-      <c r="F305" s="146"/>
-      <c r="G305" s="146"/>
+    <row r="305" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="116" t="str">
+        <f>LEFT(B305, FIND("-", B305) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B305" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C305" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D305" s="146" t="inlineStr">
+        <is>
+          <t>Within 15 seconds</t>
+        </is>
+      </c>
+      <c r="E305" s="146">
+        <v>97</v>
+      </c>
+      <c r="F305" s="146">
+        <v>95</v>
+      </c>
+      <c r="G305" s="146">
+        <v>95</v>
+      </c>
       <c r="H305" s="147"/>
     </row>
-    <row r="306" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B306" s="149"/>
-      <c r="C306" s="145"/>
-      <c r="D306" s="146"/>
-      <c r="E306" s="146"/>
-      <c r="F306" s="146"/>
-      <c r="G306" s="146"/>
+    <row r="306" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="116" t="str">
+        <f>LEFT(B306, FIND("-", B306) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B306" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C306" s="145" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D306" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E306" s="146">
+        <v>100</v>
+      </c>
+      <c r="F306" s="146">
+        <v>90</v>
+      </c>
+      <c r="G306" s="146">
+        <v>90</v>
+      </c>
       <c r="H306" s="147"/>
     </row>
-    <row r="307" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B307" s="149"/>
-      <c r="C307" s="145"/>
-      <c r="D307" s="146"/>
-      <c r="E307" s="146"/>
-      <c r="F307" s="146"/>
-      <c r="G307" s="146"/>
+    <row r="307" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="116" t="str">
+        <f>LEFT(B307, FIND("-", B307) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B307" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C307" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D307" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E307" s="146">
+        <v>99</v>
+      </c>
+      <c r="F307" s="146">
+        <v>90</v>
+      </c>
+      <c r="G307" s="146">
+        <v>90</v>
+      </c>
       <c r="H307" s="147"/>
     </row>
-    <row r="308" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="149"/>
-      <c r="C308" s="145"/>
-      <c r="D308" s="146"/>
-      <c r="E308" s="146"/>
-      <c r="F308" s="146"/>
-      <c r="G308" s="146"/>
+    <row r="308" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="116" t="str">
+        <f>LEFT(B308, FIND("-", B308) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B308" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C308" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D308" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E308" s="146">
+        <v>98</v>
+      </c>
+      <c r="F308" s="146">
+        <v>90</v>
+      </c>
+      <c r="G308" s="146">
+        <v>90</v>
+      </c>
       <c r="H308" s="147"/>
     </row>
-    <row r="309" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B309" s="149"/>
-      <c r="C309" s="145"/>
-      <c r="D309" s="146"/>
-      <c r="E309" s="146"/>
-      <c r="F309" s="146"/>
-      <c r="G309" s="146"/>
+    <row r="309" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="116" t="str">
+        <f>LEFT(B309, FIND("-", B309) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B309" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C309" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D309" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E309" s="146">
+        <v>98</v>
+      </c>
+      <c r="F309" s="146">
+        <v>90</v>
+      </c>
+      <c r="G309" s="146">
+        <v>90</v>
+      </c>
       <c r="H309" s="147"/>
     </row>
-    <row r="310" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B310" s="149"/>
-      <c r="C310" s="145"/>
-      <c r="D310" s="146"/>
-      <c r="E310" s="146"/>
-      <c r="F310" s="146"/>
-      <c r="G310" s="146"/>
+    <row r="310" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="116" t="str">
+        <f>LEFT(B310, FIND("-", B310) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B310" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C310" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D310" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E310" s="146">
+        <v>99</v>
+      </c>
+      <c r="F310" s="146">
+        <v>90</v>
+      </c>
+      <c r="G310" s="146">
+        <v>90</v>
+      </c>
       <c r="H310" s="147"/>
     </row>
-    <row r="311" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B311" s="149"/>
-      <c r="C311" s="145"/>
-      <c r="D311" s="146"/>
-      <c r="E311" s="146"/>
-      <c r="F311" s="146"/>
-      <c r="G311" s="146"/>
+    <row r="311" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="116" t="str">
+        <f>LEFT(B311, FIND("-", B311) - 1)</f>
+        <v>911</v>
+      </c>
+      <c r="B311" s="116" t="inlineStr">
+        <is>
+          <t>911-DISPATCHTIME</t>
+        </is>
+      </c>
+      <c r="C311" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D311" s="146" t="inlineStr">
+        <is>
+          <t>Within 20 seconds</t>
+        </is>
+      </c>
+      <c r="E311" s="146">
+        <v>98</v>
+      </c>
+      <c r="F311" s="146">
+        <v>90</v>
+      </c>
+      <c r="G311" s="146">
+        <v>90</v>
+      </c>
       <c r="H311" s="147"/>
     </row>
-    <row r="312" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B312" s="149"/>
-      <c r="C312" s="145"/>
+    <row r="312" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="116" t="str">
+        <f>LEFT(B312, FIND("-", B312) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B312" s="116" t="inlineStr">
+        <is>
+          <t>TRAN-CRASHDATA</t>
+        </is>
+      </c>
+      <c r="C312" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D312" s="146"/>
-      <c r="E312" s="146"/>
-      <c r="F312" s="146"/>
-      <c r="G312" s="146"/>
+      <c r="E312" s="146">
+        <v>54</v>
+      </c>
+      <c r="F312" s="146">
+        <f>ROUND(E132*0.9,0)</f>
+        <v>19</v>
+      </c>
+      <c r="G312" s="146">
+        <v>40.5</v>
+      </c>
       <c r="H312" s="147"/>
     </row>
-    <row r="313" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B313" s="149"/>
-      <c r="C313" s="145"/>
+    <row r="313" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="116" t="str">
+        <f>LEFT(B313, FIND("-", B313) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B313" s="116" t="inlineStr">
+        <is>
+          <t>TRAN-CRASHDATA</t>
+        </is>
+      </c>
+      <c r="C313" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D313" s="146"/>
-      <c r="E313" s="146"/>
-      <c r="F313" s="146"/>
-      <c r="G313" s="146"/>
+      <c r="E313" s="146">
+        <v>42</v>
+      </c>
+      <c r="F313" s="146">
+        <f>ROUND(E312*0.9,0)</f>
+        <v>49</v>
+      </c>
+      <c r="G313" s="146">
+        <v>40.5</v>
+      </c>
       <c r="H313" s="147"/>
     </row>
-    <row r="314" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B314" s="149"/>
-      <c r="C314" s="145"/>
+    <row r="314" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="116" t="str">
+        <f>LEFT(B314, FIND("-", B314) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B314" s="116" t="inlineStr">
+        <is>
+          <t>TRAN-CRASHDATA</t>
+        </is>
+      </c>
+      <c r="C314" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D314" s="146"/>
-      <c r="E314" s="146"/>
-      <c r="F314" s="146"/>
-      <c r="G314" s="146"/>
+      <c r="E314" s="146">
+        <v>45</v>
+      </c>
+      <c r="F314" s="146">
+        <f>ROUND(E313*0.9,0)</f>
+        <v>38</v>
+      </c>
+      <c r="G314" s="146">
+        <v>40.5</v>
+      </c>
       <c r="H314" s="147"/>
     </row>
-    <row r="315" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B315" s="149"/>
-      <c r="C315" s="145"/>
+    <row r="315" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="116" t="str">
+        <f>LEFT(B315, FIND("-", B315) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B315" s="116" t="inlineStr">
+        <is>
+          <t>TRAN-CRASHDATA</t>
+        </is>
+      </c>
+      <c r="C315" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D315" s="146"/>
-      <c r="E315" s="146"/>
-      <c r="F315" s="146"/>
-      <c r="G315" s="146"/>
+      <c r="E315" s="146">
+        <v>44</v>
+      </c>
+      <c r="F315" s="146">
+        <f>ROUND(E314*0.9,0)</f>
+        <v>41</v>
+      </c>
+      <c r="G315" s="146">
+        <v>40.5</v>
+      </c>
       <c r="H315" s="147"/>
     </row>
-    <row r="316" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B316" s="149"/>
-      <c r="C316" s="145"/>
+    <row r="316" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="116" t="str">
+        <f>LEFT(B316, FIND("-", B316) - 1)</f>
+        <v>TRAN</v>
+      </c>
+      <c r="B316" s="116" t="inlineStr">
+        <is>
+          <t>TRAN-CRASHDATA</t>
+        </is>
+      </c>
+      <c r="C316" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D316" s="146"/>
-      <c r="E316" s="146"/>
-      <c r="F316" s="146"/>
-      <c r="G316" s="146"/>
+      <c r="E316" s="146">
+        <v>51</v>
+      </c>
+      <c r="F316" s="146">
+        <f>ROUND(E315*0.9,0)</f>
+        <v>40</v>
+      </c>
+      <c r="G316" s="146">
+        <v>40.5</v>
+      </c>
       <c r="H316" s="147"/>
     </row>
-    <row r="317" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B317" s="149"/>
-      <c r="C317" s="145"/>
+    <row r="317" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="116" t="str">
+        <f>LEFT(B317, FIND("-", B317) - 1)</f>
+        <v>PD</v>
+      </c>
+      <c r="B317" s="116" t="inlineStr">
+        <is>
+          <t>PD-VIOLENTPROPCRIME</t>
+        </is>
+      </c>
+      <c r="C317" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D317" s="146"/>
-      <c r="E317" s="146"/>
-      <c r="F317" s="146"/>
-      <c r="G317" s="146"/>
+      <c r="E317" s="146">
+        <v>45</v>
+      </c>
+      <c r="F317" s="146">
+        <f>ROUND(G317*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G317" s="146">
+        <v>36.4</v>
+      </c>
       <c r="H317" s="147"/>
     </row>
-    <row r="318" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B318" s="149"/>
-      <c r="C318" s="145"/>
+    <row r="318" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="116" t="str">
+        <f>LEFT(B318, FIND("-", B318) - 1)</f>
+        <v>PD</v>
+      </c>
+      <c r="B318" s="116" t="inlineStr">
+        <is>
+          <t>PD-VIOLENTPROPCRIME</t>
+        </is>
+      </c>
+      <c r="C318" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D318" s="146"/>
-      <c r="E318" s="146"/>
-      <c r="F318" s="146"/>
-      <c r="G318" s="146"/>
+      <c r="E318" s="146">
+        <v>41</v>
+      </c>
+      <c r="F318" s="146">
+        <f>ROUND(G318*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G318" s="146">
+        <v>36.4</v>
+      </c>
       <c r="H318" s="147"/>
     </row>
-    <row r="319" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B319" s="149"/>
-      <c r="C319" s="145"/>
+    <row r="319" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="116" t="str">
+        <f>LEFT(B319, FIND("-", B319) - 1)</f>
+        <v>PD</v>
+      </c>
+      <c r="B319" s="116" t="inlineStr">
+        <is>
+          <t>PD-VIOLENTPROPCRIME</t>
+        </is>
+      </c>
+      <c r="C319" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D319" s="146"/>
-      <c r="E319" s="146"/>
-      <c r="F319" s="146"/>
-      <c r="G319" s="146"/>
+      <c r="E319" s="146">
+        <v>41</v>
+      </c>
+      <c r="F319" s="146">
+        <f>ROUND(G319*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G319" s="146">
+        <v>36.4</v>
+      </c>
       <c r="H319" s="147"/>
     </row>
-    <row r="320" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B320" s="149"/>
-      <c r="C320" s="145"/>
+    <row r="320" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="116" t="str">
+        <f>LEFT(B320, FIND("-", B320) - 1)</f>
+        <v>PD</v>
+      </c>
+      <c r="B320" s="116" t="inlineStr">
+        <is>
+          <t>PD-VIOLENTPROPCRIME</t>
+        </is>
+      </c>
+      <c r="C320" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D320" s="146"/>
-      <c r="E320" s="146"/>
-      <c r="F320" s="146"/>
-      <c r="G320" s="146"/>
+      <c r="E320" s="146">
+        <v>53</v>
+      </c>
+      <c r="F320" s="146">
+        <f>ROUND(G320*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G320" s="146">
+        <v>36.4</v>
+      </c>
       <c r="H320" s="147"/>
     </row>
-    <row r="321" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B321" s="149"/>
-      <c r="C321" s="145"/>
+    <row r="321" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="116" t="str">
+        <f>LEFT(B321, FIND("-", B321) - 1)</f>
+        <v>PD</v>
+      </c>
+      <c r="B321" s="116" t="inlineStr">
+        <is>
+          <t>PD-VIOLENTPROPCRIME</t>
+        </is>
+      </c>
+      <c r="C321" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D321" s="146"/>
-      <c r="E321" s="146"/>
-      <c r="F321" s="146"/>
-      <c r="G321" s="146"/>
+      <c r="E321" s="146">
+        <v>44</v>
+      </c>
+      <c r="F321" s="146">
+        <f>ROUND(G321*0.9,1)</f>
+        <v>32.8</v>
+      </c>
+      <c r="G321" s="146">
+        <v>36.4</v>
+      </c>
       <c r="H321" s="147"/>
     </row>
     <row r="322" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -39560,27 +39560,23 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="149" t="s">
-        <v>681</v>
-      </c>
+      <c r="A27" s="149"/>
       <c r="B27" s="85" t="str">
         <f>IF(A27="","",IFERROR(INDEX('Dashboard Items'!$C$2:$C$495,MATCH(A27,'Dashboard Items'!$A$2:$A$495,0)),"ID not found"))</f>
-        <v>Community Development &amp; Planning</v>
+        <v/>
       </c>
       <c r="C27" s="85" t="str">
         <f>IF(A27="","",IFERROR(INDEX('Dashboard Items'!$E$2:$E$495,MATCH(A27,'Dashboard Items'!$A$2:$A$495,0)),"ID not found"))</f>
-        <v>Community Growth and Economic Vitality</v>
-      </c>
-      <c r="D27" s="149" t="s">
-        <v>931</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D27" s="149"/>
       <c r="E27" s="85" t="str">
         <f>IF(D27="","",IFERROR(INDEX('Dashboard Items'!$C$2:$C$495,MATCH(D27,'Dashboard Items'!$A$2:$A$495,0)),"ID not found"))</f>
-        <v>6.1 Employee Growth and Retention</v>
+        <v/>
       </c>
       <c r="F27" s="85" t="str">
         <f>IF(D27="","",IFERROR(INDEX('Dashboard Items'!$F$2:$F$495,MATCH(D27,'Dashboard Items'!$A$2:$A$495,0)),"ID not found"))</f>
-        <v>Strategic Workforce Development</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -11431,18 +11431,44 @@
         <f>IF(G9="","",IF(ISNUMBER(SEARCH(",",G9)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G9,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G9,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
+      <c r="I9" s="87" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="J9" s="87">
+        <v>0</v>
+      </c>
+      <c r="K9" s="87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="87" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M9" s="87"/>
       <c r="N9" s="87"/>
       <c r="O9" s="87"/>
-      <c r="P9" s="87"/>
+      <c r="P9" s="87" t="inlineStr">
+        <is>
+          <t>Every Quarter</t>
+        </is>
+      </c>
       <c r="Q9" s="87"/>
       <c r="R9" s="87"/>
-      <c r="S9" s="87"/>
-      <c r="T9" s="87"/>
+      <c r="S9" s="87" t="inlineStr">
+        <is>
+          <t>Share of regular City Council meeting agendas posted at least 48 hours before the meeting, each quarter.</t>
+        </is>
+      </c>
+      <c r="T9" s="87" t="inlineStr">
+        <is>
+          <t>Target: more than 90% posted within 48 hours. Results swing from quarter to quarter because the number of meetings varies.</t>
+        </is>
+      </c>
       <c r="U9" s="85" t="str">
         <f>IF(B9="","",IF(IF(D9&lt;&gt;"",D9,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E9,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O9="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D9&lt;&gt;"",D9,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E9,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G9)),IF(O9="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O9="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D9&lt;&gt;"",D9,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E9,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge + sets Program chip</v>
@@ -11564,18 +11590,44 @@
         <f>IF(G12="","",IF(ISNUMBER(SEARCH(",",G12)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G12,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G12,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v>Key Service: City Clerk &amp; Records Management</v>
       </c>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="87"/>
+      <c r="I12" s="87" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="J12" s="87">
+        <v>0</v>
+      </c>
+      <c r="K12" s="87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" s="87" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M12" s="87"/>
       <c r="N12" s="87"/>
       <c r="O12" s="87"/>
-      <c r="P12" s="87"/>
+      <c r="P12" s="87" t="inlineStr">
+        <is>
+          <t>Every Quarter</t>
+        </is>
+      </c>
       <c r="Q12" s="87"/>
       <c r="R12" s="87"/>
-      <c r="S12" s="87"/>
-      <c r="T12" s="87"/>
+      <c r="S12" s="87" t="inlineStr">
+        <is>
+          <t>Share of public records requests closed within 24 hours, each quarter.</t>
+        </is>
+      </c>
+      <c r="T12" s="87" t="inlineStr">
+        <is>
+          <t>Target: 90% closed within 24 hours. The legal deadline is 3 days. Some requests are delayed while waiting on the requester, especially for payment.</t>
+        </is>
+      </c>
       <c r="U12" s="85" t="str">
         <f>IF(B12="","",IF(IF(D12&lt;&gt;"",D12,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E12,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O12="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D12&lt;&gt;"",D12,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E12,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G12)),IF(O12="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O12="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D12&lt;&gt;"",D12,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E12,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge + sets Program chip</v>
@@ -12157,18 +12209,44 @@
         <f>IF(G25="","",IF(ISNUMBER(SEARCH(",",G25)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G25,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G25,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v>Program: Recruitment &amp; Retention</v>
       </c>
-      <c r="I25" s="81"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="81"/>
-      <c r="L25" s="81"/>
+      <c r="I25" s="81" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="J25" s="81">
+        <v>2</v>
+      </c>
+      <c r="K25" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" s="81" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M25" s="81"/>
       <c r="N25" s="81"/>
       <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
+      <c r="P25" s="81" t="inlineStr">
+        <is>
+          <t>Every year</t>
+        </is>
+      </c>
       <c r="Q25" s="81"/>
       <c r="R25" s="81"/>
-      <c r="S25" s="81"/>
-      <c r="T25" s="81"/>
+      <c r="S25" s="81" t="inlineStr">
+        <is>
+          <t>Internal promotion rate for full-time City positions each fiscal year.</t>
+        </is>
+      </c>
+      <c r="T25" s="81" t="inlineStr">
+        <is>
+          <t>Target: 10%. Benchmark: 6%, SHRM's average internal promotion rate.</t>
+        </is>
+      </c>
       <c r="U25" s="85" t="str">
         <f>IF(B25="","",IF(IF(D25&lt;&gt;"",D25,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E25,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O25="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D25&lt;&gt;"",D25,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E25,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G25)),IF(O25="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O25="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D25&lt;&gt;"",D25,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E25,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -12646,18 +12724,44 @@
         <f>IF(G36="","",IF(ISNUMBER(SEARCH(",",G36)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G36,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G36,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v>Program: Recruitment &amp; Retention</v>
       </c>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
+      <c r="I36" s="81" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="J36" s="81">
+        <v>2</v>
+      </c>
+      <c r="K36" s="81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" s="81" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M36" s="81"/>
       <c r="N36" s="81"/>
       <c r="O36" s="81"/>
-      <c r="P36" s="81"/>
+      <c r="P36" s="81" t="inlineStr">
+        <is>
+          <t>Every year</t>
+        </is>
+      </c>
       <c r="Q36" s="81"/>
       <c r="R36" s="81"/>
-      <c r="S36" s="81"/>
-      <c r="T36" s="81"/>
+      <c r="S36" s="81" t="inlineStr">
+        <is>
+          <t>Cumulative turnover rate for City employees each fiscal year. Lower is better.</t>
+        </is>
+      </c>
+      <c r="T36" s="81" t="inlineStr">
+        <is>
+          <t>Target: 20%. Benchmark: the Colorado average (18% in 2021, 20% in 2022, 18% in 2023); from 2024, SHRM's 20% average for government, as the Colorado figure is not available. Shown as one total; a voluntary/involuntary split is not available yet.</t>
+        </is>
+      </c>
       <c r="U36" s="85" t="str">
         <f>IF(B36="","",IF(IF(D36&lt;&gt;"",D36,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E36,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O36="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D36&lt;&gt;"",D36,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E36,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G36)),IF(O36="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O36="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D36&lt;&gt;"",D36,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E36,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -15244,7 +15348,7 @@
         <v>550</v>
       </c>
       <c r="J79" s="116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K79" s="116" t="s">
         <v>551</v>
@@ -15268,8 +15372,16 @@
         <v>668</v>
       </c>
       <c r="R79" s="116"/>
-      <c r="S79" s="116"/>
-      <c r="T79" s="116"/>
+      <c r="S79" s="116" t="inlineStr">
+        <is>
+          <t>Community events supported with City services such as production, facilities and equipment, each fiscal year.</t>
+        </is>
+      </c>
+      <c r="T79" s="116" t="inlineStr">
+        <is>
+          <t>Target: 250 events, set from Customer Service portal and self-service capacity. Growth is limited by the calendar and the number of facilities available.</t>
+        </is>
+      </c>
       <c r="U79" s="85" t="str">
         <f>IF(B79="","",IF(IF(D79&lt;&gt;"",D79,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E79,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O79="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D79&lt;&gt;"",D79,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E79,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G79)),IF(O79="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O79="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D79&lt;&gt;"",D79,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E79,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -15622,7 +15734,7 @@
         <v>550</v>
       </c>
       <c r="J85" s="116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K85" s="116" t="s">
         <v>551</v>
@@ -15646,8 +15758,16 @@
         <v>668</v>
       </c>
       <c r="R85" s="116"/>
-      <c r="S85" s="116"/>
-      <c r="T85" s="116"/>
+      <c r="S85" s="116" t="inlineStr">
+        <is>
+          <t>Community event permits issued each fiscal year.</t>
+        </is>
+      </c>
+      <c r="T85" s="116" t="inlineStr">
+        <is>
+          <t>Target: 240 permits, set from Customer Service portal and self-service capacity. Growth is limited by the calendar and the number of facilities available. Counts community event permits only; activity, park and banner permits are not included yet.</t>
+        </is>
+      </c>
       <c r="U85" s="85" t="str">
         <f>IF(B85="","",IF(IF(D85&lt;&gt;"",D85,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E85,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O85="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D85&lt;&gt;"",D85,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E85,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G85)),IF(O85="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O85="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D85&lt;&gt;"",D85,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E85,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Sets Program status chip</v>
@@ -23696,13 +23816,20 @@
       <c r="B6" s="127" t="s">
         <v>569</v>
       </c>
-      <c r="C6" s="128" t="s">
-        <v>777</v>
+      <c r="C6" s="128" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
       </c>
       <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
+      <c r="E6" s="128">
+        <v>88</v>
+      </c>
+      <c r="F6" s="128">
+        <v>90</v>
+      </c>
       <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
     </row>
     <row r="7" spans="1:8" s="127" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="127" t="str">
@@ -23712,13 +23839,20 @@
       <c r="B7" s="127" t="s">
         <v>565</v>
       </c>
-      <c r="C7" s="128" t="s">
-        <v>777</v>
+      <c r="C7" s="128" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
       </c>
       <c r="D7" s="128"/>
-      <c r="E7" s="128"/>
-      <c r="F7" s="128"/>
+      <c r="E7" s="128">
+        <v>95</v>
+      </c>
+      <c r="F7" s="128">
+        <v>90</v>
+      </c>
       <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
     </row>
     <row r="8" spans="1:8" s="127" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="127" t="str">
@@ -23886,7 +24020,7 @@
       <c r="F16" s="129"/>
       <c r="G16" s="129"/>
     </row>
-    <row r="17" spans="1:7" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="94" t="str">
         <f t="shared" si="0"/>
         <v>HR</v>
@@ -23894,11 +24028,22 @@
       <c r="B17" s="94" t="s">
         <v>605</v>
       </c>
-      <c r="C17" s="129"/>
+      <c r="C17" s="129" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
+      <c r="E17" s="129">
+        <v>20.34</v>
+      </c>
+      <c r="F17" s="129">
+        <v>20</v>
+      </c>
+      <c r="G17" s="129">
+        <v>18</v>
+      </c>
+      <c r="H17" s="129"/>
     </row>
     <row r="18" spans="1:7" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="94" t="str">
@@ -24026,7 +24171,7 @@
       <c r="F26" s="129"/>
       <c r="G26" s="129"/>
     </row>
-    <row r="27" spans="1:7" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="94" t="str">
         <f t="shared" si="0"/>
         <v>HR</v>
@@ -24034,11 +24179,22 @@
       <c r="B27" s="94" t="s">
         <v>593</v>
       </c>
-      <c r="C27" s="129"/>
+      <c r="C27" s="129" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
+      <c r="E27" s="129">
+        <v>49.3</v>
+      </c>
+      <c r="F27" s="129">
+        <v>10</v>
+      </c>
+      <c r="G27" s="129">
+        <v>6</v>
+      </c>
+      <c r="H27" s="129"/>
     </row>
     <row r="28" spans="1:7" s="94" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="94" t="str">
@@ -29985,246 +30141,692 @@
       </c>
       <c r="H321" s="147"/>
     </row>
-    <row r="322" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B322" s="149"/>
-      <c r="C322" s="145"/>
+    <row r="322" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="116" t="str">
+        <f>LEFT(B322, FIND("-", B322) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B322" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-AGENDAPOST</t>
+        </is>
+      </c>
+      <c r="C322" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
       <c r="D322" s="146"/>
-      <c r="E322" s="146"/>
-      <c r="F322" s="146"/>
+      <c r="E322" s="146">
+        <v>95</v>
+      </c>
+      <c r="F322" s="146">
+        <v>90</v>
+      </c>
       <c r="G322" s="146"/>
       <c r="H322" s="147"/>
     </row>
-    <row r="323" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B323" s="149"/>
-      <c r="C323" s="145"/>
+    <row r="323" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="116" t="str">
+        <f>LEFT(B323, FIND("-", B323) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B323" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-AGENDAPOST</t>
+        </is>
+      </c>
+      <c r="C323" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
       <c r="D323" s="146"/>
-      <c r="E323" s="146"/>
-      <c r="F323" s="146"/>
+      <c r="E323" s="146">
+        <v>95</v>
+      </c>
+      <c r="F323" s="146">
+        <v>90</v>
+      </c>
       <c r="G323" s="146"/>
       <c r="H323" s="147"/>
     </row>
-    <row r="324" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B324" s="149"/>
-      <c r="C324" s="145"/>
+    <row r="324" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="116" t="str">
+        <f>LEFT(B324, FIND("-", B324) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B324" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-AGENDAPOST</t>
+        </is>
+      </c>
+      <c r="C324" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
       <c r="D324" s="146"/>
-      <c r="E324" s="146"/>
-      <c r="F324" s="146"/>
+      <c r="E324" s="146">
+        <v>97</v>
+      </c>
+      <c r="F324" s="146">
+        <v>90</v>
+      </c>
       <c r="G324" s="146"/>
       <c r="H324" s="147"/>
     </row>
-    <row r="325" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B325" s="149"/>
-      <c r="C325" s="145"/>
+    <row r="325" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="116" t="str">
+        <f>LEFT(B325, FIND("-", B325) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B325" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-AGENDAPOST</t>
+        </is>
+      </c>
+      <c r="C325" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
       <c r="D325" s="146"/>
-      <c r="E325" s="146"/>
-      <c r="F325" s="146"/>
+      <c r="E325" s="146">
+        <v>97</v>
+      </c>
+      <c r="F325" s="146">
+        <v>90</v>
+      </c>
       <c r="G325" s="146"/>
       <c r="H325" s="147"/>
     </row>
-    <row r="326" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B326" s="149"/>
-      <c r="C326" s="145"/>
+    <row r="326" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="116" t="str">
+        <f>LEFT(B326, FIND("-", B326) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B326" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-AGENDAPOST</t>
+        </is>
+      </c>
+      <c r="C326" s="145" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
       <c r="D326" s="146"/>
-      <c r="E326" s="146"/>
-      <c r="F326" s="146"/>
+      <c r="E326" s="146">
+        <v>95</v>
+      </c>
+      <c r="F326" s="146">
+        <v>90</v>
+      </c>
       <c r="G326" s="146"/>
       <c r="H326" s="147"/>
     </row>
-    <row r="327" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B327" s="149"/>
-      <c r="C327" s="145"/>
+    <row r="327" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="116" t="str">
+        <f>LEFT(B327, FIND("-", B327) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B327" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-CORARESPRATE</t>
+        </is>
+      </c>
+      <c r="C327" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
       <c r="D327" s="146"/>
-      <c r="E327" s="146"/>
-      <c r="F327" s="146"/>
+      <c r="E327" s="146">
+        <v>87</v>
+      </c>
+      <c r="F327" s="146">
+        <v>90</v>
+      </c>
       <c r="G327" s="146"/>
       <c r="H327" s="147"/>
     </row>
-    <row r="328" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B328" s="149"/>
-      <c r="C328" s="145"/>
+    <row r="328" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="116" t="str">
+        <f>LEFT(B328, FIND("-", B328) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B328" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-CORARESPRATE</t>
+        </is>
+      </c>
+      <c r="C328" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
       <c r="D328" s="146"/>
-      <c r="E328" s="146"/>
-      <c r="F328" s="146"/>
+      <c r="E328" s="146">
+        <v>87</v>
+      </c>
+      <c r="F328" s="146">
+        <v>90</v>
+      </c>
       <c r="G328" s="146"/>
       <c r="H328" s="147"/>
     </row>
-    <row r="329" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B329" s="149"/>
-      <c r="C329" s="145"/>
+    <row r="329" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="116" t="str">
+        <f>LEFT(B329, FIND("-", B329) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B329" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-CORARESPRATE</t>
+        </is>
+      </c>
+      <c r="C329" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
       <c r="D329" s="146"/>
-      <c r="E329" s="146"/>
-      <c r="F329" s="146"/>
+      <c r="E329" s="146">
+        <v>88</v>
+      </c>
+      <c r="F329" s="146">
+        <v>90</v>
+      </c>
       <c r="G329" s="146"/>
       <c r="H329" s="147"/>
     </row>
-    <row r="330" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B330" s="149"/>
-      <c r="C330" s="145"/>
+    <row r="330" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="116" t="str">
+        <f>LEFT(B330, FIND("-", B330) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B330" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-CORARESPRATE</t>
+        </is>
+      </c>
+      <c r="C330" s="145" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
       <c r="D330" s="146"/>
-      <c r="E330" s="146"/>
-      <c r="F330" s="146"/>
+      <c r="E330" s="146">
+        <v>88</v>
+      </c>
+      <c r="F330" s="146">
+        <v>90</v>
+      </c>
       <c r="G330" s="146"/>
       <c r="H330" s="147"/>
     </row>
-    <row r="331" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B331" s="149"/>
-      <c r="C331" s="145"/>
+    <row r="331" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="116" t="str">
+        <f>LEFT(B331, FIND("-", B331) - 1)</f>
+        <v>CLERK</v>
+      </c>
+      <c r="B331" s="116" t="inlineStr">
+        <is>
+          <t>CLERK-CORARESPRATE</t>
+        </is>
+      </c>
+      <c r="C331" s="145" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
       <c r="D331" s="146"/>
-      <c r="E331" s="146"/>
-      <c r="F331" s="146"/>
+      <c r="E331" s="146">
+        <v>88</v>
+      </c>
+      <c r="F331" s="146">
+        <v>90</v>
+      </c>
       <c r="G331" s="146"/>
       <c r="H331" s="147"/>
     </row>
-    <row r="332" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B332" s="149"/>
-      <c r="C332" s="145"/>
+    <row r="332" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="116" t="str">
+        <f>LEFT(B332, FIND("-", B332) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B332" s="116" t="inlineStr">
+        <is>
+          <t>HR-TURNRATE</t>
+        </is>
+      </c>
+      <c r="C332" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D332" s="146"/>
-      <c r="E332" s="146"/>
-      <c r="F332" s="146"/>
-      <c r="G332" s="146"/>
+      <c r="E332" s="146">
+        <v>20.3</v>
+      </c>
+      <c r="F332" s="146">
+        <v>20</v>
+      </c>
+      <c r="G332" s="146">
+        <v>20</v>
+      </c>
       <c r="H332" s="147"/>
     </row>
-    <row r="333" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B333" s="149"/>
-      <c r="C333" s="145"/>
+    <row r="333" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="116" t="str">
+        <f>LEFT(B333, FIND("-", B333) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B333" s="116" t="inlineStr">
+        <is>
+          <t>HR-TURNRATE</t>
+        </is>
+      </c>
+      <c r="C333" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D333" s="146"/>
-      <c r="E333" s="146"/>
-      <c r="F333" s="146"/>
-      <c r="G333" s="146"/>
+      <c r="E333" s="146">
+        <v>21.18</v>
+      </c>
+      <c r="F333" s="146">
+        <v>20</v>
+      </c>
+      <c r="G333" s="146">
+        <v>18</v>
+      </c>
       <c r="H333" s="147"/>
     </row>
-    <row r="334" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B334" s="149"/>
-      <c r="C334" s="145"/>
+    <row r="334" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="116" t="str">
+        <f>LEFT(B334, FIND("-", B334) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B334" s="116" t="inlineStr">
+        <is>
+          <t>HR-TURNRATE</t>
+        </is>
+      </c>
+      <c r="C334" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D334" s="146"/>
-      <c r="E334" s="146"/>
-      <c r="F334" s="146"/>
-      <c r="G334" s="146"/>
+      <c r="E334" s="146">
+        <v>19.85</v>
+      </c>
+      <c r="F334" s="146">
+        <v>20</v>
+      </c>
+      <c r="G334" s="146">
+        <v>20</v>
+      </c>
       <c r="H334" s="147"/>
     </row>
-    <row r="335" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B335" s="149"/>
-      <c r="C335" s="145"/>
+    <row r="335" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="116" t="str">
+        <f>LEFT(B335, FIND("-", B335) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B335" s="116" t="inlineStr">
+        <is>
+          <t>HR-TURNRATE</t>
+        </is>
+      </c>
+      <c r="C335" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D335" s="146"/>
-      <c r="E335" s="146"/>
-      <c r="F335" s="146"/>
-      <c r="G335" s="146"/>
+      <c r="E335" s="146">
+        <v>16.6</v>
+      </c>
+      <c r="F335" s="146">
+        <v>20</v>
+      </c>
+      <c r="G335" s="146">
+        <v>20</v>
+      </c>
       <c r="H335" s="147"/>
     </row>
-    <row r="336" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B336" s="149"/>
-      <c r="C336" s="145"/>
+    <row r="336" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="116" t="str">
+        <f>LEFT(B336, FIND("-", B336) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B336" s="116" t="inlineStr">
+        <is>
+          <t>HR-INTPROMO</t>
+        </is>
+      </c>
+      <c r="C336" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D336" s="146"/>
-      <c r="E336" s="146"/>
-      <c r="F336" s="146"/>
-      <c r="G336" s="146"/>
+      <c r="E336" s="146">
+        <v>20.6</v>
+      </c>
+      <c r="F336" s="146">
+        <v>10</v>
+      </c>
+      <c r="G336" s="146">
+        <v>6</v>
+      </c>
       <c r="H336" s="147"/>
     </row>
-    <row r="337" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B337" s="149"/>
-      <c r="C337" s="145"/>
+    <row r="337" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="116" t="str">
+        <f>LEFT(B337, FIND("-", B337) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B337" s="116" t="inlineStr">
+        <is>
+          <t>HR-INTPROMO</t>
+        </is>
+      </c>
+      <c r="C337" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D337" s="146"/>
-      <c r="E337" s="146"/>
-      <c r="F337" s="146"/>
-      <c r="G337" s="146"/>
+      <c r="E337" s="146">
+        <v>17.6</v>
+      </c>
+      <c r="F337" s="146">
+        <v>10</v>
+      </c>
+      <c r="G337" s="146">
+        <v>6</v>
+      </c>
       <c r="H337" s="147"/>
     </row>
-    <row r="338" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B338" s="149"/>
-      <c r="C338" s="145"/>
+    <row r="338" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="116" t="str">
+        <f>LEFT(B338, FIND("-", B338) - 1)</f>
+        <v>HR</v>
+      </c>
+      <c r="B338" s="116" t="inlineStr">
+        <is>
+          <t>HR-INTPROMO</t>
+        </is>
+      </c>
+      <c r="C338" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D338" s="146"/>
-      <c r="E338" s="146"/>
-      <c r="F338" s="146"/>
-      <c r="G338" s="146"/>
+      <c r="E338" s="146">
+        <v>30.09</v>
+      </c>
+      <c r="F338" s="146">
+        <v>10</v>
+      </c>
+      <c r="G338" s="146">
+        <v>6</v>
+      </c>
       <c r="H338" s="147"/>
     </row>
-    <row r="339" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B339" s="149"/>
-      <c r="C339" s="145"/>
+    <row r="339" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="116" t="str">
+        <f>LEFT(B339, FIND("-", B339) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B339" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C339" s="145" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="D339" s="146"/>
-      <c r="E339" s="146"/>
-      <c r="F339" s="146"/>
+      <c r="E339" s="146">
+        <v>47</v>
+      </c>
+      <c r="F339" s="146">
+        <v>250</v>
+      </c>
       <c r="G339" s="146"/>
       <c r="H339" s="147"/>
     </row>
-    <row r="340" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B340" s="149"/>
-      <c r="C340" s="145"/>
+    <row r="340" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="116" t="str">
+        <f>LEFT(B340, FIND("-", B340) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B340" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C340" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D340" s="146"/>
-      <c r="E340" s="146"/>
-      <c r="F340" s="146"/>
+      <c r="E340" s="146">
+        <v>202</v>
+      </c>
+      <c r="F340" s="146">
+        <v>250</v>
+      </c>
       <c r="G340" s="146"/>
       <c r="H340" s="147"/>
     </row>
-    <row r="341" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B341" s="149"/>
-      <c r="C341" s="145"/>
+    <row r="341" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="116" t="str">
+        <f>LEFT(B341, FIND("-", B341) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B341" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C341" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D341" s="146"/>
-      <c r="E341" s="146"/>
-      <c r="F341" s="146"/>
+      <c r="E341" s="146">
+        <v>264</v>
+      </c>
+      <c r="F341" s="146">
+        <v>250</v>
+      </c>
       <c r="G341" s="146"/>
       <c r="H341" s="147"/>
     </row>
-    <row r="342" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B342" s="149"/>
-      <c r="C342" s="145"/>
+    <row r="342" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="116" t="str">
+        <f>LEFT(B342, FIND("-", B342) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B342" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C342" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D342" s="146"/>
-      <c r="E342" s="146"/>
-      <c r="F342" s="146"/>
+      <c r="E342" s="146">
+        <v>236</v>
+      </c>
+      <c r="F342" s="146">
+        <v>250</v>
+      </c>
       <c r="G342" s="146"/>
       <c r="H342" s="147"/>
     </row>
-    <row r="343" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B343" s="149"/>
-      <c r="C343" s="145"/>
+    <row r="343" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="116" t="str">
+        <f>LEFT(B343, FIND("-", B343) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B343" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C343" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D343" s="146"/>
-      <c r="E343" s="146"/>
-      <c r="F343" s="146"/>
+      <c r="E343" s="146">
+        <v>236</v>
+      </c>
+      <c r="F343" s="146">
+        <v>250</v>
+      </c>
       <c r="G343" s="146"/>
       <c r="H343" s="147"/>
     </row>
-    <row r="344" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B344" s="149"/>
-      <c r="C344" s="145"/>
+    <row r="344" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="116" t="str">
+        <f>LEFT(B344, FIND("-", B344) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B344" s="116" t="inlineStr">
+        <is>
+          <t>PROS-ALLCOMMEVENTS</t>
+        </is>
+      </c>
+      <c r="C344" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D344" s="146"/>
-      <c r="E344" s="146"/>
-      <c r="F344" s="146"/>
+      <c r="E344" s="146">
+        <v>239</v>
+      </c>
+      <c r="F344" s="146">
+        <v>250</v>
+      </c>
       <c r="G344" s="146"/>
       <c r="H344" s="147"/>
     </row>
-    <row r="345" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B345" s="149"/>
-      <c r="C345" s="145"/>
+    <row r="345" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="116" t="str">
+        <f>LEFT(B345, FIND("-", B345) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B345" s="116" t="inlineStr">
+        <is>
+          <t>PROS-PERMITNUM</t>
+        </is>
+      </c>
+      <c r="C345" s="145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="D345" s="146"/>
-      <c r="E345" s="146"/>
-      <c r="F345" s="146"/>
+      <c r="E345" s="146">
+        <v>171</v>
+      </c>
+      <c r="F345" s="146">
+        <v>240</v>
+      </c>
       <c r="G345" s="146"/>
       <c r="H345" s="147"/>
     </row>
-    <row r="346" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B346" s="149"/>
-      <c r="C346" s="145"/>
+    <row r="346" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="116" t="str">
+        <f>LEFT(B346, FIND("-", B346) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B346" s="116" t="inlineStr">
+        <is>
+          <t>PROS-PERMITNUM</t>
+        </is>
+      </c>
+      <c r="C346" s="145" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="D346" s="146"/>
-      <c r="E346" s="146"/>
-      <c r="F346" s="146"/>
+      <c r="E346" s="146">
+        <v>221</v>
+      </c>
+      <c r="F346" s="146">
+        <v>240</v>
+      </c>
       <c r="G346" s="146"/>
       <c r="H346" s="147"/>
     </row>
-    <row r="347" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B347" s="149"/>
-      <c r="C347" s="145"/>
+    <row r="347" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="116" t="str">
+        <f>LEFT(B347, FIND("-", B347) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B347" s="116" t="inlineStr">
+        <is>
+          <t>PROS-PERMITNUM</t>
+        </is>
+      </c>
+      <c r="C347" s="145" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="D347" s="146"/>
-      <c r="E347" s="146"/>
-      <c r="F347" s="146"/>
+      <c r="E347" s="146">
+        <v>242</v>
+      </c>
+      <c r="F347" s="146">
+        <v>240</v>
+      </c>
       <c r="G347" s="146"/>
       <c r="H347" s="147"/>
     </row>
-    <row r="348" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B348" s="149"/>
-      <c r="C348" s="145"/>
+    <row r="348" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348" s="116" t="str">
+        <f>LEFT(B348, FIND("-", B348) - 1)</f>
+        <v>PROS</v>
+      </c>
+      <c r="B348" s="116" t="inlineStr">
+        <is>
+          <t>PROS-PERMITNUM</t>
+        </is>
+      </c>
+      <c r="C348" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D348" s="146"/>
-      <c r="E348" s="146"/>
-      <c r="F348" s="146"/>
+      <c r="E348" s="146">
+        <v>239</v>
+      </c>
+      <c r="F348" s="146">
+        <v>240</v>
+      </c>
       <c r="G348" s="146"/>
       <c r="H348" s="147"/>
     </row>

--- a/KPI_Tracking.xlsx
+++ b/KPI_Tracking.xlsx
@@ -15868,7 +15868,7 @@
         <v>550</v>
       </c>
       <c r="J87" s="116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K87" s="116" t="s">
         <v>551</v>
@@ -17082,18 +17082,52 @@
         <f>IF(G111="","",IF(ISNUMBER(SEARCH(",",G111)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G111,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G111,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v/>
       </c>
-      <c r="I111" s="81"/>
-      <c r="J111" s="81"/>
-      <c r="K111" s="81"/>
-      <c r="L111" s="81"/>
+      <c r="I111" s="81" t="inlineStr">
+        <is>
+          <t>out of 5</t>
+        </is>
+      </c>
+      <c r="J111" s="81">
+        <v>2</v>
+      </c>
+      <c r="K111" s="81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L111" s="81" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M111" s="81"/>
       <c r="N111" s="81"/>
       <c r="O111" s="81"/>
-      <c r="P111" s="81"/>
-      <c r="Q111" s="81"/>
-      <c r="R111" s="81"/>
-      <c r="S111" s="81"/>
-      <c r="T111" s="81"/>
+      <c r="P111" s="81" t="inlineStr">
+        <is>
+          <t>Every year</t>
+        </is>
+      </c>
+      <c r="Q111" s="81" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="R111" s="81" t="inlineStr">
+        <is>
+          <t>IT Liaison Feedback Survey (Microsoft Forms)</t>
+        </is>
+      </c>
+      <c r="S111" s="81" t="inlineStr">
+        <is>
+          <t>Average rating from City department liaisons on four questions about the IT Department, on a 1 to 5 scale: how well IT understands their business needs, how proactive it is, how well its services align with their goals, and how innovative it is.</t>
+        </is>
+      </c>
+      <c r="T111" s="81" t="inlineStr">
+        <is>
+          <t>Overall is the average of all four questions. Responses are grouped by the year they were submitted; three test responses are excluded.</t>
+        </is>
+      </c>
       <c r="U111" s="85" t="str">
         <f>IF(B111="","",IF(IF(D111&lt;&gt;"",D111,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E111,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O111="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D111&lt;&gt;"",D111,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E111,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G111)),IF(O111="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O111="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D111&lt;&gt;"",D111,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E111,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Counts in Key Service gauge</v>
@@ -17125,18 +17159,52 @@
         <f>IF(G112="","",IF(ISNUMBER(SEARCH(",",G112)),"Several items (the script lists them)",IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(G112,'Dashboard Items'!$A$2:$A$495,0))&amp;": "&amp;INDEX('Dashboard Items'!$C$2:$C$495,MATCH(G112,'Dashboard Items'!$A$2:$A$495,0)),"ID not found")))</f>
         <v/>
       </c>
-      <c r="I112" s="81"/>
-      <c r="J112" s="81"/>
-      <c r="K112" s="81"/>
-      <c r="L112" s="81"/>
+      <c r="I112" s="81" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="J112" s="81">
+        <v>0</v>
+      </c>
+      <c r="K112" s="81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L112" s="81" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
       <c r="M112" s="81"/>
       <c r="N112" s="81"/>
       <c r="O112" s="81"/>
-      <c r="P112" s="81"/>
-      <c r="Q112" s="81"/>
-      <c r="R112" s="81"/>
-      <c r="S112" s="81"/>
-      <c r="T112" s="81"/>
+      <c r="P112" s="81" t="inlineStr">
+        <is>
+          <t>Every year</t>
+        </is>
+      </c>
+      <c r="Q112" s="81" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="R112" s="81" t="inlineStr">
+        <is>
+          <t>SysAid</t>
+        </is>
+      </c>
+      <c r="S112" s="81" t="inlineStr">
+        <is>
+          <t>Number of help desk tickets filed under the Applications category in SysAid each year, split into incidents (something stopped working) and requests (asking for access, installs or changes).</t>
+        </is>
+      </c>
+      <c r="T112" s="81" t="inlineStr">
+        <is>
+          <t>Counts tickets by the year they were opened. Automatic Workflow Processing tickets (P-card and Innoprise account setups) are excluded, and 2023 is left out because only 34 tickets were recorded. Largest SysAid sub-categories for 2025 and 2026: Microsoft Office Issues (453), CitySuite (388), Install/Update Program (325), Teams (162) and Adobe Acrobat (138); about 40% of tickets are filed as Other Issue or Request.</t>
+        </is>
+      </c>
       <c r="U112" s="85" t="str">
         <f>IF(B112="","",IF(IF(D112&lt;&gt;"",D112,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E112,'Dashboard Items'!$A$2:$A$495,0)),""))="Key Service",IF(O112="No","Key Service: shown, not counted","Counts in Key Service gauge"),IF(IF(D112&lt;&gt;"",D112,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E112,'Dashboard Items'!$A$2:$A$495,0)),""))="Program",IF(ISNUMBER(SEARCH("ks",G112)),IF(O112="No","Program, also at Key Service: not counted","Counts in Key Service gauge + sets Program chip"),IF(O112="No","Program: shown, no status chip","Sets Program status chip")),IF(IF(D112&lt;&gt;"",D112,IFERROR(INDEX('Dashboard Items'!$B$2:$B$495,MATCH(E112,'Dashboard Items'!$A$2:$A$495,0)),""))="Work System","Work System: shown, not counted","Check Level"))))</f>
         <v>Sets Program status chip</v>
@@ -30830,173 +30898,507 @@
       <c r="G348" s="146"/>
       <c r="H348" s="147"/>
     </row>
-    <row r="349" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B349" s="149"/>
-      <c r="C349" s="145"/>
+    <row r="349" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="116" t="str">
+        <f>LEFT(B349, FIND("-", B349) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B349" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C349" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D349" s="146"/>
-      <c r="E349" s="146"/>
+      <c r="E349" s="146">
+        <v>3.83</v>
+      </c>
       <c r="F349" s="146"/>
       <c r="G349" s="146"/>
-      <c r="H349" s="147"/>
-    </row>
-    <row r="350" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B350" s="149"/>
-      <c r="C350" s="145"/>
+      <c r="H349" s="147" t="inlineStr">
+        <is>
+          <t>6 responses</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="116" t="str">
+        <f>LEFT(B350, FIND("-", B350) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B350" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C350" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="D350" s="146"/>
-      <c r="E350" s="146"/>
+      <c r="E350" s="146">
+        <v>4.07</v>
+      </c>
       <c r="F350" s="146"/>
       <c r="G350" s="146"/>
-      <c r="H350" s="147"/>
-    </row>
-    <row r="351" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B351" s="149"/>
-      <c r="C351" s="145"/>
-      <c r="D351" s="146"/>
-      <c r="E351" s="146"/>
+      <c r="H350" s="147" t="inlineStr">
+        <is>
+          <t>Year to date: 17 responses through Sep 22, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="116" t="str">
+        <f>LEFT(B351, FIND("-", B351) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B351" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C351" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D351" s="146" t="inlineStr">
+        <is>
+          <t>Understands business needs</t>
+        </is>
+      </c>
+      <c r="E351" s="146">
+        <v>3.67</v>
+      </c>
       <c r="F351" s="146"/>
       <c r="G351" s="146"/>
       <c r="H351" s="147"/>
     </row>
-    <row r="352" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B352" s="149"/>
-      <c r="C352" s="145"/>
-      <c r="D352" s="146"/>
-      <c r="E352" s="146"/>
+    <row r="352" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="116" t="str">
+        <f>LEFT(B352, FIND("-", B352) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B352" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C352" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D352" s="146" t="inlineStr">
+        <is>
+          <t>Understands business needs</t>
+        </is>
+      </c>
+      <c r="E352" s="146">
+        <v>4.24</v>
+      </c>
       <c r="F352" s="146"/>
       <c r="G352" s="146"/>
       <c r="H352" s="147"/>
     </row>
-    <row r="353" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B353" s="149"/>
-      <c r="C353" s="145"/>
-      <c r="D353" s="146"/>
-      <c r="E353" s="146"/>
+    <row r="353" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="116" t="str">
+        <f>LEFT(B353, FIND("-", B353) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B353" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C353" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D353" s="146" t="inlineStr">
+        <is>
+          <t>Proactive</t>
+        </is>
+      </c>
+      <c r="E353" s="146">
+        <v>3.83</v>
+      </c>
       <c r="F353" s="146"/>
       <c r="G353" s="146"/>
       <c r="H353" s="147"/>
     </row>
-    <row r="354" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B354" s="149"/>
-      <c r="C354" s="145"/>
-      <c r="D354" s="146"/>
-      <c r="E354" s="146"/>
+    <row r="354" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="116" t="str">
+        <f>LEFT(B354, FIND("-", B354) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B354" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C354" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D354" s="146" t="inlineStr">
+        <is>
+          <t>Proactive</t>
+        </is>
+      </c>
+      <c r="E354" s="146">
+        <v>4.06</v>
+      </c>
       <c r="F354" s="146"/>
       <c r="G354" s="146"/>
       <c r="H354" s="147"/>
     </row>
-    <row r="355" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B355" s="149"/>
-      <c r="C355" s="145"/>
-      <c r="D355" s="146"/>
-      <c r="E355" s="146"/>
+    <row r="355" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355" s="116" t="str">
+        <f>LEFT(B355, FIND("-", B355) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B355" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C355" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D355" s="146" t="inlineStr">
+        <is>
+          <t>Aligned with business goals</t>
+        </is>
+      </c>
+      <c r="E355" s="146">
+        <v>4.33</v>
+      </c>
       <c r="F355" s="146"/>
       <c r="G355" s="146"/>
       <c r="H355" s="147"/>
     </row>
-    <row r="356" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B356" s="149"/>
-      <c r="C356" s="145"/>
-      <c r="D356" s="146"/>
-      <c r="E356" s="146"/>
+    <row r="356" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A356" s="116" t="str">
+        <f>LEFT(B356, FIND("-", B356) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B356" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C356" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D356" s="146" t="inlineStr">
+        <is>
+          <t>Aligned with business goals</t>
+        </is>
+      </c>
+      <c r="E356" s="146">
+        <v>4.24</v>
+      </c>
       <c r="F356" s="146"/>
       <c r="G356" s="146"/>
       <c r="H356" s="147"/>
     </row>
-    <row r="357" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B357" s="149"/>
-      <c r="C357" s="145"/>
-      <c r="D357" s="146"/>
-      <c r="E357" s="146"/>
+    <row r="357" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A357" s="116" t="str">
+        <f>LEFT(B357, FIND("-", B357) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B357" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C357" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D357" s="146" t="inlineStr">
+        <is>
+          <t>Innovative</t>
+        </is>
+      </c>
+      <c r="E357" s="146">
+        <v>3.5</v>
+      </c>
       <c r="F357" s="146"/>
       <c r="G357" s="146"/>
       <c r="H357" s="147"/>
     </row>
-    <row r="358" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B358" s="149"/>
-      <c r="C358" s="145"/>
-      <c r="D358" s="146"/>
-      <c r="E358" s="146"/>
+    <row r="358" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A358" s="116" t="str">
+        <f>LEFT(B358, FIND("-", B358) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B358" s="116" t="inlineStr">
+        <is>
+          <t>IT-LIAISONSURV</t>
+        </is>
+      </c>
+      <c r="C358" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D358" s="146" t="inlineStr">
+        <is>
+          <t>Innovative</t>
+        </is>
+      </c>
+      <c r="E358" s="146">
+        <v>3.76</v>
+      </c>
       <c r="F358" s="146"/>
       <c r="G358" s="146"/>
       <c r="H358" s="147"/>
     </row>
-    <row r="359" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B359" s="149"/>
-      <c r="C359" s="145"/>
+    <row r="359" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A359" s="116" t="str">
+        <f>LEFT(B359, FIND("-", B359) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B359" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C359" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
       <c r="D359" s="146"/>
-      <c r="E359" s="146"/>
+      <c r="E359" s="146">
+        <v>1919</v>
+      </c>
       <c r="F359" s="146"/>
       <c r="G359" s="146"/>
       <c r="H359" s="147"/>
     </row>
-    <row r="360" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B360" s="149"/>
-      <c r="C360" s="145"/>
-      <c r="D360" s="146"/>
-      <c r="E360" s="146"/>
+    <row r="360" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A360" s="116" t="str">
+        <f>LEFT(B360, FIND("-", B360) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B360" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C360" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D360" s="146" t="inlineStr">
+        <is>
+          <t>Incident</t>
+        </is>
+      </c>
+      <c r="E360" s="146">
+        <v>1456</v>
+      </c>
       <c r="F360" s="146"/>
       <c r="G360" s="146"/>
       <c r="H360" s="147"/>
     </row>
-    <row r="361" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B361" s="149"/>
-      <c r="C361" s="145"/>
-      <c r="D361" s="146"/>
-      <c r="E361" s="146"/>
+    <row r="361" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A361" s="116" t="str">
+        <f>LEFT(B361, FIND("-", B361) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B361" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C361" s="145" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D361" s="146" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="E361" s="146">
+        <v>463</v>
+      </c>
       <c r="F361" s="146"/>
       <c r="G361" s="146"/>
       <c r="H361" s="147"/>
     </row>
-    <row r="362" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B362" s="149"/>
-      <c r="C362" s="145"/>
+    <row r="362" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A362" s="116" t="str">
+        <f>LEFT(B362, FIND("-", B362) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B362" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C362" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="D362" s="146"/>
-      <c r="E362" s="146"/>
+      <c r="E362" s="146">
+        <v>1710</v>
+      </c>
       <c r="F362" s="146"/>
       <c r="G362" s="146"/>
       <c r="H362" s="147"/>
     </row>
-    <row r="363" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B363" s="149"/>
-      <c r="C363" s="145"/>
-      <c r="D363" s="146"/>
-      <c r="E363" s="146"/>
+    <row r="363" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363" s="116" t="str">
+        <f>LEFT(B363, FIND("-", B363) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B363" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C363" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D363" s="146" t="inlineStr">
+        <is>
+          <t>Incident</t>
+        </is>
+      </c>
+      <c r="E363" s="146">
+        <v>1176</v>
+      </c>
       <c r="F363" s="146"/>
       <c r="G363" s="146"/>
       <c r="H363" s="147"/>
     </row>
-    <row r="364" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B364" s="149"/>
-      <c r="C364" s="145"/>
-      <c r="D364" s="146"/>
-      <c r="E364" s="146"/>
+    <row r="364" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" s="116" t="str">
+        <f>LEFT(B364, FIND("-", B364) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B364" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C364" s="145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D364" s="146" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="E364" s="146">
+        <v>534</v>
+      </c>
       <c r="F364" s="146"/>
       <c r="G364" s="146"/>
       <c r="H364" s="147"/>
     </row>
-    <row r="365" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B365" s="149"/>
-      <c r="C365" s="145"/>
+    <row r="365" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365" s="116" t="str">
+        <f>LEFT(B365, FIND("-", B365) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B365" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C365" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="D365" s="146"/>
-      <c r="E365" s="146"/>
+      <c r="E365" s="146">
+        <v>1353</v>
+      </c>
       <c r="F365" s="146"/>
       <c r="G365" s="146"/>
-      <c r="H365" s="147"/>
-    </row>
-    <row r="366" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B366" s="149"/>
-      <c r="C366" s="145"/>
-      <c r="D366" s="146"/>
-      <c r="E366" s="146"/>
+      <c r="H365" s="147" t="inlineStr">
+        <is>
+          <t>Year to date: tickets opened through Oct 21, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="116" t="str">
+        <f>LEFT(B366, FIND("-", B366) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B366" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C366" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D366" s="146" t="inlineStr">
+        <is>
+          <t>Incident</t>
+        </is>
+      </c>
+      <c r="E366" s="146">
+        <v>747</v>
+      </c>
       <c r="F366" s="146"/>
       <c r="G366" s="146"/>
       <c r="H366" s="147"/>
     </row>
-    <row r="367" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B367" s="149"/>
-      <c r="C367" s="145"/>
-      <c r="D367" s="146"/>
-      <c r="E367" s="146"/>
+    <row r="367" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="116" t="str">
+        <f>LEFT(B367, FIND("-", B367) - 1)</f>
+        <v>IT</v>
+      </c>
+      <c r="B367" s="116" t="inlineStr">
+        <is>
+          <t>IT-APPTICKETS</t>
+        </is>
+      </c>
+      <c r="C367" s="145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D367" s="146" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="E367" s="146">
+        <v>606</v>
+      </c>
       <c r="F367" s="146"/>
       <c r="G367" s="146"/>
       <c r="H367" s="147"/>
